--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_laag.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_laag.xlsx
@@ -430,7 +430,7 @@
         <v>11495</v>
       </c>
       <c r="C2">
-        <v>10410</v>
+        <v>10894</v>
       </c>
       <c r="D2">
         <v>6742</v>
@@ -442,7 +442,7 @@
         <v>13294</v>
       </c>
       <c r="G2">
-        <v>14247</v>
+        <v>14254</v>
       </c>
       <c r="H2">
         <v>17594</v>
@@ -456,7 +456,7 @@
         <v>10950</v>
       </c>
       <c r="C3">
-        <v>10986</v>
+        <v>11590</v>
       </c>
       <c r="D3">
         <v>7537</v>
@@ -468,7 +468,7 @@
         <v>13115</v>
       </c>
       <c r="G3">
-        <v>15219</v>
+        <v>15227</v>
       </c>
       <c r="H3">
         <v>17857</v>
@@ -482,7 +482,7 @@
         <v>8997</v>
       </c>
       <c r="C4">
-        <v>8914</v>
+        <v>9121</v>
       </c>
       <c r="D4">
         <v>4916</v>
@@ -494,7 +494,7 @@
         <v>10663</v>
       </c>
       <c r="G4">
-        <v>11751</v>
+        <v>11807</v>
       </c>
       <c r="H4">
         <v>14363</v>
@@ -508,7 +508,7 @@
         <v>8997</v>
       </c>
       <c r="C5">
-        <v>8914</v>
+        <v>9121</v>
       </c>
       <c r="D5">
         <v>4916</v>
@@ -520,7 +520,7 @@
         <v>10663</v>
       </c>
       <c r="G5">
-        <v>11751</v>
+        <v>11807</v>
       </c>
       <c r="H5">
         <v>14363</v>
@@ -534,7 +534,7 @@
         <v>8997</v>
       </c>
       <c r="C6">
-        <v>8914</v>
+        <v>9121</v>
       </c>
       <c r="D6">
         <v>4916</v>
@@ -546,7 +546,7 @@
         <v>10663</v>
       </c>
       <c r="G6">
-        <v>11751</v>
+        <v>11807</v>
       </c>
       <c r="H6">
         <v>14363</v>
@@ -560,7 +560,7 @@
         <v>10950</v>
       </c>
       <c r="C7">
-        <v>10567</v>
+        <v>11191</v>
       </c>
       <c r="D7">
         <v>7537</v>
@@ -572,7 +572,7 @@
         <v>13115</v>
       </c>
       <c r="G7">
-        <v>14852</v>
+        <v>14865</v>
       </c>
       <c r="H7">
         <v>17532</v>
@@ -586,7 +586,7 @@
         <v>10950</v>
       </c>
       <c r="C8">
-        <v>10567</v>
+        <v>11191</v>
       </c>
       <c r="D8">
         <v>7537</v>
@@ -598,7 +598,7 @@
         <v>13115</v>
       </c>
       <c r="G8">
-        <v>14852</v>
+        <v>14865</v>
       </c>
       <c r="H8">
         <v>17532</v>
@@ -612,7 +612,7 @@
         <v>10950</v>
       </c>
       <c r="C9">
-        <v>10158</v>
+        <v>10801</v>
       </c>
       <c r="D9">
         <v>7537</v>
@@ -624,7 +624,7 @@
         <v>13115</v>
       </c>
       <c r="G9">
-        <v>14495</v>
+        <v>14511</v>
       </c>
       <c r="H9">
         <v>17214</v>
@@ -638,7 +638,7 @@
         <v>10950</v>
       </c>
       <c r="C10">
-        <v>10567</v>
+        <v>11191</v>
       </c>
       <c r="D10">
         <v>7537</v>
@@ -650,7 +650,7 @@
         <v>13115</v>
       </c>
       <c r="G10">
-        <v>14852</v>
+        <v>14865</v>
       </c>
       <c r="H10">
         <v>17532</v>
@@ -664,7 +664,7 @@
         <v>10950</v>
       </c>
       <c r="C11">
-        <v>10567</v>
+        <v>11191</v>
       </c>
       <c r="D11">
         <v>7537</v>
@@ -676,7 +676,7 @@
         <v>13115</v>
       </c>
       <c r="G11">
-        <v>14852</v>
+        <v>14865</v>
       </c>
       <c r="H11">
         <v>17532</v>
@@ -690,7 +690,7 @@
         <v>8997</v>
       </c>
       <c r="C12">
-        <v>8914</v>
+        <v>9121</v>
       </c>
       <c r="D12">
         <v>4916</v>
@@ -702,7 +702,7 @@
         <v>10663</v>
       </c>
       <c r="G12">
-        <v>11751</v>
+        <v>11807</v>
       </c>
       <c r="H12">
         <v>14363</v>
@@ -716,7 +716,7 @@
         <v>10950</v>
       </c>
       <c r="C13">
-        <v>10986</v>
+        <v>11590</v>
       </c>
       <c r="D13">
         <v>7537</v>
@@ -728,7 +728,7 @@
         <v>13115</v>
       </c>
       <c r="G13">
-        <v>15219</v>
+        <v>15227</v>
       </c>
       <c r="H13">
         <v>17857</v>
@@ -742,7 +742,7 @@
         <v>8997</v>
       </c>
       <c r="C14">
-        <v>8914</v>
+        <v>9121</v>
       </c>
       <c r="D14">
         <v>4916</v>
@@ -754,7 +754,7 @@
         <v>10663</v>
       </c>
       <c r="G14">
-        <v>11751</v>
+        <v>11807</v>
       </c>
       <c r="H14">
         <v>14363</v>
@@ -768,7 +768,7 @@
         <v>10950</v>
       </c>
       <c r="C15">
-        <v>10567</v>
+        <v>11191</v>
       </c>
       <c r="D15">
         <v>7537</v>
@@ -780,7 +780,7 @@
         <v>13115</v>
       </c>
       <c r="G15">
-        <v>14852</v>
+        <v>14865</v>
       </c>
       <c r="H15">
         <v>17532</v>
@@ -794,7 +794,7 @@
         <v>11495</v>
       </c>
       <c r="C16">
-        <v>9970</v>
+        <v>10469</v>
       </c>
       <c r="D16">
         <v>6742</v>
@@ -806,7 +806,7 @@
         <v>13294</v>
       </c>
       <c r="G16">
-        <v>13850</v>
+        <v>13862</v>
       </c>
       <c r="H16">
         <v>17253</v>
@@ -820,7 +820,7 @@
         <v>8997</v>
       </c>
       <c r="C17">
-        <v>8914</v>
+        <v>9121</v>
       </c>
       <c r="D17">
         <v>4916</v>
@@ -832,7 +832,7 @@
         <v>10663</v>
       </c>
       <c r="G17">
-        <v>11751</v>
+        <v>11807</v>
       </c>
       <c r="H17">
         <v>14363</v>
@@ -846,7 +846,7 @@
         <v>10950</v>
       </c>
       <c r="C18">
-        <v>10986</v>
+        <v>11590</v>
       </c>
       <c r="D18">
         <v>7537</v>
@@ -858,7 +858,7 @@
         <v>13115</v>
       </c>
       <c r="G18">
-        <v>15219</v>
+        <v>15227</v>
       </c>
       <c r="H18">
         <v>17857</v>
@@ -872,7 +872,7 @@
         <v>11495</v>
       </c>
       <c r="C19">
-        <v>9970</v>
+        <v>10469</v>
       </c>
       <c r="D19">
         <v>6742</v>
@@ -884,7 +884,7 @@
         <v>13294</v>
       </c>
       <c r="G19">
-        <v>13850</v>
+        <v>13862</v>
       </c>
       <c r="H19">
         <v>17253</v>
@@ -898,7 +898,7 @@
         <v>11495</v>
       </c>
       <c r="C20">
-        <v>9970</v>
+        <v>10469</v>
       </c>
       <c r="D20">
         <v>6742</v>
@@ -910,7 +910,7 @@
         <v>13294</v>
       </c>
       <c r="G20">
-        <v>13850</v>
+        <v>13862</v>
       </c>
       <c r="H20">
         <v>17253</v>
@@ -924,7 +924,7 @@
         <v>11495</v>
       </c>
       <c r="C21">
-        <v>9970</v>
+        <v>10469</v>
       </c>
       <c r="D21">
         <v>6742</v>
@@ -936,7 +936,7 @@
         <v>13294</v>
       </c>
       <c r="G21">
-        <v>13850</v>
+        <v>13862</v>
       </c>
       <c r="H21">
         <v>17253</v>
@@ -950,7 +950,7 @@
         <v>14730</v>
       </c>
       <c r="C22">
-        <v>13186</v>
+        <v>13615</v>
       </c>
       <c r="D22">
         <v>1908</v>
@@ -962,7 +962,7 @@
         <v>14923</v>
       </c>
       <c r="G22">
-        <v>14095</v>
+        <v>14367</v>
       </c>
       <c r="H22">
         <v>20999</v>
@@ -976,7 +976,7 @@
         <v>11495</v>
       </c>
       <c r="C23">
-        <v>10410</v>
+        <v>10894</v>
       </c>
       <c r="D23">
         <v>6742</v>
@@ -988,7 +988,7 @@
         <v>13294</v>
       </c>
       <c r="G23">
-        <v>14247</v>
+        <v>14254</v>
       </c>
       <c r="H23">
         <v>17594</v>
@@ -1002,7 +1002,7 @@
         <v>6968</v>
       </c>
       <c r="C24">
-        <v>6861</v>
+        <v>6920</v>
       </c>
       <c r="D24">
         <v>3289</v>
@@ -1014,7 +1014,7 @@
         <v>7444</v>
       </c>
       <c r="G24">
-        <v>8384</v>
+        <v>8385</v>
       </c>
       <c r="H24">
         <v>10353</v>
@@ -1028,7 +1028,7 @@
         <v>6968</v>
       </c>
       <c r="C25">
-        <v>6861</v>
+        <v>6920</v>
       </c>
       <c r="D25">
         <v>3289</v>
@@ -1040,7 +1040,7 @@
         <v>7444</v>
       </c>
       <c r="G25">
-        <v>8384</v>
+        <v>8385</v>
       </c>
       <c r="H25">
         <v>10353</v>
@@ -1054,7 +1054,7 @@
         <v>6968</v>
       </c>
       <c r="C26">
-        <v>6861</v>
+        <v>6920</v>
       </c>
       <c r="D26">
         <v>3289</v>
@@ -1066,7 +1066,7 @@
         <v>7444</v>
       </c>
       <c r="G26">
-        <v>8384</v>
+        <v>8385</v>
       </c>
       <c r="H26">
         <v>10353</v>
@@ -1080,7 +1080,7 @@
         <v>13522</v>
       </c>
       <c r="C27">
-        <v>9866</v>
+        <v>10098</v>
       </c>
       <c r="D27">
         <v>3217</v>
@@ -1092,7 +1092,7 @@
         <v>13898</v>
       </c>
       <c r="G27">
-        <v>11393</v>
+        <v>11426</v>
       </c>
       <c r="H27">
         <v>17163</v>
@@ -1106,7 +1106,7 @@
         <v>13522</v>
       </c>
       <c r="C28">
-        <v>9866</v>
+        <v>10098</v>
       </c>
       <c r="D28">
         <v>3217</v>
@@ -1118,7 +1118,7 @@
         <v>13898</v>
       </c>
       <c r="G28">
-        <v>11393</v>
+        <v>11426</v>
       </c>
       <c r="H28">
         <v>17163</v>
@@ -1132,7 +1132,7 @@
         <v>13522</v>
       </c>
       <c r="C29">
-        <v>9866</v>
+        <v>10098</v>
       </c>
       <c r="D29">
         <v>3217</v>
@@ -1144,7 +1144,7 @@
         <v>13898</v>
       </c>
       <c r="G29">
-        <v>11393</v>
+        <v>11426</v>
       </c>
       <c r="H29">
         <v>17163</v>
@@ -1158,7 +1158,7 @@
         <v>22665</v>
       </c>
       <c r="C30">
-        <v>13159</v>
+        <v>14384</v>
       </c>
       <c r="D30">
         <v>12854</v>
@@ -1170,7 +1170,7 @@
         <v>25117</v>
       </c>
       <c r="G30">
-        <v>20866</v>
+        <v>21013</v>
       </c>
       <c r="H30">
         <v>28821</v>
@@ -1184,7 +1184,7 @@
         <v>22665</v>
       </c>
       <c r="C31">
-        <v>13159</v>
+        <v>14384</v>
       </c>
       <c r="D31">
         <v>12854</v>
@@ -1196,7 +1196,7 @@
         <v>25117</v>
       </c>
       <c r="G31">
-        <v>20866</v>
+        <v>21013</v>
       </c>
       <c r="H31">
         <v>28821</v>
@@ -1210,7 +1210,7 @@
         <v>22665</v>
       </c>
       <c r="C32">
-        <v>13766</v>
+        <v>14955</v>
       </c>
       <c r="D32">
         <v>12854</v>
@@ -1222,7 +1222,7 @@
         <v>25117</v>
       </c>
       <c r="G32">
-        <v>21390</v>
+        <v>21534</v>
       </c>
       <c r="H32">
         <v>29232</v>
@@ -1236,7 +1236,7 @@
         <v>22665</v>
       </c>
       <c r="C33">
-        <v>13159</v>
+        <v>14384</v>
       </c>
       <c r="D33">
         <v>12854</v>
@@ -1248,7 +1248,7 @@
         <v>25117</v>
       </c>
       <c r="G33">
-        <v>20866</v>
+        <v>21013</v>
       </c>
       <c r="H33">
         <v>28821</v>
@@ -1262,22 +1262,22 @@
         <v>27989</v>
       </c>
       <c r="C34">
-        <v>16048</v>
+        <v>17665</v>
       </c>
       <c r="D34">
         <v>14142</v>
       </c>
       <c r="E34">
-        <v>32601</v>
+        <v>32619</v>
       </c>
       <c r="F34">
         <v>29597</v>
       </c>
       <c r="G34">
-        <v>24247</v>
+        <v>24623</v>
       </c>
       <c r="H34">
-        <v>33975</v>
+        <v>33990</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1288,7 +1288,7 @@
         <v>28724</v>
       </c>
       <c r="C35">
-        <v>16724</v>
+        <v>17717</v>
       </c>
       <c r="D35">
         <v>13465</v>
@@ -1300,7 +1300,7 @@
         <v>30146</v>
       </c>
       <c r="G35">
-        <v>24642</v>
+        <v>24782</v>
       </c>
       <c r="H35">
         <v>35252</v>
@@ -1314,7 +1314,7 @@
         <v>18829</v>
       </c>
       <c r="C36">
-        <v>11288</v>
+        <v>11879</v>
       </c>
       <c r="D36">
         <v>11925</v>
@@ -1326,7 +1326,7 @@
         <v>21926</v>
       </c>
       <c r="G36">
-        <v>18544</v>
+        <v>18617</v>
       </c>
       <c r="H36">
         <v>25066</v>
@@ -1340,7 +1340,7 @@
         <v>23067</v>
       </c>
       <c r="C37">
-        <v>13571</v>
+        <v>14892</v>
       </c>
       <c r="D37">
         <v>13102</v>
@@ -1352,7 +1352,7 @@
         <v>25377</v>
       </c>
       <c r="G37">
-        <v>21512</v>
+        <v>21579</v>
       </c>
       <c r="H37">
         <v>29538</v>
@@ -1366,7 +1366,7 @@
         <v>23067</v>
       </c>
       <c r="C38">
-        <v>13571</v>
+        <v>14892</v>
       </c>
       <c r="D38">
         <v>13102</v>
@@ -1378,7 +1378,7 @@
         <v>25377</v>
       </c>
       <c r="G38">
-        <v>21512</v>
+        <v>21579</v>
       </c>
       <c r="H38">
         <v>29538</v>
@@ -1392,22 +1392,22 @@
         <v>27989</v>
       </c>
       <c r="C39">
-        <v>15395</v>
+        <v>17076</v>
       </c>
       <c r="D39">
         <v>14142</v>
       </c>
       <c r="E39">
-        <v>32146</v>
+        <v>32164</v>
       </c>
       <c r="F39">
         <v>29597</v>
       </c>
       <c r="G39">
-        <v>23691</v>
+        <v>24082</v>
       </c>
       <c r="H39">
-        <v>33549</v>
+        <v>33564</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1418,7 +1418,7 @@
         <v>28724</v>
       </c>
       <c r="C40">
-        <v>16724</v>
+        <v>17717</v>
       </c>
       <c r="D40">
         <v>13465</v>
@@ -1430,7 +1430,7 @@
         <v>30146</v>
       </c>
       <c r="G40">
-        <v>24642</v>
+        <v>24782</v>
       </c>
       <c r="H40">
         <v>35252</v>
@@ -1444,7 +1444,7 @@
         <v>28724</v>
       </c>
       <c r="C41">
-        <v>16724</v>
+        <v>17717</v>
       </c>
       <c r="D41">
         <v>13465</v>
@@ -1456,7 +1456,7 @@
         <v>30146</v>
       </c>
       <c r="G41">
-        <v>24642</v>
+        <v>24782</v>
       </c>
       <c r="H41">
         <v>35252</v>
@@ -1470,7 +1470,7 @@
         <v>20187</v>
       </c>
       <c r="C42">
-        <v>12583</v>
+        <v>13418</v>
       </c>
       <c r="D42">
         <v>11552</v>
@@ -1482,7 +1482,7 @@
         <v>22425</v>
       </c>
       <c r="G42">
-        <v>19400</v>
+        <v>19448</v>
       </c>
       <c r="H42">
         <v>26633</v>
@@ -1496,7 +1496,7 @@
         <v>20187</v>
       </c>
       <c r="C43">
-        <v>13190</v>
+        <v>13998</v>
       </c>
       <c r="D43">
         <v>11552</v>
@@ -1508,7 +1508,7 @@
         <v>22425</v>
       </c>
       <c r="G43">
-        <v>19933</v>
+        <v>19980</v>
       </c>
       <c r="H43">
         <v>27068</v>
@@ -1522,7 +1522,7 @@
         <v>18733</v>
       </c>
       <c r="C44">
-        <v>13610</v>
+        <v>14230</v>
       </c>
       <c r="D44">
         <v>8522</v>
@@ -1534,7 +1534,7 @@
         <v>20077</v>
       </c>
       <c r="G44">
-        <v>18110</v>
+        <v>18273</v>
       </c>
       <c r="H44">
         <v>25135</v>
@@ -1548,7 +1548,7 @@
         <v>18179</v>
       </c>
       <c r="C45">
-        <v>10995</v>
+        <v>11656</v>
       </c>
       <c r="D45">
         <v>10462</v>
@@ -1560,7 +1560,7 @@
         <v>20650</v>
       </c>
       <c r="G45">
-        <v>17460</v>
+        <v>17465</v>
       </c>
       <c r="H45">
         <v>24242</v>
@@ -1574,7 +1574,7 @@
         <v>23067</v>
       </c>
       <c r="C46">
-        <v>14205</v>
+        <v>15495</v>
       </c>
       <c r="D46">
         <v>13102</v>
@@ -1586,7 +1586,7 @@
         <v>25377</v>
       </c>
       <c r="G46">
-        <v>22055</v>
+        <v>22121</v>
       </c>
       <c r="H46">
         <v>29978</v>
@@ -1600,7 +1600,7 @@
         <v>18829</v>
       </c>
       <c r="C47">
-        <v>11812</v>
+        <v>12372</v>
       </c>
       <c r="D47">
         <v>11925</v>
@@ -1612,7 +1612,7 @@
         <v>21926</v>
       </c>
       <c r="G47">
-        <v>18986</v>
+        <v>19058</v>
       </c>
       <c r="H47">
         <v>25420</v>
@@ -1626,7 +1626,7 @@
         <v>18179</v>
       </c>
       <c r="C48">
-        <v>11542</v>
+        <v>12188</v>
       </c>
       <c r="D48">
         <v>10462</v>
@@ -1638,7 +1638,7 @@
         <v>20650</v>
       </c>
       <c r="G48">
-        <v>17944</v>
+        <v>17948</v>
       </c>
       <c r="H48">
         <v>24634</v>
@@ -1652,7 +1652,7 @@
         <v>13844</v>
       </c>
       <c r="C49">
-        <v>11146</v>
+        <v>11781</v>
       </c>
       <c r="D49">
         <v>7581</v>
@@ -1664,7 +1664,7 @@
         <v>15622</v>
       </c>
       <c r="G49">
-        <v>15334</v>
+        <v>15370</v>
       </c>
       <c r="H49">
         <v>19561</v>
@@ -1678,7 +1678,7 @@
         <v>13821</v>
       </c>
       <c r="C50">
-        <v>10001</v>
+        <v>10447</v>
       </c>
       <c r="D50">
         <v>10724</v>
@@ -1690,7 +1690,7 @@
         <v>17337</v>
       </c>
       <c r="G50">
-        <v>16876</v>
+        <v>16890</v>
       </c>
       <c r="H50">
         <v>20354</v>
@@ -1704,7 +1704,7 @@
         <v>10444</v>
       </c>
       <c r="C51">
-        <v>9008</v>
+        <v>9415</v>
       </c>
       <c r="D51">
         <v>4446</v>
@@ -1716,7 +1716,7 @@
         <v>11038</v>
       </c>
       <c r="G51">
-        <v>11091</v>
+        <v>11123</v>
       </c>
       <c r="H51">
         <v>14627</v>
@@ -1730,7 +1730,7 @@
         <v>10816</v>
       </c>
       <c r="C52">
-        <v>9939</v>
+        <v>10306</v>
       </c>
       <c r="D52">
         <v>4312</v>
@@ -1742,7 +1742,7 @@
         <v>11296</v>
       </c>
       <c r="G52">
-        <v>11933</v>
+        <v>12007</v>
       </c>
       <c r="H52">
         <v>15607</v>
@@ -1756,7 +1756,7 @@
         <v>11224</v>
       </c>
       <c r="C53">
-        <v>8936</v>
+        <v>9601</v>
       </c>
       <c r="D53">
         <v>5126</v>
@@ -1768,7 +1768,7 @@
         <v>12103</v>
       </c>
       <c r="G53">
-        <v>11670</v>
+        <v>11690</v>
       </c>
       <c r="H53">
         <v>15438</v>
@@ -1782,7 +1782,7 @@
         <v>10444</v>
       </c>
       <c r="C54">
-        <v>8641</v>
+        <v>9059</v>
       </c>
       <c r="D54">
         <v>4446</v>
@@ -1794,7 +1794,7 @@
         <v>11038</v>
       </c>
       <c r="G54">
-        <v>10745</v>
+        <v>10779</v>
       </c>
       <c r="H54">
         <v>14336</v>
@@ -1808,7 +1808,7 @@
         <v>13821</v>
       </c>
       <c r="C55">
-        <v>10001</v>
+        <v>10447</v>
       </c>
       <c r="D55">
         <v>10724</v>
@@ -1820,7 +1820,7 @@
         <v>17337</v>
       </c>
       <c r="G55">
-        <v>16876</v>
+        <v>16890</v>
       </c>
       <c r="H55">
         <v>20354</v>
@@ -1834,7 +1834,7 @@
         <v>15947</v>
       </c>
       <c r="C56">
-        <v>13012</v>
+        <v>13520</v>
       </c>
       <c r="D56">
         <v>5226</v>
@@ -1846,7 +1846,7 @@
         <v>16648</v>
       </c>
       <c r="G56">
-        <v>15411</v>
+        <v>15702</v>
       </c>
       <c r="H56">
         <v>21155</v>
@@ -1860,7 +1860,7 @@
         <v>10045</v>
       </c>
       <c r="C57">
-        <v>9157</v>
+        <v>9417</v>
       </c>
       <c r="D57">
         <v>3810</v>
@@ -1872,7 +1872,7 @@
         <v>10461</v>
       </c>
       <c r="G57">
-        <v>10829</v>
+        <v>10863</v>
       </c>
       <c r="H57">
         <v>14234</v>
@@ -1886,7 +1886,7 @@
         <v>16656</v>
       </c>
       <c r="C58">
-        <v>10700</v>
+        <v>10909</v>
       </c>
       <c r="D58">
         <v>4683</v>
@@ -1898,7 +1898,7 @@
         <v>16984</v>
       </c>
       <c r="G58">
-        <v>12732</v>
+        <v>12781</v>
       </c>
       <c r="H58">
         <v>19704</v>
@@ -1912,7 +1912,7 @@
         <v>16656</v>
       </c>
       <c r="C59">
-        <v>10700</v>
+        <v>10909</v>
       </c>
       <c r="D59">
         <v>4683</v>
@@ -1924,7 +1924,7 @@
         <v>16984</v>
       </c>
       <c r="G59">
-        <v>12732</v>
+        <v>12781</v>
       </c>
       <c r="H59">
         <v>19704</v>
@@ -1938,7 +1938,7 @@
         <v>8608</v>
       </c>
       <c r="C60">
-        <v>7228</v>
+        <v>7374</v>
       </c>
       <c r="D60">
         <v>3245</v>
@@ -1950,7 +1950,7 @@
         <v>9119</v>
       </c>
       <c r="G60">
-        <v>8745</v>
+        <v>8770</v>
       </c>
       <c r="H60">
         <v>11599</v>
@@ -1964,7 +1964,7 @@
         <v>8608</v>
       </c>
       <c r="C61">
-        <v>7228</v>
+        <v>7374</v>
       </c>
       <c r="D61">
         <v>3245</v>
@@ -1976,7 +1976,7 @@
         <v>9119</v>
       </c>
       <c r="G61">
-        <v>8745</v>
+        <v>8770</v>
       </c>
       <c r="H61">
         <v>11599</v>
@@ -1990,7 +1990,7 @@
         <v>3059</v>
       </c>
       <c r="C62">
-        <v>4052</v>
+        <v>4125</v>
       </c>
       <c r="D62">
         <v>1308</v>
@@ -2002,7 +2002,7 @@
         <v>3405</v>
       </c>
       <c r="G62">
-        <v>4704</v>
+        <v>4716</v>
       </c>
       <c r="H62">
         <v>5771</v>
@@ -2016,7 +2016,7 @@
         <v>3059</v>
       </c>
       <c r="C63">
-        <v>4052</v>
+        <v>4125</v>
       </c>
       <c r="D63">
         <v>1308</v>
@@ -2028,7 +2028,7 @@
         <v>3405</v>
       </c>
       <c r="G63">
-        <v>4704</v>
+        <v>4716</v>
       </c>
       <c r="H63">
         <v>5771</v>
@@ -2042,7 +2042,7 @@
         <v>1689</v>
       </c>
       <c r="C64">
-        <v>3130</v>
+        <v>3179</v>
       </c>
       <c r="D64">
         <v>703</v>
@@ -2054,7 +2054,7 @@
         <v>2015</v>
       </c>
       <c r="G64">
-        <v>3545</v>
+        <v>3567</v>
       </c>
       <c r="H64">
         <v>4170</v>
@@ -2068,7 +2068,7 @@
         <v>1689</v>
       </c>
       <c r="C65">
-        <v>3130</v>
+        <v>3179</v>
       </c>
       <c r="D65">
         <v>703</v>
@@ -2080,7 +2080,7 @@
         <v>2015</v>
       </c>
       <c r="G65">
-        <v>3545</v>
+        <v>3567</v>
       </c>
       <c r="H65">
         <v>4170</v>
@@ -2094,7 +2094,7 @@
         <v>12077</v>
       </c>
       <c r="C66">
-        <v>11269</v>
+        <v>11696</v>
       </c>
       <c r="D66">
         <v>8309</v>
@@ -2106,7 +2106,7 @@
         <v>14755</v>
       </c>
       <c r="G66">
-        <v>16126</v>
+        <v>16147</v>
       </c>
       <c r="H66">
         <v>19365</v>
@@ -2120,7 +2120,7 @@
         <v>12077</v>
       </c>
       <c r="C67">
-        <v>11730</v>
+        <v>12138</v>
       </c>
       <c r="D67">
         <v>8309</v>
@@ -2132,7 +2132,7 @@
         <v>14755</v>
       </c>
       <c r="G67">
-        <v>16532</v>
+        <v>16549</v>
       </c>
       <c r="H67">
         <v>19716</v>
@@ -2146,7 +2146,7 @@
         <v>12077</v>
       </c>
       <c r="C68">
-        <v>11269</v>
+        <v>11696</v>
       </c>
       <c r="D68">
         <v>8309</v>
@@ -2158,7 +2158,7 @@
         <v>14755</v>
       </c>
       <c r="G68">
-        <v>16126</v>
+        <v>16147</v>
       </c>
       <c r="H68">
         <v>19365</v>
@@ -2172,7 +2172,7 @@
         <v>12077</v>
       </c>
       <c r="C69">
-        <v>11730</v>
+        <v>12138</v>
       </c>
       <c r="D69">
         <v>8309</v>
@@ -2184,7 +2184,7 @@
         <v>14755</v>
       </c>
       <c r="G69">
-        <v>16532</v>
+        <v>16549</v>
       </c>
       <c r="H69">
         <v>19716</v>
@@ -2198,7 +2198,7 @@
         <v>12077</v>
       </c>
       <c r="C70">
-        <v>11730</v>
+        <v>12138</v>
       </c>
       <c r="D70">
         <v>8309</v>
@@ -2210,7 +2210,7 @@
         <v>14755</v>
       </c>
       <c r="G70">
-        <v>16532</v>
+        <v>16549</v>
       </c>
       <c r="H70">
         <v>19716</v>
@@ -2224,7 +2224,7 @@
         <v>13205</v>
       </c>
       <c r="C71">
-        <v>12483</v>
+        <v>12818</v>
       </c>
       <c r="D71">
         <v>9243</v>
@@ -2236,7 +2236,7 @@
         <v>16291</v>
       </c>
       <c r="G71">
-        <v>18021</v>
+        <v>18032</v>
       </c>
       <c r="H71">
         <v>21627</v>
@@ -2250,7 +2250,7 @@
         <v>12077</v>
       </c>
       <c r="C72">
-        <v>11730</v>
+        <v>12138</v>
       </c>
       <c r="D72">
         <v>8309</v>
@@ -2262,7 +2262,7 @@
         <v>14755</v>
       </c>
       <c r="G72">
-        <v>16532</v>
+        <v>16549</v>
       </c>
       <c r="H72">
         <v>19716</v>
@@ -2276,7 +2276,7 @@
         <v>12077</v>
       </c>
       <c r="C73">
-        <v>11730</v>
+        <v>12138</v>
       </c>
       <c r="D73">
         <v>8309</v>
@@ -2288,7 +2288,7 @@
         <v>14755</v>
       </c>
       <c r="G73">
-        <v>16532</v>
+        <v>16549</v>
       </c>
       <c r="H73">
         <v>19716</v>
@@ -2302,7 +2302,7 @@
         <v>12077</v>
       </c>
       <c r="C74">
-        <v>11730</v>
+        <v>12138</v>
       </c>
       <c r="D74">
         <v>8309</v>
@@ -2314,7 +2314,7 @@
         <v>14755</v>
       </c>
       <c r="G74">
-        <v>16532</v>
+        <v>16549</v>
       </c>
       <c r="H74">
         <v>19716</v>
@@ -2328,7 +2328,7 @@
         <v>8904</v>
       </c>
       <c r="C75">
-        <v>8394</v>
+        <v>8564</v>
       </c>
       <c r="D75">
         <v>4147</v>
@@ -2340,7 +2340,7 @@
         <v>10164</v>
       </c>
       <c r="G75">
-        <v>10732</v>
+        <v>10737</v>
       </c>
       <c r="H75">
         <v>13711</v>
@@ -2354,7 +2354,7 @@
         <v>12077</v>
       </c>
       <c r="C76">
-        <v>11730</v>
+        <v>12138</v>
       </c>
       <c r="D76">
         <v>8309</v>
@@ -2366,7 +2366,7 @@
         <v>14755</v>
       </c>
       <c r="G76">
-        <v>16532</v>
+        <v>16549</v>
       </c>
       <c r="H76">
         <v>19716</v>
@@ -2380,7 +2380,7 @@
         <v>11761</v>
       </c>
       <c r="C77">
-        <v>11014</v>
+        <v>11338</v>
       </c>
       <c r="D77">
         <v>7733</v>
@@ -2392,7 +2392,7 @@
         <v>14077</v>
       </c>
       <c r="G77">
-        <v>15442</v>
+        <v>15452</v>
       </c>
       <c r="H77">
         <v>18690</v>
@@ -2406,7 +2406,7 @@
         <v>11761</v>
       </c>
       <c r="C78">
-        <v>11014</v>
+        <v>11338</v>
       </c>
       <c r="D78">
         <v>7733</v>
@@ -2418,7 +2418,7 @@
         <v>14077</v>
       </c>
       <c r="G78">
-        <v>15442</v>
+        <v>15452</v>
       </c>
       <c r="H78">
         <v>18690</v>
@@ -2432,7 +2432,7 @@
         <v>11761</v>
       </c>
       <c r="C79">
-        <v>11014</v>
+        <v>11338</v>
       </c>
       <c r="D79">
         <v>7733</v>
@@ -2444,7 +2444,7 @@
         <v>14077</v>
       </c>
       <c r="G79">
-        <v>15442</v>
+        <v>15452</v>
       </c>
       <c r="H79">
         <v>18690</v>
@@ -2458,7 +2458,7 @@
         <v>11761</v>
       </c>
       <c r="C80">
-        <v>11014</v>
+        <v>11338</v>
       </c>
       <c r="D80">
         <v>7733</v>
@@ -2470,7 +2470,7 @@
         <v>14077</v>
       </c>
       <c r="G80">
-        <v>15442</v>
+        <v>15452</v>
       </c>
       <c r="H80">
         <v>18690</v>
@@ -2484,7 +2484,7 @@
         <v>20111</v>
       </c>
       <c r="C81">
-        <v>14404</v>
+        <v>14759</v>
       </c>
       <c r="D81">
         <v>11751</v>
@@ -2496,7 +2496,7 @@
         <v>23498</v>
       </c>
       <c r="G81">
-        <v>21640</v>
+        <v>21656</v>
       </c>
       <c r="H81">
         <v>28041</v>
@@ -2510,7 +2510,7 @@
         <v>20111</v>
       </c>
       <c r="C82">
-        <v>14404</v>
+        <v>14759</v>
       </c>
       <c r="D82">
         <v>11751</v>
@@ -2522,7 +2522,7 @@
         <v>23498</v>
       </c>
       <c r="G82">
-        <v>21640</v>
+        <v>21656</v>
       </c>
       <c r="H82">
         <v>28041</v>
@@ -2536,7 +2536,7 @@
         <v>12548</v>
       </c>
       <c r="C83">
-        <v>9728</v>
+        <v>9826</v>
       </c>
       <c r="D83">
         <v>2904</v>
@@ -2548,7 +2548,7 @@
         <v>13025</v>
       </c>
       <c r="G83">
-        <v>11293</v>
+        <v>11313</v>
       </c>
       <c r="H83">
         <v>17135</v>
@@ -2562,7 +2562,7 @@
         <v>12548</v>
       </c>
       <c r="C84">
-        <v>9728</v>
+        <v>9826</v>
       </c>
       <c r="D84">
         <v>2904</v>
@@ -2574,7 +2574,7 @@
         <v>13025</v>
       </c>
       <c r="G84">
-        <v>11293</v>
+        <v>11313</v>
       </c>
       <c r="H84">
         <v>17135</v>
@@ -2588,7 +2588,7 @@
         <v>20986</v>
       </c>
       <c r="C85">
-        <v>13996</v>
+        <v>14389</v>
       </c>
       <c r="D85">
         <v>4253</v>
@@ -2600,7 +2600,7 @@
         <v>21349</v>
       </c>
       <c r="G85">
-        <v>16194</v>
+        <v>16299</v>
       </c>
       <c r="H85">
         <v>26942</v>
@@ -2614,7 +2614,7 @@
         <v>20986</v>
       </c>
       <c r="C86">
-        <v>13996</v>
+        <v>14389</v>
       </c>
       <c r="D86">
         <v>4253</v>
@@ -2626,7 +2626,7 @@
         <v>21349</v>
       </c>
       <c r="G86">
-        <v>16194</v>
+        <v>16299</v>
       </c>
       <c r="H86">
         <v>26942</v>
@@ -2640,7 +2640,7 @@
         <v>20344</v>
       </c>
       <c r="C87">
-        <v>14286</v>
+        <v>14682</v>
       </c>
       <c r="D87">
         <v>1507</v>
@@ -2652,7 +2652,7 @@
         <v>20625</v>
       </c>
       <c r="G87">
-        <v>14992</v>
+        <v>15331</v>
       </c>
       <c r="H87">
         <v>25806</v>
@@ -2666,7 +2666,7 @@
         <v>20344</v>
       </c>
       <c r="C88">
-        <v>14286</v>
+        <v>14682</v>
       </c>
       <c r="D88">
         <v>1507</v>
@@ -2678,7 +2678,7 @@
         <v>20625</v>
       </c>
       <c r="G88">
-        <v>14992</v>
+        <v>15331</v>
       </c>
       <c r="H88">
         <v>25806</v>
@@ -2692,7 +2692,7 @@
         <v>20344</v>
       </c>
       <c r="C89">
-        <v>14286</v>
+        <v>14682</v>
       </c>
       <c r="D89">
         <v>1507</v>
@@ -2704,7 +2704,7 @@
         <v>20625</v>
       </c>
       <c r="G89">
-        <v>14992</v>
+        <v>15331</v>
       </c>
       <c r="H89">
         <v>25806</v>
@@ -2718,7 +2718,7 @@
         <v>44253</v>
       </c>
       <c r="C90">
-        <v>25769</v>
+        <v>31430</v>
       </c>
       <c r="D90">
         <v>40385</v>
@@ -2730,10 +2730,10 @@
         <v>49711</v>
       </c>
       <c r="G90">
-        <v>50737</v>
+        <v>50838</v>
       </c>
       <c r="H90">
-        <v>55671</v>
+        <v>55672</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2744,7 +2744,7 @@
         <v>44253</v>
       </c>
       <c r="C91">
-        <v>25769</v>
+        <v>31430</v>
       </c>
       <c r="D91">
         <v>40385</v>
@@ -2756,10 +2756,10 @@
         <v>49711</v>
       </c>
       <c r="G91">
-        <v>50737</v>
+        <v>50838</v>
       </c>
       <c r="H91">
-        <v>55671</v>
+        <v>55672</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2770,7 +2770,7 @@
         <v>44253</v>
       </c>
       <c r="C92">
-        <v>25769</v>
+        <v>31430</v>
       </c>
       <c r="D92">
         <v>40385</v>
@@ -2782,10 +2782,10 @@
         <v>49711</v>
       </c>
       <c r="G92">
-        <v>50737</v>
+        <v>50838</v>
       </c>
       <c r="H92">
-        <v>55671</v>
+        <v>55672</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2796,7 +2796,7 @@
         <v>44253</v>
       </c>
       <c r="C93">
-        <v>25769</v>
+        <v>31430</v>
       </c>
       <c r="D93">
         <v>40385</v>
@@ -2808,10 +2808,10 @@
         <v>49711</v>
       </c>
       <c r="G93">
-        <v>50737</v>
+        <v>50838</v>
       </c>
       <c r="H93">
-        <v>55671</v>
+        <v>55672</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -2822,19 +2822,19 @@
         <v>44748</v>
       </c>
       <c r="C94">
-        <v>27522</v>
+        <v>32245</v>
       </c>
       <c r="D94">
         <v>38768</v>
       </c>
       <c r="E94">
-        <v>52411</v>
+        <v>52419</v>
       </c>
       <c r="F94">
         <v>50019</v>
       </c>
       <c r="G94">
-        <v>50775</v>
+        <v>50964</v>
       </c>
       <c r="H94">
         <v>56619</v>
@@ -2848,7 +2848,7 @@
         <v>44253</v>
       </c>
       <c r="C95">
-        <v>25769</v>
+        <v>31430</v>
       </c>
       <c r="D95">
         <v>40385</v>
@@ -2860,10 +2860,10 @@
         <v>49711</v>
       </c>
       <c r="G95">
-        <v>50737</v>
+        <v>50838</v>
       </c>
       <c r="H95">
-        <v>55671</v>
+        <v>55672</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -2874,7 +2874,7 @@
         <v>44253</v>
       </c>
       <c r="C96">
-        <v>25769</v>
+        <v>31430</v>
       </c>
       <c r="D96">
         <v>40385</v>
@@ -2886,10 +2886,10 @@
         <v>49711</v>
       </c>
       <c r="G96">
-        <v>50737</v>
+        <v>50838</v>
       </c>
       <c r="H96">
-        <v>55671</v>
+        <v>55672</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -2900,7 +2900,7 @@
         <v>44253</v>
       </c>
       <c r="C97">
-        <v>25769</v>
+        <v>31430</v>
       </c>
       <c r="D97">
         <v>40385</v>
@@ -2912,10 +2912,10 @@
         <v>49711</v>
       </c>
       <c r="G97">
-        <v>50737</v>
+        <v>50838</v>
       </c>
       <c r="H97">
-        <v>55671</v>
+        <v>55672</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -2926,7 +2926,7 @@
         <v>42085</v>
       </c>
       <c r="C98">
-        <v>25048</v>
+        <v>30047</v>
       </c>
       <c r="D98">
         <v>35970</v>
@@ -2938,7 +2938,7 @@
         <v>46615</v>
       </c>
       <c r="G98">
-        <v>47361</v>
+        <v>47473</v>
       </c>
       <c r="H98">
         <v>53353</v>
@@ -2952,7 +2952,7 @@
         <v>42085</v>
       </c>
       <c r="C99">
-        <v>25048</v>
+        <v>30047</v>
       </c>
       <c r="D99">
         <v>35970</v>
@@ -2964,7 +2964,7 @@
         <v>46615</v>
       </c>
       <c r="G99">
-        <v>47361</v>
+        <v>47473</v>
       </c>
       <c r="H99">
         <v>53353</v>
@@ -2978,7 +2978,7 @@
         <v>43795</v>
       </c>
       <c r="C100">
-        <v>25026</v>
+        <v>30037</v>
       </c>
       <c r="D100">
         <v>34829</v>
@@ -2990,7 +2990,7 @@
         <v>47200</v>
       </c>
       <c r="G100">
-        <v>46355</v>
+        <v>46506</v>
       </c>
       <c r="H100">
         <v>53168</v>
@@ -3004,7 +3004,7 @@
         <v>43795</v>
       </c>
       <c r="C101">
-        <v>25026</v>
+        <v>30037</v>
       </c>
       <c r="D101">
         <v>34829</v>
@@ -3016,7 +3016,7 @@
         <v>47200</v>
       </c>
       <c r="G101">
-        <v>46355</v>
+        <v>46506</v>
       </c>
       <c r="H101">
         <v>53168</v>
@@ -3030,7 +3030,7 @@
         <v>43795</v>
       </c>
       <c r="C102">
-        <v>25026</v>
+        <v>30037</v>
       </c>
       <c r="D102">
         <v>34829</v>
@@ -3042,7 +3042,7 @@
         <v>47200</v>
       </c>
       <c r="G102">
-        <v>46355</v>
+        <v>46506</v>
       </c>
       <c r="H102">
         <v>53168</v>
@@ -3056,7 +3056,7 @@
         <v>39732</v>
       </c>
       <c r="C103">
-        <v>24075</v>
+        <v>28327</v>
       </c>
       <c r="D103">
         <v>31198</v>
@@ -3068,7 +3068,7 @@
         <v>43581</v>
       </c>
       <c r="G103">
-        <v>43370</v>
+        <v>43526</v>
       </c>
       <c r="H103">
         <v>50510</v>
@@ -3082,7 +3082,7 @@
         <v>39732</v>
       </c>
       <c r="C104">
-        <v>24075</v>
+        <v>28327</v>
       </c>
       <c r="D104">
         <v>31198</v>
@@ -3094,7 +3094,7 @@
         <v>43581</v>
       </c>
       <c r="G104">
-        <v>43370</v>
+        <v>43526</v>
       </c>
       <c r="H104">
         <v>50510</v>
@@ -3108,7 +3108,7 @@
         <v>41292</v>
       </c>
       <c r="C105">
-        <v>23631</v>
+        <v>26852</v>
       </c>
       <c r="D105">
         <v>33095</v>
@@ -3120,7 +3120,7 @@
         <v>44893</v>
       </c>
       <c r="G105">
-        <v>43938</v>
+        <v>43998</v>
       </c>
       <c r="H105">
         <v>50834</v>
@@ -3134,7 +3134,7 @@
         <v>39732</v>
       </c>
       <c r="C106">
-        <v>25934</v>
+        <v>29922</v>
       </c>
       <c r="D106">
         <v>31198</v>
@@ -3146,7 +3146,7 @@
         <v>43581</v>
       </c>
       <c r="G106">
-        <v>44741</v>
+        <v>44893</v>
       </c>
       <c r="H106">
         <v>51673</v>
@@ -3160,7 +3160,7 @@
         <v>39732</v>
       </c>
       <c r="C107">
-        <v>25934</v>
+        <v>29922</v>
       </c>
       <c r="D107">
         <v>31198</v>
@@ -3172,7 +3172,7 @@
         <v>43581</v>
       </c>
       <c r="G107">
-        <v>44741</v>
+        <v>44893</v>
       </c>
       <c r="H107">
         <v>51673</v>
@@ -3186,7 +3186,7 @@
         <v>41292</v>
       </c>
       <c r="C108">
-        <v>25485</v>
+        <v>28449</v>
       </c>
       <c r="D108">
         <v>33095</v>
@@ -3198,7 +3198,7 @@
         <v>44893</v>
       </c>
       <c r="G108">
-        <v>45270</v>
+        <v>45328</v>
       </c>
       <c r="H108">
         <v>51944</v>
@@ -3212,7 +3212,7 @@
         <v>39116</v>
       </c>
       <c r="C109">
-        <v>23538</v>
+        <v>27594</v>
       </c>
       <c r="D109">
         <v>29788</v>
@@ -3224,7 +3224,7 @@
         <v>43121</v>
       </c>
       <c r="G109">
-        <v>42341</v>
+        <v>42493</v>
       </c>
       <c r="H109">
         <v>50121</v>
@@ -3238,7 +3238,7 @@
         <v>39116</v>
       </c>
       <c r="C110">
-        <v>23538</v>
+        <v>27594</v>
       </c>
       <c r="D110">
         <v>29788</v>
@@ -3250,7 +3250,7 @@
         <v>43121</v>
       </c>
       <c r="G110">
-        <v>42341</v>
+        <v>42493</v>
       </c>
       <c r="H110">
         <v>50121</v>
@@ -3264,7 +3264,7 @@
         <v>39116</v>
       </c>
       <c r="C111">
-        <v>23538</v>
+        <v>27594</v>
       </c>
       <c r="D111">
         <v>29788</v>
@@ -3276,7 +3276,7 @@
         <v>43121</v>
       </c>
       <c r="G111">
-        <v>42341</v>
+        <v>42493</v>
       </c>
       <c r="H111">
         <v>50121</v>
@@ -3290,22 +3290,22 @@
         <v>39718</v>
       </c>
       <c r="C112">
-        <v>24333</v>
+        <v>29392</v>
       </c>
       <c r="D112">
         <v>31408</v>
       </c>
       <c r="E112">
-        <v>47955</v>
+        <v>47957</v>
       </c>
       <c r="F112">
         <v>43784</v>
       </c>
       <c r="G112">
-        <v>44177</v>
+        <v>44396</v>
       </c>
       <c r="H112">
-        <v>51220</v>
+        <v>51222</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -3316,7 +3316,7 @@
         <v>38292</v>
       </c>
       <c r="C113">
-        <v>23228</v>
+        <v>26298</v>
       </c>
       <c r="D113">
         <v>28732</v>
@@ -3328,7 +3328,7 @@
         <v>42232</v>
       </c>
       <c r="G113">
-        <v>40797</v>
+        <v>40945</v>
       </c>
       <c r="H113">
         <v>48853</v>
@@ -3342,7 +3342,7 @@
         <v>38292</v>
       </c>
       <c r="C114">
-        <v>24183</v>
+        <v>27106</v>
       </c>
       <c r="D114">
         <v>28732</v>
@@ -3354,7 +3354,7 @@
         <v>42232</v>
       </c>
       <c r="G114">
-        <v>41484</v>
+        <v>41628</v>
       </c>
       <c r="H114">
         <v>49418</v>
@@ -3368,22 +3368,22 @@
         <v>39718</v>
       </c>
       <c r="C115">
-        <v>24333</v>
+        <v>29392</v>
       </c>
       <c r="D115">
         <v>31408</v>
       </c>
       <c r="E115">
-        <v>47955</v>
+        <v>47957</v>
       </c>
       <c r="F115">
         <v>43784</v>
       </c>
       <c r="G115">
-        <v>44177</v>
+        <v>44396</v>
       </c>
       <c r="H115">
-        <v>51220</v>
+        <v>51222</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -3394,22 +3394,22 @@
         <v>39718</v>
       </c>
       <c r="C116">
-        <v>24333</v>
+        <v>29392</v>
       </c>
       <c r="D116">
         <v>31408</v>
       </c>
       <c r="E116">
-        <v>47955</v>
+        <v>47957</v>
       </c>
       <c r="F116">
         <v>43784</v>
       </c>
       <c r="G116">
-        <v>44177</v>
+        <v>44396</v>
       </c>
       <c r="H116">
-        <v>51220</v>
+        <v>51222</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -3420,7 +3420,7 @@
         <v>38292</v>
       </c>
       <c r="C117">
-        <v>23228</v>
+        <v>26298</v>
       </c>
       <c r="D117">
         <v>28732</v>
@@ -3432,7 +3432,7 @@
         <v>42232</v>
       </c>
       <c r="G117">
-        <v>40797</v>
+        <v>40945</v>
       </c>
       <c r="H117">
         <v>48853</v>
@@ -3446,7 +3446,7 @@
         <v>38292</v>
       </c>
       <c r="C118">
-        <v>25141</v>
+        <v>27913</v>
       </c>
       <c r="D118">
         <v>28732</v>
@@ -3458,7 +3458,7 @@
         <v>42232</v>
       </c>
       <c r="G118">
-        <v>42181</v>
+        <v>42320</v>
       </c>
       <c r="H118">
         <v>50001</v>
@@ -3472,7 +3472,7 @@
         <v>36866</v>
       </c>
       <c r="C119">
-        <v>21590</v>
+        <v>23617</v>
       </c>
       <c r="D119">
         <v>25039</v>
@@ -3484,7 +3484,7 @@
         <v>40552</v>
       </c>
       <c r="G119">
-        <v>37428</v>
+        <v>37531</v>
       </c>
       <c r="H119">
         <v>46892</v>
@@ -3498,22 +3498,22 @@
         <v>43034</v>
       </c>
       <c r="C120">
-        <v>24993</v>
+        <v>30432</v>
       </c>
       <c r="D120">
         <v>35777</v>
       </c>
       <c r="E120">
-        <v>50256</v>
+        <v>50257</v>
       </c>
       <c r="F120">
         <v>47154</v>
       </c>
       <c r="G120">
-        <v>47099</v>
+        <v>47226</v>
       </c>
       <c r="H120">
-        <v>53557</v>
+        <v>53558</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -3524,22 +3524,22 @@
         <v>43034</v>
       </c>
       <c r="C121">
-        <v>24993</v>
+        <v>30432</v>
       </c>
       <c r="D121">
         <v>35777</v>
       </c>
       <c r="E121">
-        <v>50256</v>
+        <v>50257</v>
       </c>
       <c r="F121">
         <v>47154</v>
       </c>
       <c r="G121">
-        <v>47099</v>
+        <v>47226</v>
       </c>
       <c r="H121">
-        <v>53557</v>
+        <v>53558</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -3550,7 +3550,7 @@
         <v>41394</v>
       </c>
       <c r="C122">
-        <v>25217</v>
+        <v>28872</v>
       </c>
       <c r="D122">
         <v>29582</v>
@@ -3562,7 +3562,7 @@
         <v>44513</v>
       </c>
       <c r="G122">
-        <v>42799</v>
+        <v>42984</v>
       </c>
       <c r="H122">
         <v>51523</v>
@@ -3576,7 +3576,7 @@
         <v>41394</v>
       </c>
       <c r="C123">
-        <v>25217</v>
+        <v>28872</v>
       </c>
       <c r="D123">
         <v>29582</v>
@@ -3588,7 +3588,7 @@
         <v>44513</v>
       </c>
       <c r="G123">
-        <v>42799</v>
+        <v>42984</v>
       </c>
       <c r="H123">
         <v>51523</v>
@@ -3602,7 +3602,7 @@
         <v>41394</v>
       </c>
       <c r="C124">
-        <v>25217</v>
+        <v>28872</v>
       </c>
       <c r="D124">
         <v>29582</v>
@@ -3614,7 +3614,7 @@
         <v>44513</v>
       </c>
       <c r="G124">
-        <v>42799</v>
+        <v>42984</v>
       </c>
       <c r="H124">
         <v>51523</v>
@@ -3628,19 +3628,19 @@
         <v>40921</v>
       </c>
       <c r="C125">
-        <v>24994</v>
+        <v>28155</v>
       </c>
       <c r="D125">
         <v>27104</v>
       </c>
       <c r="E125">
-        <v>48716</v>
+        <v>48718</v>
       </c>
       <c r="F125">
         <v>43630</v>
       </c>
       <c r="G125">
-        <v>40935</v>
+        <v>41143</v>
       </c>
       <c r="H125">
         <v>50835</v>
@@ -3654,19 +3654,19 @@
         <v>40921</v>
       </c>
       <c r="C126">
-        <v>26003</v>
+        <v>28992</v>
       </c>
       <c r="D126">
         <v>27104</v>
       </c>
       <c r="E126">
-        <v>49336</v>
+        <v>49338</v>
       </c>
       <c r="F126">
         <v>43630</v>
       </c>
       <c r="G126">
-        <v>41679</v>
+        <v>41885</v>
       </c>
       <c r="H126">
         <v>51411</v>
@@ -3680,22 +3680,22 @@
         <v>42740</v>
       </c>
       <c r="C127">
-        <v>26939</v>
+        <v>31698</v>
       </c>
       <c r="D127">
         <v>28328</v>
       </c>
       <c r="E127">
-        <v>51744</v>
+        <v>51766</v>
       </c>
       <c r="F127">
         <v>45508</v>
       </c>
       <c r="G127">
-        <v>44137</v>
+        <v>44568</v>
       </c>
       <c r="H127">
-        <v>53819</v>
+        <v>53820</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -3706,7 +3706,7 @@
         <v>43040</v>
       </c>
       <c r="C128">
-        <v>27521</v>
+        <v>30482</v>
       </c>
       <c r="D128">
         <v>32179</v>
@@ -3718,7 +3718,7 @@
         <v>46252</v>
       </c>
       <c r="G128">
-        <v>45525</v>
+        <v>45731</v>
       </c>
       <c r="H128">
         <v>53208</v>
@@ -3732,7 +3732,7 @@
         <v>43040</v>
       </c>
       <c r="C129">
-        <v>27521</v>
+        <v>30482</v>
       </c>
       <c r="D129">
         <v>32179</v>
@@ -3744,7 +3744,7 @@
         <v>46252</v>
       </c>
       <c r="G129">
-        <v>45525</v>
+        <v>45731</v>
       </c>
       <c r="H129">
         <v>53208</v>
@@ -3758,19 +3758,19 @@
         <v>44674</v>
       </c>
       <c r="C130">
-        <v>25652</v>
+        <v>31382</v>
       </c>
       <c r="D130">
         <v>36234</v>
       </c>
       <c r="E130">
-        <v>51104</v>
+        <v>51106</v>
       </c>
       <c r="F130">
         <v>48260</v>
       </c>
       <c r="G130">
-        <v>47544</v>
+        <v>47777</v>
       </c>
       <c r="H130">
         <v>53996</v>
@@ -3784,19 +3784,19 @@
         <v>44674</v>
       </c>
       <c r="C131">
-        <v>25652</v>
+        <v>31382</v>
       </c>
       <c r="D131">
         <v>36234</v>
       </c>
       <c r="E131">
-        <v>51104</v>
+        <v>51106</v>
       </c>
       <c r="F131">
         <v>48260</v>
       </c>
       <c r="G131">
-        <v>47544</v>
+        <v>47777</v>
       </c>
       <c r="H131">
         <v>53996</v>
@@ -3810,19 +3810,19 @@
         <v>44674</v>
       </c>
       <c r="C132">
-        <v>25652</v>
+        <v>31382</v>
       </c>
       <c r="D132">
         <v>36234</v>
       </c>
       <c r="E132">
-        <v>51104</v>
+        <v>51106</v>
       </c>
       <c r="F132">
         <v>48260</v>
       </c>
       <c r="G132">
-        <v>47544</v>
+        <v>47777</v>
       </c>
       <c r="H132">
         <v>53996</v>
@@ -3836,19 +3836,19 @@
         <v>44674</v>
       </c>
       <c r="C133">
-        <v>25652</v>
+        <v>31382</v>
       </c>
       <c r="D133">
         <v>36234</v>
       </c>
       <c r="E133">
-        <v>51104</v>
+        <v>51106</v>
       </c>
       <c r="F133">
         <v>48260</v>
       </c>
       <c r="G133">
-        <v>47544</v>
+        <v>47777</v>
       </c>
       <c r="H133">
         <v>53996</v>
@@ -3862,19 +3862,19 @@
         <v>44748</v>
       </c>
       <c r="C134">
-        <v>26633</v>
+        <v>31514</v>
       </c>
       <c r="D134">
         <v>38768</v>
       </c>
       <c r="E134">
-        <v>51848</v>
+        <v>51855</v>
       </c>
       <c r="F134">
         <v>50019</v>
       </c>
       <c r="G134">
-        <v>50185</v>
+        <v>50376</v>
       </c>
       <c r="H134">
         <v>56130</v>
@@ -3888,19 +3888,19 @@
         <v>43989</v>
       </c>
       <c r="C135">
-        <v>24945</v>
+        <v>30640</v>
       </c>
       <c r="D135">
         <v>35667</v>
       </c>
       <c r="E135">
-        <v>50207</v>
+        <v>50209</v>
       </c>
       <c r="F135">
         <v>47496</v>
       </c>
       <c r="G135">
-        <v>46632</v>
+        <v>46840</v>
       </c>
       <c r="H135">
         <v>53055</v>
@@ -3914,22 +3914,22 @@
         <v>43804</v>
       </c>
       <c r="C136">
-        <v>24855</v>
+        <v>30548</v>
       </c>
       <c r="D136">
         <v>33646</v>
       </c>
       <c r="E136">
-        <v>49859</v>
+        <v>49861</v>
       </c>
       <c r="F136">
         <v>46557</v>
       </c>
       <c r="G136">
-        <v>45026</v>
+        <v>45366</v>
       </c>
       <c r="H136">
-        <v>52084</v>
+        <v>52086</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -3940,22 +3940,22 @@
         <v>43804</v>
       </c>
       <c r="C137">
-        <v>24855</v>
+        <v>30548</v>
       </c>
       <c r="D137">
         <v>33646</v>
       </c>
       <c r="E137">
-        <v>49859</v>
+        <v>49861</v>
       </c>
       <c r="F137">
         <v>46557</v>
       </c>
       <c r="G137">
-        <v>45026</v>
+        <v>45366</v>
       </c>
       <c r="H137">
-        <v>52084</v>
+        <v>52086</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -3966,22 +3966,22 @@
         <v>43804</v>
       </c>
       <c r="C138">
-        <v>24855</v>
+        <v>30548</v>
       </c>
       <c r="D138">
         <v>33646</v>
       </c>
       <c r="E138">
-        <v>49859</v>
+        <v>49861</v>
       </c>
       <c r="F138">
         <v>46557</v>
       </c>
       <c r="G138">
-        <v>45026</v>
+        <v>45366</v>
       </c>
       <c r="H138">
-        <v>52084</v>
+        <v>52086</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -3992,7 +3992,7 @@
         <v>43342</v>
       </c>
       <c r="C139">
-        <v>24678</v>
+        <v>29928</v>
       </c>
       <c r="D139">
         <v>34706</v>
@@ -4004,7 +4004,7 @@
         <v>46433</v>
       </c>
       <c r="G139">
-        <v>45524</v>
+        <v>45697</v>
       </c>
       <c r="H139">
         <v>51934</v>
@@ -4018,22 +4018,22 @@
         <v>40919</v>
       </c>
       <c r="C140">
-        <v>24878</v>
+        <v>28136</v>
       </c>
       <c r="D140">
         <v>25783</v>
       </c>
       <c r="E140">
-        <v>47544</v>
+        <v>47547</v>
       </c>
       <c r="F140">
         <v>42415</v>
       </c>
       <c r="G140">
-        <v>39332</v>
+        <v>39736</v>
       </c>
       <c r="H140">
-        <v>48696</v>
+        <v>48699</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -4044,7 +4044,7 @@
         <v>43342</v>
       </c>
       <c r="C141">
-        <v>24678</v>
+        <v>29928</v>
       </c>
       <c r="D141">
         <v>34706</v>
@@ -4056,7 +4056,7 @@
         <v>46433</v>
       </c>
       <c r="G141">
-        <v>45524</v>
+        <v>45697</v>
       </c>
       <c r="H141">
         <v>51934</v>
@@ -4070,7 +4070,7 @@
         <v>43342</v>
       </c>
       <c r="C142">
-        <v>24678</v>
+        <v>29928</v>
       </c>
       <c r="D142">
         <v>34706</v>
@@ -4082,7 +4082,7 @@
         <v>46433</v>
       </c>
       <c r="G142">
-        <v>45524</v>
+        <v>45697</v>
       </c>
       <c r="H142">
         <v>51934</v>
@@ -4096,7 +4096,7 @@
         <v>43040</v>
       </c>
       <c r="C143">
-        <v>25669</v>
+        <v>29014</v>
       </c>
       <c r="D143">
         <v>32179</v>
@@ -4108,7 +4108,7 @@
         <v>46252</v>
       </c>
       <c r="G143">
-        <v>44250</v>
+        <v>44464</v>
       </c>
       <c r="H143">
         <v>52198</v>
@@ -4122,7 +4122,7 @@
         <v>43040</v>
       </c>
       <c r="C144">
-        <v>25669</v>
+        <v>29014</v>
       </c>
       <c r="D144">
         <v>32179</v>
@@ -4134,7 +4134,7 @@
         <v>46252</v>
       </c>
       <c r="G144">
-        <v>44250</v>
+        <v>44464</v>
       </c>
       <c r="H144">
         <v>52198</v>
@@ -4148,7 +4148,7 @@
         <v>43040</v>
       </c>
       <c r="C145">
-        <v>25669</v>
+        <v>29014</v>
       </c>
       <c r="D145">
         <v>32179</v>
@@ -4160,7 +4160,7 @@
         <v>46252</v>
       </c>
       <c r="G145">
-        <v>44250</v>
+        <v>44464</v>
       </c>
       <c r="H145">
         <v>52198</v>
@@ -4174,7 +4174,7 @@
         <v>43040</v>
       </c>
       <c r="C146">
-        <v>27521</v>
+        <v>30482</v>
       </c>
       <c r="D146">
         <v>32179</v>
@@ -4186,7 +4186,7 @@
         <v>46252</v>
       </c>
       <c r="G146">
-        <v>45525</v>
+        <v>45731</v>
       </c>
       <c r="H146">
         <v>53208</v>
@@ -4200,7 +4200,7 @@
         <v>41953</v>
       </c>
       <c r="C147">
-        <v>23827</v>
+        <v>28296</v>
       </c>
       <c r="D147">
         <v>28842</v>
@@ -4212,7 +4212,7 @@
         <v>44405</v>
       </c>
       <c r="G147">
-        <v>41138</v>
+        <v>41460</v>
       </c>
       <c r="H147">
         <v>49843</v>
@@ -4226,7 +4226,7 @@
         <v>41953</v>
       </c>
       <c r="C148">
-        <v>23047</v>
+        <v>27658</v>
       </c>
       <c r="D148">
         <v>28842</v>
@@ -4238,7 +4238,7 @@
         <v>44405</v>
       </c>
       <c r="G148">
-        <v>40577</v>
+        <v>40906</v>
       </c>
       <c r="H148">
         <v>49404</v>
@@ -4252,7 +4252,7 @@
         <v>40393</v>
       </c>
       <c r="C149">
-        <v>20445</v>
+        <v>24546</v>
       </c>
       <c r="D149">
         <v>32100</v>
@@ -4264,7 +4264,7 @@
         <v>44003</v>
       </c>
       <c r="G149">
-        <v>40925</v>
+        <v>40997</v>
       </c>
       <c r="H149">
         <v>47901</v>
@@ -4278,7 +4278,7 @@
         <v>40393</v>
       </c>
       <c r="C150">
-        <v>20445</v>
+        <v>24546</v>
       </c>
       <c r="D150">
         <v>32100</v>
@@ -4290,7 +4290,7 @@
         <v>44003</v>
       </c>
       <c r="G150">
-        <v>40925</v>
+        <v>40997</v>
       </c>
       <c r="H150">
         <v>47901</v>
@@ -4304,7 +4304,7 @@
         <v>40393</v>
       </c>
       <c r="C151">
-        <v>20445</v>
+        <v>24546</v>
       </c>
       <c r="D151">
         <v>32100</v>
@@ -4316,7 +4316,7 @@
         <v>44003</v>
       </c>
       <c r="G151">
-        <v>40925</v>
+        <v>40997</v>
       </c>
       <c r="H151">
         <v>47901</v>
@@ -4330,7 +4330,7 @@
         <v>40393</v>
       </c>
       <c r="C152">
-        <v>20445</v>
+        <v>24546</v>
       </c>
       <c r="D152">
         <v>32100</v>
@@ -4342,7 +4342,7 @@
         <v>44003</v>
       </c>
       <c r="G152">
-        <v>40925</v>
+        <v>40997</v>
       </c>
       <c r="H152">
         <v>47901</v>
@@ -4356,7 +4356,7 @@
         <v>37174</v>
       </c>
       <c r="C153">
-        <v>22582</v>
+        <v>24919</v>
       </c>
       <c r="D153">
         <v>25089</v>
@@ -4368,7 +4368,7 @@
         <v>39491</v>
       </c>
       <c r="G153">
-        <v>36874</v>
+        <v>37010</v>
       </c>
       <c r="H153">
         <v>45061</v>
@@ -4382,7 +4382,7 @@
         <v>37174</v>
       </c>
       <c r="C154">
-        <v>22582</v>
+        <v>24919</v>
       </c>
       <c r="D154">
         <v>25089</v>
@@ -4394,7 +4394,7 @@
         <v>39491</v>
       </c>
       <c r="G154">
-        <v>36874</v>
+        <v>37010</v>
       </c>
       <c r="H154">
         <v>45061</v>
@@ -4408,7 +4408,7 @@
         <v>36560</v>
       </c>
       <c r="C155">
-        <v>19894</v>
+        <v>22479</v>
       </c>
       <c r="D155">
         <v>21756</v>
@@ -4420,7 +4420,7 @@
         <v>38319</v>
       </c>
       <c r="G155">
-        <v>32253</v>
+        <v>32491</v>
       </c>
       <c r="H155">
         <v>42515</v>
@@ -4434,7 +4434,7 @@
         <v>36560</v>
       </c>
       <c r="C156">
-        <v>19894</v>
+        <v>22479</v>
       </c>
       <c r="D156">
         <v>21756</v>
@@ -4446,7 +4446,7 @@
         <v>38319</v>
       </c>
       <c r="G156">
-        <v>32253</v>
+        <v>32491</v>
       </c>
       <c r="H156">
         <v>42515</v>
@@ -4460,7 +4460,7 @@
         <v>36560</v>
       </c>
       <c r="C157">
-        <v>20638</v>
+        <v>23080</v>
       </c>
       <c r="D157">
         <v>21756</v>
@@ -4472,7 +4472,7 @@
         <v>38319</v>
       </c>
       <c r="G157">
-        <v>32796</v>
+        <v>33029</v>
       </c>
       <c r="H157">
         <v>42914</v>
@@ -4486,7 +4486,7 @@
         <v>37593</v>
       </c>
       <c r="C158">
-        <v>20474</v>
+        <v>24055</v>
       </c>
       <c r="D158">
         <v>29699</v>
@@ -4498,7 +4498,7 @@
         <v>41183</v>
       </c>
       <c r="G158">
-        <v>38799</v>
+        <v>38866</v>
       </c>
       <c r="H158">
         <v>45613</v>
@@ -4512,7 +4512,7 @@
         <v>37593</v>
       </c>
       <c r="C159">
-        <v>19709</v>
+        <v>23404</v>
       </c>
       <c r="D159">
         <v>29699</v>
@@ -4524,7 +4524,7 @@
         <v>41183</v>
       </c>
       <c r="G159">
-        <v>38284</v>
+        <v>38352</v>
       </c>
       <c r="H159">
         <v>45192</v>
@@ -4538,7 +4538,7 @@
         <v>35522</v>
       </c>
       <c r="C160">
-        <v>18631</v>
+        <v>21376</v>
       </c>
       <c r="D160">
         <v>23834</v>
@@ -4550,7 +4550,7 @@
         <v>38085</v>
       </c>
       <c r="G160">
-        <v>33512</v>
+        <v>33641</v>
       </c>
       <c r="H160">
         <v>42201</v>
@@ -4564,22 +4564,22 @@
         <v>34546</v>
       </c>
       <c r="C161">
-        <v>20202</v>
+        <v>23033</v>
       </c>
       <c r="D161">
         <v>24308</v>
       </c>
       <c r="E161">
-        <v>40247</v>
+        <v>40257</v>
       </c>
       <c r="F161">
         <v>37221</v>
       </c>
       <c r="G161">
-        <v>34830</v>
+        <v>34982</v>
       </c>
       <c r="H161">
-        <v>42478</v>
+        <v>42484</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -4590,7 +4590,7 @@
         <v>35522</v>
       </c>
       <c r="C162">
-        <v>20089</v>
+        <v>22633</v>
       </c>
       <c r="D162">
         <v>23834</v>
@@ -4602,7 +4602,7 @@
         <v>38085</v>
       </c>
       <c r="G162">
-        <v>34615</v>
+        <v>34727</v>
       </c>
       <c r="H162">
         <v>43046</v>
@@ -4616,7 +4616,7 @@
         <v>40710</v>
       </c>
       <c r="C163">
-        <v>21222</v>
+        <v>25096</v>
       </c>
       <c r="D163">
         <v>30750</v>
@@ -4628,7 +4628,7 @@
         <v>44169</v>
       </c>
       <c r="G163">
-        <v>40514</v>
+        <v>40660</v>
       </c>
       <c r="H163">
         <v>48548</v>
@@ -4642,7 +4642,7 @@
         <v>40710</v>
       </c>
       <c r="C164">
-        <v>22039</v>
+        <v>25774</v>
       </c>
       <c r="D164">
         <v>30750</v>
@@ -4654,7 +4654,7 @@
         <v>44169</v>
       </c>
       <c r="G164">
-        <v>41062</v>
+        <v>41208</v>
       </c>
       <c r="H164">
         <v>48975</v>
@@ -4668,7 +4668,7 @@
         <v>37476</v>
       </c>
       <c r="C165">
-        <v>20281</v>
+        <v>22908</v>
       </c>
       <c r="D165">
         <v>26191</v>
@@ -4680,7 +4680,7 @@
         <v>40580</v>
       </c>
       <c r="G165">
-        <v>36035</v>
+        <v>36165</v>
       </c>
       <c r="H165">
         <v>44961</v>
@@ -4694,7 +4694,7 @@
         <v>37476</v>
       </c>
       <c r="C166">
-        <v>20281</v>
+        <v>22908</v>
       </c>
       <c r="D166">
         <v>26191</v>
@@ -4706,7 +4706,7 @@
         <v>40580</v>
       </c>
       <c r="G166">
-        <v>36035</v>
+        <v>36165</v>
       </c>
       <c r="H166">
         <v>44961</v>
@@ -4720,7 +4720,7 @@
         <v>35879</v>
       </c>
       <c r="C167">
-        <v>21357</v>
+        <v>24399</v>
       </c>
       <c r="D167">
         <v>25104</v>
@@ -4732,7 +4732,7 @@
         <v>38981</v>
       </c>
       <c r="G167">
-        <v>36641</v>
+        <v>36819</v>
       </c>
       <c r="H167">
         <v>44553</v>
@@ -4746,7 +4746,7 @@
         <v>35879</v>
       </c>
       <c r="C168">
-        <v>22152</v>
+        <v>25065</v>
       </c>
       <c r="D168">
         <v>25104</v>
@@ -4758,7 +4758,7 @@
         <v>38981</v>
       </c>
       <c r="G168">
-        <v>37236</v>
+        <v>37406</v>
       </c>
       <c r="H168">
         <v>45039</v>
@@ -4772,19 +4772,19 @@
         <v>44647</v>
       </c>
       <c r="C169">
-        <v>25672</v>
+        <v>31296</v>
       </c>
       <c r="D169">
         <v>35162</v>
       </c>
       <c r="E169">
-        <v>51484</v>
+        <v>51485</v>
       </c>
       <c r="F169">
         <v>47808</v>
       </c>
       <c r="G169">
-        <v>47192</v>
+        <v>47385</v>
       </c>
       <c r="H169">
         <v>54013</v>
@@ -4798,7 +4798,7 @@
         <v>44303</v>
       </c>
       <c r="C170">
-        <v>23862</v>
+        <v>29430</v>
       </c>
       <c r="D170">
         <v>34072</v>
@@ -4810,7 +4810,7 @@
         <v>47164</v>
       </c>
       <c r="G170">
-        <v>45154</v>
+        <v>45291</v>
       </c>
       <c r="H170">
         <v>52419</v>
@@ -4824,19 +4824,19 @@
         <v>44647</v>
       </c>
       <c r="C171">
-        <v>25672</v>
+        <v>31296</v>
       </c>
       <c r="D171">
         <v>35162</v>
       </c>
       <c r="E171">
-        <v>51484</v>
+        <v>51485</v>
       </c>
       <c r="F171">
         <v>47808</v>
       </c>
       <c r="G171">
-        <v>47192</v>
+        <v>47385</v>
       </c>
       <c r="H171">
         <v>54013</v>
@@ -4850,7 +4850,7 @@
         <v>44303</v>
       </c>
       <c r="C172">
-        <v>23862</v>
+        <v>29430</v>
       </c>
       <c r="D172">
         <v>34072</v>
@@ -4862,7 +4862,7 @@
         <v>47164</v>
       </c>
       <c r="G172">
-        <v>45154</v>
+        <v>45291</v>
       </c>
       <c r="H172">
         <v>52419</v>
@@ -4876,7 +4876,7 @@
         <v>44303</v>
       </c>
       <c r="C173">
-        <v>23862</v>
+        <v>29430</v>
       </c>
       <c r="D173">
         <v>34072</v>
@@ -4888,7 +4888,7 @@
         <v>47164</v>
       </c>
       <c r="G173">
-        <v>45154</v>
+        <v>45291</v>
       </c>
       <c r="H173">
         <v>52419</v>
@@ -4902,19 +4902,19 @@
         <v>44473</v>
       </c>
       <c r="C174">
-        <v>24496</v>
+        <v>28792</v>
       </c>
       <c r="D174">
         <v>36769</v>
       </c>
       <c r="E174">
-        <v>49953</v>
+        <v>49955</v>
       </c>
       <c r="F174">
         <v>48312</v>
       </c>
       <c r="G174">
-        <v>46769</v>
+        <v>46896</v>
       </c>
       <c r="H174">
         <v>53157</v>
@@ -4928,22 +4928,22 @@
         <v>43464</v>
       </c>
       <c r="C175">
-        <v>26448</v>
+        <v>30723</v>
       </c>
       <c r="D175">
         <v>29789</v>
       </c>
       <c r="E175">
-        <v>50560</v>
+        <v>50562</v>
       </c>
       <c r="F175">
         <v>45664</v>
       </c>
       <c r="G175">
-        <v>43492</v>
+        <v>43957</v>
       </c>
       <c r="H175">
-        <v>52262</v>
+        <v>52264</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -4954,22 +4954,22 @@
         <v>43464</v>
       </c>
       <c r="C176">
-        <v>25588</v>
+        <v>30031</v>
       </c>
       <c r="D176">
         <v>29789</v>
       </c>
       <c r="E176">
-        <v>50014</v>
+        <v>50017</v>
       </c>
       <c r="F176">
         <v>45664</v>
       </c>
       <c r="G176">
-        <v>42858</v>
+        <v>43337</v>
       </c>
       <c r="H176">
-        <v>51752</v>
+        <v>51754</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -4980,22 +4980,22 @@
         <v>43464</v>
       </c>
       <c r="C177">
-        <v>25588</v>
+        <v>30031</v>
       </c>
       <c r="D177">
         <v>29789</v>
       </c>
       <c r="E177">
-        <v>50014</v>
+        <v>50017</v>
       </c>
       <c r="F177">
         <v>45664</v>
       </c>
       <c r="G177">
-        <v>42858</v>
+        <v>43337</v>
       </c>
       <c r="H177">
-        <v>51752</v>
+        <v>51754</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -5006,19 +5006,19 @@
         <v>44066</v>
       </c>
       <c r="C178">
-        <v>24820</v>
+        <v>29273</v>
       </c>
       <c r="D178">
         <v>31550</v>
       </c>
       <c r="E178">
-        <v>49974</v>
+        <v>49975</v>
       </c>
       <c r="F178">
         <v>46345</v>
       </c>
       <c r="G178">
-        <v>43436</v>
+        <v>43742</v>
       </c>
       <c r="H178">
         <v>51815</v>
@@ -5032,7 +5032,7 @@
         <v>43373</v>
       </c>
       <c r="C179">
-        <v>25330</v>
+        <v>29443</v>
       </c>
       <c r="D179">
         <v>31258</v>
@@ -5044,7 +5044,7 @@
         <v>45481</v>
       </c>
       <c r="G179">
-        <v>43423</v>
+        <v>43718</v>
       </c>
       <c r="H179">
         <v>51218</v>
@@ -5058,19 +5058,19 @@
         <v>43373</v>
       </c>
       <c r="C180">
-        <v>27036</v>
+        <v>30786</v>
       </c>
       <c r="D180">
         <v>31258</v>
       </c>
       <c r="E180">
-        <v>50572</v>
+        <v>50573</v>
       </c>
       <c r="F180">
         <v>45481</v>
       </c>
       <c r="G180">
-        <v>44630</v>
+        <v>44903</v>
       </c>
       <c r="H180">
         <v>52208</v>
@@ -5084,19 +5084,19 @@
         <v>43373</v>
       </c>
       <c r="C181">
-        <v>27036</v>
+        <v>30786</v>
       </c>
       <c r="D181">
         <v>31258</v>
       </c>
       <c r="E181">
-        <v>50572</v>
+        <v>50573</v>
       </c>
       <c r="F181">
         <v>45481</v>
       </c>
       <c r="G181">
-        <v>44630</v>
+        <v>44903</v>
       </c>
       <c r="H181">
         <v>52208</v>
@@ -5110,22 +5110,22 @@
         <v>36941</v>
       </c>
       <c r="C182">
-        <v>22041</v>
+        <v>23938</v>
       </c>
       <c r="D182">
         <v>22807</v>
       </c>
       <c r="E182">
-        <v>43173</v>
+        <v>43174</v>
       </c>
       <c r="F182">
         <v>38802</v>
       </c>
       <c r="G182">
-        <v>35256</v>
+        <v>35464</v>
       </c>
       <c r="H182">
-        <v>44705</v>
+        <v>44707</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -5136,7 +5136,7 @@
         <v>37338</v>
       </c>
       <c r="C183">
-        <v>19986</v>
+        <v>21538</v>
       </c>
       <c r="D183">
         <v>17726</v>
@@ -5148,7 +5148,7 @@
         <v>38589</v>
       </c>
       <c r="G183">
-        <v>30445</v>
+        <v>30686</v>
       </c>
       <c r="H183">
         <v>43319</v>
@@ -5162,7 +5162,7 @@
         <v>40317</v>
       </c>
       <c r="C184">
-        <v>22892</v>
+        <v>25948</v>
       </c>
       <c r="D184">
         <v>25483</v>
@@ -5174,7 +5174,7 @@
         <v>42442</v>
       </c>
       <c r="G184">
-        <v>38236</v>
+        <v>38414</v>
       </c>
       <c r="H184">
         <v>48316</v>
@@ -5188,7 +5188,7 @@
         <v>40317</v>
       </c>
       <c r="C185">
-        <v>22892</v>
+        <v>25948</v>
       </c>
       <c r="D185">
         <v>25483</v>
@@ -5200,7 +5200,7 @@
         <v>42442</v>
       </c>
       <c r="G185">
-        <v>38236</v>
+        <v>38414</v>
       </c>
       <c r="H185">
         <v>48316</v>
@@ -5214,7 +5214,7 @@
         <v>37055</v>
       </c>
       <c r="C186">
-        <v>20013</v>
+        <v>22171</v>
       </c>
       <c r="D186">
         <v>25757</v>
@@ -5226,7 +5226,7 @@
         <v>40174</v>
       </c>
       <c r="G186">
-        <v>36280</v>
+        <v>36352</v>
       </c>
       <c r="H186">
         <v>45007</v>
@@ -5240,7 +5240,7 @@
         <v>37055</v>
       </c>
       <c r="C187">
-        <v>19190</v>
+        <v>21450</v>
       </c>
       <c r="D187">
         <v>25757</v>
@@ -5252,7 +5252,7 @@
         <v>40174</v>
       </c>
       <c r="G187">
-        <v>35680</v>
+        <v>35760</v>
       </c>
       <c r="H187">
         <v>44551</v>
@@ -5266,19 +5266,19 @@
         <v>36011</v>
       </c>
       <c r="C188">
-        <v>21758</v>
+        <v>23740</v>
       </c>
       <c r="D188">
         <v>21468</v>
       </c>
       <c r="E188">
-        <v>42278</v>
+        <v>42279</v>
       </c>
       <c r="F188">
         <v>38350</v>
       </c>
       <c r="G188">
-        <v>34321</v>
+        <v>34597</v>
       </c>
       <c r="H188">
         <v>44162</v>
@@ -5292,19 +5292,19 @@
         <v>36011</v>
       </c>
       <c r="C189">
-        <v>21758</v>
+        <v>23740</v>
       </c>
       <c r="D189">
         <v>21468</v>
       </c>
       <c r="E189">
-        <v>42278</v>
+        <v>42279</v>
       </c>
       <c r="F189">
         <v>38350</v>
       </c>
       <c r="G189">
-        <v>34321</v>
+        <v>34597</v>
       </c>
       <c r="H189">
         <v>44162</v>
@@ -5318,19 +5318,19 @@
         <v>36011</v>
       </c>
       <c r="C190">
-        <v>21758</v>
+        <v>23740</v>
       </c>
       <c r="D190">
         <v>21468</v>
       </c>
       <c r="E190">
-        <v>42278</v>
+        <v>42279</v>
       </c>
       <c r="F190">
         <v>38350</v>
       </c>
       <c r="G190">
-        <v>34321</v>
+        <v>34597</v>
       </c>
       <c r="H190">
         <v>44162</v>
@@ -5344,7 +5344,7 @@
         <v>39796</v>
       </c>
       <c r="C191">
-        <v>23414</v>
+        <v>26383</v>
       </c>
       <c r="D191">
         <v>25336</v>
@@ -5356,7 +5356,7 @@
         <v>42139</v>
       </c>
       <c r="G191">
-        <v>38366</v>
+        <v>38665</v>
       </c>
       <c r="H191">
         <v>48299</v>
@@ -5370,7 +5370,7 @@
         <v>37055</v>
       </c>
       <c r="C192">
-        <v>19190</v>
+        <v>21450</v>
       </c>
       <c r="D192">
         <v>25757</v>
@@ -5382,7 +5382,7 @@
         <v>40174</v>
       </c>
       <c r="G192">
-        <v>35680</v>
+        <v>35760</v>
       </c>
       <c r="H192">
         <v>44551</v>
@@ -5396,7 +5396,7 @@
         <v>43795</v>
       </c>
       <c r="C193">
-        <v>25026</v>
+        <v>30037</v>
       </c>
       <c r="D193">
         <v>34829</v>
@@ -5408,7 +5408,7 @@
         <v>47200</v>
       </c>
       <c r="G193">
-        <v>46355</v>
+        <v>46506</v>
       </c>
       <c r="H193">
         <v>53168</v>
@@ -5422,7 +5422,7 @@
         <v>43795</v>
       </c>
       <c r="C194">
-        <v>25026</v>
+        <v>30037</v>
       </c>
       <c r="D194">
         <v>34829</v>
@@ -5434,7 +5434,7 @@
         <v>47200</v>
       </c>
       <c r="G194">
-        <v>46355</v>
+        <v>46506</v>
       </c>
       <c r="H194">
         <v>53168</v>
@@ -5448,19 +5448,19 @@
         <v>44647</v>
       </c>
       <c r="C195">
-        <v>25672</v>
+        <v>31296</v>
       </c>
       <c r="D195">
         <v>35162</v>
       </c>
       <c r="E195">
-        <v>51484</v>
+        <v>51485</v>
       </c>
       <c r="F195">
         <v>47808</v>
       </c>
       <c r="G195">
-        <v>47192</v>
+        <v>47385</v>
       </c>
       <c r="H195">
         <v>54013</v>
@@ -5474,7 +5474,7 @@
         <v>41998</v>
       </c>
       <c r="C196">
-        <v>22548</v>
+        <v>26894</v>
       </c>
       <c r="D196">
         <v>29420</v>
@@ -5486,7 +5486,7 @@
         <v>44432</v>
       </c>
       <c r="G196">
-        <v>40571</v>
+        <v>40703</v>
       </c>
       <c r="H196">
         <v>49493</v>
@@ -5500,7 +5500,7 @@
         <v>42011</v>
       </c>
       <c r="C197">
-        <v>23198</v>
+        <v>27494</v>
       </c>
       <c r="D197">
         <v>30567</v>
@@ -5512,7 +5512,7 @@
         <v>44404</v>
       </c>
       <c r="G197">
-        <v>41609</v>
+        <v>41786</v>
       </c>
       <c r="H197">
         <v>49791</v>
@@ -5526,7 +5526,7 @@
         <v>42011</v>
       </c>
       <c r="C198">
-        <v>23198</v>
+        <v>27494</v>
       </c>
       <c r="D198">
         <v>30567</v>
@@ -5538,7 +5538,7 @@
         <v>44404</v>
       </c>
       <c r="G198">
-        <v>41609</v>
+        <v>41786</v>
       </c>
       <c r="H198">
         <v>49791</v>
@@ -5552,7 +5552,7 @@
         <v>42011</v>
       </c>
       <c r="C199">
-        <v>24099</v>
+        <v>28245</v>
       </c>
       <c r="D199">
         <v>30567</v>
@@ -5564,7 +5564,7 @@
         <v>44404</v>
       </c>
       <c r="G199">
-        <v>42255</v>
+        <v>42430</v>
       </c>
       <c r="H199">
         <v>50289</v>
@@ -5578,7 +5578,7 @@
         <v>42011</v>
       </c>
       <c r="C200">
-        <v>24099</v>
+        <v>28245</v>
       </c>
       <c r="D200">
         <v>30567</v>
@@ -5590,7 +5590,7 @@
         <v>44404</v>
       </c>
       <c r="G200">
-        <v>42255</v>
+        <v>42430</v>
       </c>
       <c r="H200">
         <v>50289</v>
@@ -5604,7 +5604,7 @@
         <v>41292</v>
       </c>
       <c r="C201">
-        <v>24557</v>
+        <v>27651</v>
       </c>
       <c r="D201">
         <v>33095</v>
@@ -5616,7 +5616,7 @@
         <v>44893</v>
       </c>
       <c r="G201">
-        <v>44600</v>
+        <v>44659</v>
       </c>
       <c r="H201">
         <v>51379</v>
@@ -5630,7 +5630,7 @@
         <v>39223</v>
       </c>
       <c r="C202">
-        <v>25309</v>
+        <v>27328</v>
       </c>
       <c r="D202">
         <v>27787</v>
@@ -5642,7 +5642,7 @@
         <v>41941</v>
       </c>
       <c r="G202">
-        <v>40770</v>
+        <v>40937</v>
       </c>
       <c r="H202">
         <v>48907</v>
@@ -5656,7 +5656,7 @@
         <v>41998</v>
       </c>
       <c r="C203">
-        <v>23420</v>
+        <v>27624</v>
       </c>
       <c r="D203">
         <v>29420</v>
@@ -5668,7 +5668,7 @@
         <v>44432</v>
       </c>
       <c r="G203">
-        <v>41207</v>
+        <v>41335</v>
       </c>
       <c r="H203">
         <v>49980</v>
@@ -5682,7 +5682,7 @@
         <v>39788</v>
       </c>
       <c r="C204">
-        <v>22531</v>
+        <v>25863</v>
       </c>
       <c r="D204">
         <v>27645</v>
@@ -5694,7 +5694,7 @@
         <v>42275</v>
       </c>
       <c r="G204">
-        <v>39063</v>
+        <v>39223</v>
       </c>
       <c r="H204">
         <v>47863</v>
@@ -5708,7 +5708,7 @@
         <v>39788</v>
       </c>
       <c r="C205">
-        <v>23420</v>
+        <v>26608</v>
       </c>
       <c r="D205">
         <v>27645</v>
@@ -5720,7 +5720,7 @@
         <v>42275</v>
       </c>
       <c r="G205">
-        <v>39715</v>
+        <v>39872</v>
       </c>
       <c r="H205">
         <v>48372</v>
@@ -5734,19 +5734,19 @@
         <v>23929</v>
       </c>
       <c r="C206">
-        <v>18211</v>
+        <v>20833</v>
       </c>
       <c r="D206">
         <v>22386</v>
       </c>
       <c r="E206">
-        <v>30313</v>
+        <v>30322</v>
       </c>
       <c r="F206">
         <v>30103</v>
       </c>
       <c r="G206">
-        <v>32116</v>
+        <v>32157</v>
       </c>
       <c r="H206">
         <v>35637</v>
@@ -5760,22 +5760,22 @@
         <v>23233</v>
       </c>
       <c r="C207">
-        <v>17091</v>
+        <v>19836</v>
       </c>
       <c r="D207">
         <v>17758</v>
       </c>
       <c r="E207">
-        <v>28793</v>
+        <v>28795</v>
       </c>
       <c r="F207">
         <v>26542</v>
       </c>
       <c r="G207">
-        <v>27505</v>
+        <v>27590</v>
       </c>
       <c r="H207">
-        <v>31585</v>
+        <v>31586</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -5786,22 +5786,22 @@
         <v>23233</v>
       </c>
       <c r="C208">
-        <v>17091</v>
+        <v>19836</v>
       </c>
       <c r="D208">
         <v>17758</v>
       </c>
       <c r="E208">
-        <v>28793</v>
+        <v>28795</v>
       </c>
       <c r="F208">
         <v>26542</v>
       </c>
       <c r="G208">
-        <v>27505</v>
+        <v>27590</v>
       </c>
       <c r="H208">
-        <v>31585</v>
+        <v>31586</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -5812,19 +5812,19 @@
         <v>23929</v>
       </c>
       <c r="C209">
-        <v>18211</v>
+        <v>20833</v>
       </c>
       <c r="D209">
         <v>22386</v>
       </c>
       <c r="E209">
-        <v>30313</v>
+        <v>30322</v>
       </c>
       <c r="F209">
         <v>30103</v>
       </c>
       <c r="G209">
-        <v>32116</v>
+        <v>32157</v>
       </c>
       <c r="H209">
         <v>35637</v>
@@ -5838,22 +5838,22 @@
         <v>23233</v>
       </c>
       <c r="C210">
-        <v>17091</v>
+        <v>19836</v>
       </c>
       <c r="D210">
         <v>17758</v>
       </c>
       <c r="E210">
-        <v>28793</v>
+        <v>28795</v>
       </c>
       <c r="F210">
         <v>26542</v>
       </c>
       <c r="G210">
-        <v>27505</v>
+        <v>27590</v>
       </c>
       <c r="H210">
-        <v>31585</v>
+        <v>31586</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -5864,7 +5864,7 @@
         <v>23288</v>
       </c>
       <c r="C211">
-        <v>17791</v>
+        <v>19487</v>
       </c>
       <c r="D211">
         <v>17600</v>
@@ -5876,7 +5876,7 @@
         <v>26735</v>
       </c>
       <c r="G211">
-        <v>27902</v>
+        <v>27958</v>
       </c>
       <c r="H211">
         <v>32413</v>
@@ -5890,22 +5890,22 @@
         <v>25694</v>
       </c>
       <c r="C212">
-        <v>18845</v>
+        <v>20712</v>
       </c>
       <c r="D212">
         <v>19352</v>
       </c>
       <c r="E212">
-        <v>32117</v>
+        <v>32119</v>
       </c>
       <c r="F212">
         <v>29196</v>
       </c>
       <c r="G212">
-        <v>29950</v>
+        <v>29998</v>
       </c>
       <c r="H212">
-        <v>35027</v>
+        <v>35028</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -5916,22 +5916,22 @@
         <v>23233</v>
       </c>
       <c r="C213">
-        <v>17091</v>
+        <v>19836</v>
       </c>
       <c r="D213">
         <v>17758</v>
       </c>
       <c r="E213">
-        <v>28793</v>
+        <v>28795</v>
       </c>
       <c r="F213">
         <v>26542</v>
       </c>
       <c r="G213">
-        <v>27505</v>
+        <v>27590</v>
       </c>
       <c r="H213">
-        <v>31585</v>
+        <v>31586</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -5942,7 +5942,7 @@
         <v>22709</v>
       </c>
       <c r="C214">
-        <v>15609</v>
+        <v>17468</v>
       </c>
       <c r="D214">
         <v>15030</v>
@@ -5954,7 +5954,7 @@
         <v>24951</v>
       </c>
       <c r="G214">
-        <v>24282</v>
+        <v>24363</v>
       </c>
       <c r="H214">
         <v>29083</v>
@@ -5968,7 +5968,7 @@
         <v>22709</v>
       </c>
       <c r="C215">
-        <v>15609</v>
+        <v>17468</v>
       </c>
       <c r="D215">
         <v>15030</v>
@@ -5980,7 +5980,7 @@
         <v>24951</v>
       </c>
       <c r="G215">
-        <v>24282</v>
+        <v>24363</v>
       </c>
       <c r="H215">
         <v>29083</v>
@@ -5994,7 +5994,7 @@
         <v>22474</v>
       </c>
       <c r="C216">
-        <v>15591</v>
+        <v>17484</v>
       </c>
       <c r="D216">
         <v>15031</v>
@@ -6006,7 +6006,7 @@
         <v>24306</v>
       </c>
       <c r="G216">
-        <v>23990</v>
+        <v>24052</v>
       </c>
       <c r="H216">
         <v>28328</v>
@@ -6020,7 +6020,7 @@
         <v>22563</v>
       </c>
       <c r="C217">
-        <v>16101</v>
+        <v>18024</v>
       </c>
       <c r="D217">
         <v>16894</v>
@@ -6032,7 +6032,7 @@
         <v>24985</v>
       </c>
       <c r="G217">
-        <v>25582</v>
+        <v>25632</v>
       </c>
       <c r="H217">
         <v>29338</v>
@@ -6046,7 +6046,7 @@
         <v>22563</v>
       </c>
       <c r="C218">
-        <v>16633</v>
+        <v>18514</v>
       </c>
       <c r="D218">
         <v>16894</v>
@@ -6058,7 +6058,7 @@
         <v>24985</v>
       </c>
       <c r="G218">
-        <v>26022</v>
+        <v>26070</v>
       </c>
       <c r="H218">
         <v>29714</v>
@@ -6072,7 +6072,7 @@
         <v>25851</v>
       </c>
       <c r="C219">
-        <v>17611</v>
+        <v>19095</v>
       </c>
       <c r="D219">
         <v>18687</v>
@@ -6084,7 +6084,7 @@
         <v>29813</v>
       </c>
       <c r="G219">
-        <v>28865</v>
+        <v>28908</v>
       </c>
       <c r="H219">
         <v>35199</v>
@@ -6098,22 +6098,22 @@
         <v>24948</v>
       </c>
       <c r="C220">
-        <v>19267</v>
+        <v>21330</v>
       </c>
       <c r="D220">
         <v>18564</v>
       </c>
       <c r="E220">
-        <v>32267</v>
+        <v>32274</v>
       </c>
       <c r="F220">
         <v>28563</v>
       </c>
       <c r="G220">
-        <v>30079</v>
+        <v>30139</v>
       </c>
       <c r="H220">
-        <v>35220</v>
+        <v>35221</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -6124,7 +6124,7 @@
         <v>27045</v>
       </c>
       <c r="C221">
-        <v>18076</v>
+        <v>19508</v>
       </c>
       <c r="D221">
         <v>19709</v>
@@ -6136,7 +6136,7 @@
         <v>32239</v>
       </c>
       <c r="G221">
-        <v>30861</v>
+        <v>30929</v>
       </c>
       <c r="H221">
         <v>37882</v>
@@ -6150,7 +6150,7 @@
         <v>25851</v>
       </c>
       <c r="C222">
-        <v>17611</v>
+        <v>19095</v>
       </c>
       <c r="D222">
         <v>18687</v>
@@ -6162,7 +6162,7 @@
         <v>29813</v>
       </c>
       <c r="G222">
-        <v>28865</v>
+        <v>28908</v>
       </c>
       <c r="H222">
         <v>35199</v>
@@ -6176,7 +6176,7 @@
         <v>27045</v>
       </c>
       <c r="C223">
-        <v>18885</v>
+        <v>20252</v>
       </c>
       <c r="D223">
         <v>19709</v>
@@ -6188,7 +6188,7 @@
         <v>32239</v>
       </c>
       <c r="G223">
-        <v>31504</v>
+        <v>31563</v>
       </c>
       <c r="H223">
         <v>38414</v>
@@ -6202,7 +6202,7 @@
         <v>21656</v>
       </c>
       <c r="C224">
-        <v>15813</v>
+        <v>16785</v>
       </c>
       <c r="D224">
         <v>14213</v>
@@ -6214,7 +6214,7 @@
         <v>24969</v>
       </c>
       <c r="G224">
-        <v>24122</v>
+        <v>24185</v>
       </c>
       <c r="H224">
         <v>29241</v>
@@ -6228,7 +6228,7 @@
         <v>21656</v>
       </c>
       <c r="C225">
-        <v>14710</v>
+        <v>15823</v>
       </c>
       <c r="D225">
         <v>14213</v>
@@ -6240,7 +6240,7 @@
         <v>24969</v>
       </c>
       <c r="G225">
-        <v>23250</v>
+        <v>23330</v>
       </c>
       <c r="H225">
         <v>28555</v>
@@ -6254,7 +6254,7 @@
         <v>21656</v>
       </c>
       <c r="C226">
-        <v>15262</v>
+        <v>16304</v>
       </c>
       <c r="D226">
         <v>14213</v>
@@ -6266,7 +6266,7 @@
         <v>24969</v>
       </c>
       <c r="G226">
-        <v>23685</v>
+        <v>23757</v>
       </c>
       <c r="H226">
         <v>28894</v>
@@ -6280,7 +6280,7 @@
         <v>21846</v>
       </c>
       <c r="C227">
-        <v>15305</v>
+        <v>16363</v>
       </c>
       <c r="D227">
         <v>15499</v>
@@ -6292,7 +6292,7 @@
         <v>25629</v>
       </c>
       <c r="G227">
-        <v>24544</v>
+        <v>24595</v>
       </c>
       <c r="H227">
         <v>29342</v>
@@ -6306,7 +6306,7 @@
         <v>19998</v>
       </c>
       <c r="C228">
-        <v>14861</v>
+        <v>15544</v>
       </c>
       <c r="D228">
         <v>9150</v>
@@ -6318,7 +6318,7 @@
         <v>20878</v>
       </c>
       <c r="G228">
-        <v>19937</v>
+        <v>20116</v>
       </c>
       <c r="H228">
         <v>25742</v>
@@ -6332,22 +6332,22 @@
         <v>24948</v>
       </c>
       <c r="C229">
-        <v>19267</v>
+        <v>21330</v>
       </c>
       <c r="D229">
         <v>18564</v>
       </c>
       <c r="E229">
-        <v>32267</v>
+        <v>32274</v>
       </c>
       <c r="F229">
         <v>28563</v>
       </c>
       <c r="G229">
-        <v>30079</v>
+        <v>30139</v>
       </c>
       <c r="H229">
-        <v>35220</v>
+        <v>35221</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -6358,7 +6358,7 @@
         <v>27045</v>
       </c>
       <c r="C230">
-        <v>17286</v>
+        <v>18780</v>
       </c>
       <c r="D230">
         <v>19709</v>
@@ -6370,7 +6370,7 @@
         <v>32239</v>
       </c>
       <c r="G230">
-        <v>30237</v>
+        <v>30315</v>
       </c>
       <c r="H230">
         <v>37366</v>
@@ -6384,22 +6384,22 @@
         <v>25694</v>
       </c>
       <c r="C231">
-        <v>19539</v>
+        <v>21360</v>
       </c>
       <c r="D231">
         <v>19352</v>
       </c>
       <c r="E231">
-        <v>32655</v>
+        <v>32656</v>
       </c>
       <c r="F231">
         <v>29196</v>
       </c>
       <c r="G231">
-        <v>30536</v>
+        <v>30582</v>
       </c>
       <c r="H231">
-        <v>35520</v>
+        <v>35521</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -6410,7 +6410,7 @@
         <v>24801</v>
       </c>
       <c r="C232">
-        <v>17391</v>
+        <v>18649</v>
       </c>
       <c r="D232">
         <v>17519</v>
@@ -6422,7 +6422,7 @@
         <v>27152</v>
       </c>
       <c r="G232">
-        <v>26885</v>
+        <v>26905</v>
       </c>
       <c r="H232">
         <v>31937</v>
@@ -6436,7 +6436,7 @@
         <v>24801</v>
       </c>
       <c r="C233">
-        <v>18018</v>
+        <v>19227</v>
       </c>
       <c r="D233">
         <v>17519</v>
@@ -6448,7 +6448,7 @@
         <v>27152</v>
       </c>
       <c r="G233">
-        <v>27405</v>
+        <v>27423</v>
       </c>
       <c r="H233">
         <v>32364</v>
@@ -6462,7 +6462,7 @@
         <v>27752</v>
       </c>
       <c r="C234">
-        <v>18960</v>
+        <v>19861</v>
       </c>
       <c r="D234">
         <v>19166</v>
@@ -6474,7 +6474,7 @@
         <v>31799</v>
       </c>
       <c r="G234">
-        <v>30292</v>
+        <v>30307</v>
       </c>
       <c r="H234">
         <v>37264</v>
@@ -6488,7 +6488,7 @@
         <v>27752</v>
       </c>
       <c r="C235">
-        <v>18960</v>
+        <v>19861</v>
       </c>
       <c r="D235">
         <v>19166</v>
@@ -6500,7 +6500,7 @@
         <v>31799</v>
       </c>
       <c r="G235">
-        <v>30292</v>
+        <v>30307</v>
       </c>
       <c r="H235">
         <v>37264</v>
@@ -6514,7 +6514,7 @@
         <v>27752</v>
       </c>
       <c r="C236">
-        <v>18960</v>
+        <v>19861</v>
       </c>
       <c r="D236">
         <v>19166</v>
@@ -6526,7 +6526,7 @@
         <v>31799</v>
       </c>
       <c r="G236">
-        <v>30292</v>
+        <v>30307</v>
       </c>
       <c r="H236">
         <v>37264</v>
@@ -6540,7 +6540,7 @@
         <v>21846</v>
       </c>
       <c r="C237">
-        <v>15814</v>
+        <v>16799</v>
       </c>
       <c r="D237">
         <v>15499</v>
@@ -6552,7 +6552,7 @@
         <v>25629</v>
       </c>
       <c r="G237">
-        <v>24927</v>
+        <v>24974</v>
       </c>
       <c r="H237">
         <v>29655</v>
@@ -6566,7 +6566,7 @@
         <v>21846</v>
       </c>
       <c r="C238">
-        <v>15305</v>
+        <v>16363</v>
       </c>
       <c r="D238">
         <v>15499</v>
@@ -6578,7 +6578,7 @@
         <v>25629</v>
       </c>
       <c r="G238">
-        <v>24544</v>
+        <v>24595</v>
       </c>
       <c r="H238">
         <v>29342</v>
@@ -6592,7 +6592,7 @@
         <v>21846</v>
       </c>
       <c r="C239">
-        <v>16320</v>
+        <v>17233</v>
       </c>
       <c r="D239">
         <v>15499</v>
@@ -6604,7 +6604,7 @@
         <v>25629</v>
       </c>
       <c r="G239">
-        <v>25312</v>
+        <v>25354</v>
       </c>
       <c r="H239">
         <v>29971</v>
@@ -6618,7 +6618,7 @@
         <v>21676</v>
       </c>
       <c r="C240">
-        <v>15937</v>
+        <v>17225</v>
       </c>
       <c r="D240">
         <v>11597</v>
@@ -6630,7 +6630,7 @@
         <v>22772</v>
       </c>
       <c r="G240">
-        <v>22176</v>
+        <v>22271</v>
       </c>
       <c r="H240">
         <v>27222</v>
@@ -6644,7 +6644,7 @@
         <v>21416</v>
       </c>
       <c r="C241">
-        <v>15632</v>
+        <v>16837</v>
       </c>
       <c r="D241">
         <v>11476</v>
@@ -6656,7 +6656,7 @@
         <v>22819</v>
       </c>
       <c r="G241">
-        <v>22065</v>
+        <v>22180</v>
       </c>
       <c r="H241">
         <v>27073</v>
@@ -6670,7 +6670,7 @@
         <v>27045</v>
       </c>
       <c r="C242">
-        <v>18076</v>
+        <v>19508</v>
       </c>
       <c r="D242">
         <v>19709</v>
@@ -6682,7 +6682,7 @@
         <v>32239</v>
       </c>
       <c r="G242">
-        <v>30861</v>
+        <v>30929</v>
       </c>
       <c r="H242">
         <v>37882</v>
@@ -6696,7 +6696,7 @@
         <v>29006</v>
       </c>
       <c r="C243">
-        <v>18291</v>
+        <v>19522</v>
       </c>
       <c r="D243">
         <v>19442</v>
@@ -6708,7 +6708,7 @@
         <v>34181</v>
       </c>
       <c r="G243">
-        <v>31149</v>
+        <v>31230</v>
       </c>
       <c r="H243">
         <v>39916</v>
@@ -6722,7 +6722,7 @@
         <v>27045</v>
       </c>
       <c r="C244">
-        <v>18076</v>
+        <v>19508</v>
       </c>
       <c r="D244">
         <v>19709</v>
@@ -6734,7 +6734,7 @@
         <v>32239</v>
       </c>
       <c r="G244">
-        <v>30861</v>
+        <v>30929</v>
       </c>
       <c r="H244">
         <v>37882</v>
@@ -6748,7 +6748,7 @@
         <v>29006</v>
       </c>
       <c r="C245">
-        <v>19173</v>
+        <v>20344</v>
       </c>
       <c r="D245">
         <v>19442</v>
@@ -6760,7 +6760,7 @@
         <v>34181</v>
       </c>
       <c r="G245">
-        <v>31856</v>
+        <v>31928</v>
       </c>
       <c r="H245">
         <v>40496</v>
@@ -6774,7 +6774,7 @@
         <v>28062</v>
       </c>
       <c r="C246">
-        <v>20512</v>
+        <v>21653</v>
       </c>
       <c r="D246">
         <v>21813</v>
@@ -6786,7 +6786,7 @@
         <v>34977</v>
       </c>
       <c r="G246">
-        <v>34675</v>
+        <v>34748</v>
       </c>
       <c r="H246">
         <v>41858</v>
@@ -6800,7 +6800,7 @@
         <v>28062</v>
       </c>
       <c r="C247">
-        <v>20512</v>
+        <v>21653</v>
       </c>
       <c r="D247">
         <v>21813</v>
@@ -6812,7 +6812,7 @@
         <v>34977</v>
       </c>
       <c r="G247">
-        <v>34675</v>
+        <v>34748</v>
       </c>
       <c r="H247">
         <v>41858</v>
@@ -6826,7 +6826,7 @@
         <v>23288</v>
       </c>
       <c r="C248">
-        <v>18980</v>
+        <v>20596</v>
       </c>
       <c r="D248">
         <v>17600</v>
@@ -6838,7 +6838,7 @@
         <v>26735</v>
       </c>
       <c r="G248">
-        <v>28909</v>
+        <v>28958</v>
       </c>
       <c r="H248">
         <v>33261</v>
@@ -6852,7 +6852,7 @@
         <v>19998</v>
       </c>
       <c r="C249">
-        <v>14861</v>
+        <v>15544</v>
       </c>
       <c r="D249">
         <v>9150</v>
@@ -6864,7 +6864,7 @@
         <v>20878</v>
       </c>
       <c r="G249">
-        <v>19937</v>
+        <v>20116</v>
       </c>
       <c r="H249">
         <v>25742</v>
@@ -6878,7 +6878,7 @@
         <v>38691</v>
       </c>
       <c r="C250">
-        <v>23370</v>
+        <v>25603</v>
       </c>
       <c r="D250">
         <v>29414</v>
@@ -6890,7 +6890,7 @@
         <v>43076</v>
       </c>
       <c r="G250">
-        <v>41643</v>
+        <v>41675</v>
       </c>
       <c r="H250">
         <v>49576</v>
@@ -6904,7 +6904,7 @@
         <v>39389</v>
       </c>
       <c r="C251">
-        <v>24891</v>
+        <v>27541</v>
       </c>
       <c r="D251">
         <v>29622</v>
@@ -6916,7 +6916,7 @@
         <v>43491</v>
       </c>
       <c r="G251">
-        <v>43174</v>
+        <v>43274</v>
       </c>
       <c r="H251">
         <v>51005</v>
@@ -6930,7 +6930,7 @@
         <v>36334</v>
       </c>
       <c r="C252">
-        <v>19772</v>
+        <v>21219</v>
       </c>
       <c r="D252">
         <v>28870</v>
@@ -6942,7 +6942,7 @@
         <v>42102</v>
       </c>
       <c r="G252">
-        <v>39254</v>
+        <v>39283</v>
       </c>
       <c r="H252">
         <v>47127</v>
@@ -6956,7 +6956,7 @@
         <v>36973</v>
       </c>
       <c r="C253">
-        <v>21266</v>
+        <v>22485</v>
       </c>
       <c r="D253">
         <v>26218</v>
@@ -6968,7 +6968,7 @@
         <v>41284</v>
       </c>
       <c r="G253">
-        <v>38434</v>
+        <v>38523</v>
       </c>
       <c r="H253">
         <v>47518</v>
@@ -6982,7 +6982,7 @@
         <v>40231</v>
       </c>
       <c r="C254">
-        <v>24621</v>
+        <v>26684</v>
       </c>
       <c r="D254">
         <v>30319</v>
@@ -6994,7 +6994,7 @@
         <v>43854</v>
       </c>
       <c r="G254">
-        <v>43053</v>
+        <v>43109</v>
       </c>
       <c r="H254">
         <v>50893</v>
@@ -7008,7 +7008,7 @@
         <v>36973</v>
       </c>
       <c r="C255">
-        <v>21266</v>
+        <v>22485</v>
       </c>
       <c r="D255">
         <v>26218</v>
@@ -7020,7 +7020,7 @@
         <v>41284</v>
       </c>
       <c r="G255">
-        <v>38434</v>
+        <v>38523</v>
       </c>
       <c r="H255">
         <v>47518</v>
@@ -7034,7 +7034,7 @@
         <v>33775</v>
       </c>
       <c r="C256">
-        <v>18935</v>
+        <v>19697</v>
       </c>
       <c r="D256">
         <v>29336</v>
@@ -7046,7 +7046,7 @@
         <v>40854</v>
       </c>
       <c r="G256">
-        <v>39226</v>
+        <v>39236</v>
       </c>
       <c r="H256">
         <v>45753</v>
@@ -7060,7 +7060,7 @@
         <v>30186</v>
       </c>
       <c r="C257">
-        <v>15242</v>
+        <v>15531</v>
       </c>
       <c r="D257">
         <v>22452</v>
@@ -7072,7 +7072,7 @@
         <v>36190</v>
       </c>
       <c r="G257">
-        <v>31303</v>
+        <v>31308</v>
       </c>
       <c r="H257">
         <v>39732</v>
@@ -7086,7 +7086,7 @@
         <v>34588</v>
       </c>
       <c r="C258">
-        <v>14874</v>
+        <v>15164</v>
       </c>
       <c r="D258">
         <v>18125</v>
@@ -7098,7 +7098,7 @@
         <v>36844</v>
       </c>
       <c r="G258">
-        <v>27163</v>
+        <v>27165</v>
       </c>
       <c r="H258">
         <v>40346</v>
@@ -7112,7 +7112,7 @@
         <v>34588</v>
       </c>
       <c r="C259">
-        <v>14874</v>
+        <v>15164</v>
       </c>
       <c r="D259">
         <v>18125</v>
@@ -7124,7 +7124,7 @@
         <v>36844</v>
       </c>
       <c r="G259">
-        <v>27163</v>
+        <v>27165</v>
       </c>
       <c r="H259">
         <v>40346</v>
@@ -7138,7 +7138,7 @@
         <v>11132</v>
       </c>
       <c r="C260">
-        <v>8005</v>
+        <v>8457</v>
       </c>
       <c r="D260">
         <v>5532</v>
@@ -7150,7 +7150,7 @@
         <v>12071</v>
       </c>
       <c r="G260">
-        <v>10994</v>
+        <v>11001</v>
       </c>
       <c r="H260">
         <v>15266</v>
@@ -7164,7 +7164,7 @@
         <v>7392</v>
       </c>
       <c r="C261">
-        <v>4178</v>
+        <v>4260</v>
       </c>
       <c r="D261">
         <v>3795</v>
@@ -7190,7 +7190,7 @@
         <v>11077</v>
       </c>
       <c r="C262">
-        <v>6868</v>
+        <v>7287</v>
       </c>
       <c r="D262">
         <v>6068</v>
@@ -7202,7 +7202,7 @@
         <v>12242</v>
       </c>
       <c r="G262">
-        <v>10384</v>
+        <v>10388</v>
       </c>
       <c r="H262">
         <v>14582</v>
@@ -7216,7 +7216,7 @@
         <v>11077</v>
       </c>
       <c r="C263">
-        <v>7237</v>
+        <v>7645</v>
       </c>
       <c r="D263">
         <v>6068</v>
@@ -7228,7 +7228,7 @@
         <v>12242</v>
       </c>
       <c r="G263">
-        <v>10710</v>
+        <v>10714</v>
       </c>
       <c r="H263">
         <v>14850</v>
@@ -7242,7 +7242,7 @@
         <v>10079</v>
       </c>
       <c r="C264">
-        <v>6029</v>
+        <v>6261</v>
       </c>
       <c r="D264">
         <v>6359</v>
@@ -7254,10 +7254,10 @@
         <v>11659</v>
       </c>
       <c r="G264">
-        <v>9994</v>
+        <v>9999</v>
       </c>
       <c r="H264">
-        <v>13567</v>
+        <v>13568</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -7268,7 +7268,7 @@
         <v>10079</v>
       </c>
       <c r="C265">
-        <v>6029</v>
+        <v>6261</v>
       </c>
       <c r="D265">
         <v>6359</v>
@@ -7280,10 +7280,10 @@
         <v>11659</v>
       </c>
       <c r="G265">
-        <v>9994</v>
+        <v>9999</v>
       </c>
       <c r="H265">
-        <v>13567</v>
+        <v>13568</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -7294,7 +7294,7 @@
         <v>13062</v>
       </c>
       <c r="C266">
-        <v>9936</v>
+        <v>10217</v>
       </c>
       <c r="D266">
         <v>5451</v>
@@ -7306,7 +7306,7 @@
         <v>13759</v>
       </c>
       <c r="G266">
-        <v>12848</v>
+        <v>12866</v>
       </c>
       <c r="H266">
         <v>18221</v>
@@ -7320,7 +7320,7 @@
         <v>10079</v>
       </c>
       <c r="C267">
-        <v>6029</v>
+        <v>6261</v>
       </c>
       <c r="D267">
         <v>6359</v>
@@ -7332,10 +7332,10 @@
         <v>11659</v>
       </c>
       <c r="G267">
-        <v>9994</v>
+        <v>9999</v>
       </c>
       <c r="H267">
-        <v>13567</v>
+        <v>13568</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -7346,7 +7346,7 @@
         <v>7392</v>
       </c>
       <c r="C268">
-        <v>4178</v>
+        <v>4260</v>
       </c>
       <c r="D268">
         <v>3795</v>
@@ -7372,7 +7372,7 @@
         <v>7392</v>
       </c>
       <c r="C269">
-        <v>4178</v>
+        <v>4260</v>
       </c>
       <c r="D269">
         <v>3795</v>
@@ -7398,7 +7398,7 @@
         <v>6065</v>
       </c>
       <c r="C270">
-        <v>6369</v>
+        <v>6510</v>
       </c>
       <c r="D270">
         <v>2456</v>
@@ -7410,7 +7410,7 @@
         <v>6596</v>
       </c>
       <c r="G270">
-        <v>7629</v>
+        <v>7640</v>
       </c>
       <c r="H270">
         <v>10034</v>
@@ -7424,7 +7424,7 @@
         <v>4666</v>
       </c>
       <c r="C271">
-        <v>5022</v>
+        <v>5086</v>
       </c>
       <c r="D271">
         <v>159</v>
@@ -7436,7 +7436,7 @@
         <v>4713</v>
       </c>
       <c r="G271">
-        <v>5100</v>
+        <v>5136</v>
       </c>
       <c r="H271">
         <v>7412</v>
@@ -7450,7 +7450,7 @@
         <v>4666</v>
       </c>
       <c r="C272">
-        <v>5022</v>
+        <v>5086</v>
       </c>
       <c r="D272">
         <v>159</v>
@@ -7462,7 +7462,7 @@
         <v>4713</v>
       </c>
       <c r="G272">
-        <v>5100</v>
+        <v>5136</v>
       </c>
       <c r="H272">
         <v>7412</v>
@@ -7476,7 +7476,7 @@
         <v>6933</v>
       </c>
       <c r="C273">
-        <v>6851</v>
+        <v>6953</v>
       </c>
       <c r="D273">
         <v>2888</v>
@@ -7488,7 +7488,7 @@
         <v>7504</v>
       </c>
       <c r="G273">
-        <v>8319</v>
+        <v>8322</v>
       </c>
       <c r="H273">
         <v>11020</v>
@@ -7502,7 +7502,7 @@
         <v>6933</v>
       </c>
       <c r="C274">
-        <v>6851</v>
+        <v>6953</v>
       </c>
       <c r="D274">
         <v>2888</v>
@@ -7514,7 +7514,7 @@
         <v>7504</v>
       </c>
       <c r="G274">
-        <v>8319</v>
+        <v>8322</v>
       </c>
       <c r="H274">
         <v>11020</v>
@@ -7528,7 +7528,7 @@
         <v>8880</v>
       </c>
       <c r="C275">
-        <v>7283</v>
+        <v>7906</v>
       </c>
       <c r="D275">
         <v>5630</v>
@@ -7540,7 +7540,7 @@
         <v>10603</v>
       </c>
       <c r="G275">
-        <v>10722</v>
+        <v>10742</v>
       </c>
       <c r="H275">
         <v>13500</v>
@@ -7554,7 +7554,7 @@
         <v>6472</v>
       </c>
       <c r="C276">
-        <v>5318</v>
+        <v>5554</v>
       </c>
       <c r="D276">
         <v>1643</v>
@@ -7566,7 +7566,7 @@
         <v>6736</v>
       </c>
       <c r="G276">
-        <v>6198</v>
+        <v>6226</v>
       </c>
       <c r="H276">
         <v>8850</v>
@@ -7580,7 +7580,7 @@
         <v>11285</v>
       </c>
       <c r="C277">
-        <v>9980</v>
+        <v>10261</v>
       </c>
       <c r="D277">
         <v>7005</v>
@@ -7592,7 +7592,7 @@
         <v>13558</v>
       </c>
       <c r="G277">
-        <v>14198</v>
+        <v>14202</v>
       </c>
       <c r="H277">
         <v>17893</v>
@@ -7606,7 +7606,7 @@
         <v>17751</v>
       </c>
       <c r="C278">
-        <v>13758</v>
+        <v>14130</v>
       </c>
       <c r="D278">
         <v>8703</v>
@@ -7618,7 +7618,7 @@
         <v>21012</v>
       </c>
       <c r="G278">
-        <v>19427</v>
+        <v>19545</v>
       </c>
       <c r="H278">
         <v>26274</v>
@@ -7632,7 +7632,7 @@
         <v>21304</v>
       </c>
       <c r="C279">
-        <v>14487</v>
+        <v>15040</v>
       </c>
       <c r="D279">
         <v>11516</v>
@@ -7644,7 +7644,7 @@
         <v>26491</v>
       </c>
       <c r="G279">
-        <v>22832</v>
+        <v>23226</v>
       </c>
       <c r="H279">
         <v>31027</v>
@@ -7658,7 +7658,7 @@
         <v>21304</v>
       </c>
       <c r="C280">
-        <v>14487</v>
+        <v>15040</v>
       </c>
       <c r="D280">
         <v>11516</v>
@@ -7670,7 +7670,7 @@
         <v>26491</v>
       </c>
       <c r="G280">
-        <v>22832</v>
+        <v>23226</v>
       </c>
       <c r="H280">
         <v>31027</v>
@@ -7684,7 +7684,7 @@
         <v>6293</v>
       </c>
       <c r="C281">
-        <v>6165</v>
+        <v>6303</v>
       </c>
       <c r="D281">
         <v>2133</v>
@@ -7696,7 +7696,7 @@
         <v>6566</v>
       </c>
       <c r="G281">
-        <v>7053</v>
+        <v>7086</v>
       </c>
       <c r="H281">
         <v>9255</v>
@@ -7710,7 +7710,7 @@
         <v>5329</v>
       </c>
       <c r="C282">
-        <v>5335</v>
+        <v>5433</v>
       </c>
       <c r="D282">
         <v>1952</v>
@@ -7722,7 +7722,7 @@
         <v>5660</v>
       </c>
       <c r="G282">
-        <v>6232</v>
+        <v>6254</v>
       </c>
       <c r="H282">
         <v>7996</v>
@@ -7736,7 +7736,7 @@
         <v>5329</v>
       </c>
       <c r="C283">
-        <v>5335</v>
+        <v>5433</v>
       </c>
       <c r="D283">
         <v>1952</v>
@@ -7748,7 +7748,7 @@
         <v>5660</v>
       </c>
       <c r="G283">
-        <v>6232</v>
+        <v>6254</v>
       </c>
       <c r="H283">
         <v>7996</v>
@@ -7762,7 +7762,7 @@
         <v>5329</v>
       </c>
       <c r="C284">
-        <v>5335</v>
+        <v>5433</v>
       </c>
       <c r="D284">
         <v>1952</v>
@@ -7774,7 +7774,7 @@
         <v>5660</v>
       </c>
       <c r="G284">
-        <v>6232</v>
+        <v>6254</v>
       </c>
       <c r="H284">
         <v>7996</v>
@@ -7788,7 +7788,7 @@
         <v>6472</v>
       </c>
       <c r="C285">
-        <v>5318</v>
+        <v>5554</v>
       </c>
       <c r="D285">
         <v>1643</v>
@@ -7800,7 +7800,7 @@
         <v>6736</v>
       </c>
       <c r="G285">
-        <v>6198</v>
+        <v>6226</v>
       </c>
       <c r="H285">
         <v>8850</v>
@@ -7814,7 +7814,7 @@
         <v>21304</v>
       </c>
       <c r="C286">
-        <v>14487</v>
+        <v>15040</v>
       </c>
       <c r="D286">
         <v>11516</v>
@@ -7826,7 +7826,7 @@
         <v>26491</v>
       </c>
       <c r="G286">
-        <v>22832</v>
+        <v>23226</v>
       </c>
       <c r="H286">
         <v>31027</v>
@@ -7840,7 +7840,7 @@
         <v>27927</v>
       </c>
       <c r="C287">
-        <v>17159</v>
+        <v>18528</v>
       </c>
       <c r="D287">
         <v>19004</v>
@@ -7852,7 +7852,7 @@
         <v>31629</v>
       </c>
       <c r="G287">
-        <v>28873</v>
+        <v>28959</v>
       </c>
       <c r="H287">
         <v>36525</v>
@@ -7866,7 +7866,7 @@
         <v>20908</v>
       </c>
       <c r="C288">
-        <v>14245</v>
+        <v>15129</v>
       </c>
       <c r="D288">
         <v>13507</v>
@@ -7878,7 +7878,7 @@
         <v>24614</v>
       </c>
       <c r="G288">
-        <v>22918</v>
+        <v>23025</v>
       </c>
       <c r="H288">
         <v>29780</v>
@@ -7892,7 +7892,7 @@
         <v>31010</v>
       </c>
       <c r="C289">
-        <v>18641</v>
+        <v>19905</v>
       </c>
       <c r="D289">
         <v>16568</v>
@@ -7904,7 +7904,7 @@
         <v>32730</v>
       </c>
       <c r="G289">
-        <v>28215</v>
+        <v>28307</v>
       </c>
       <c r="H289">
         <v>38037</v>
@@ -7918,7 +7918,7 @@
         <v>27927</v>
       </c>
       <c r="C290">
-        <v>17159</v>
+        <v>18528</v>
       </c>
       <c r="D290">
         <v>19004</v>
@@ -7930,7 +7930,7 @@
         <v>31629</v>
       </c>
       <c r="G290">
-        <v>28873</v>
+        <v>28959</v>
       </c>
       <c r="H290">
         <v>36525</v>
@@ -7944,7 +7944,7 @@
         <v>18789</v>
       </c>
       <c r="C291">
-        <v>12600</v>
+        <v>13276</v>
       </c>
       <c r="D291">
         <v>11876</v>
@@ -7956,7 +7956,7 @@
         <v>22462</v>
       </c>
       <c r="G291">
-        <v>20420</v>
+        <v>20511</v>
       </c>
       <c r="H291">
         <v>27143</v>
@@ -7970,7 +7970,7 @@
         <v>23781</v>
       </c>
       <c r="C292">
-        <v>14233</v>
+        <v>14779</v>
       </c>
       <c r="D292">
         <v>13386</v>
@@ -7982,7 +7982,7 @@
         <v>27385</v>
       </c>
       <c r="G292">
-        <v>22960</v>
+        <v>23041</v>
       </c>
       <c r="H292">
         <v>31714</v>
@@ -7996,7 +7996,7 @@
         <v>23949</v>
       </c>
       <c r="C293">
-        <v>14399</v>
+        <v>15149</v>
       </c>
       <c r="D293">
         <v>14669</v>
@@ -8008,7 +8008,7 @@
         <v>27834</v>
       </c>
       <c r="G293">
-        <v>24083</v>
+        <v>24162</v>
       </c>
       <c r="H293">
         <v>32288</v>
@@ -8022,7 +8022,7 @@
         <v>23781</v>
       </c>
       <c r="C294">
-        <v>14233</v>
+        <v>14779</v>
       </c>
       <c r="D294">
         <v>13386</v>
@@ -8034,7 +8034,7 @@
         <v>27385</v>
       </c>
       <c r="G294">
-        <v>22960</v>
+        <v>23041</v>
       </c>
       <c r="H294">
         <v>31714</v>
@@ -8048,7 +8048,7 @@
         <v>20409</v>
       </c>
       <c r="C295">
-        <v>11794</v>
+        <v>12801</v>
       </c>
       <c r="D295">
         <v>13154</v>
@@ -8060,7 +8060,7 @@
         <v>23538</v>
       </c>
       <c r="G295">
-        <v>20301</v>
+        <v>20326</v>
       </c>
       <c r="H295">
         <v>27118</v>
@@ -8074,7 +8074,7 @@
         <v>21875</v>
       </c>
       <c r="C296">
-        <v>12740</v>
+        <v>13913</v>
       </c>
       <c r="D296">
         <v>15851</v>
@@ -8086,7 +8086,7 @@
         <v>25590</v>
       </c>
       <c r="G296">
-        <v>23032</v>
+        <v>23051</v>
       </c>
       <c r="H296">
         <v>29337</v>
@@ -8100,7 +8100,7 @@
         <v>20526</v>
       </c>
       <c r="C297">
-        <v>13666</v>
+        <v>14502</v>
       </c>
       <c r="D297">
         <v>14206</v>
@@ -8112,7 +8112,7 @@
         <v>24061</v>
       </c>
       <c r="G297">
-        <v>22638</v>
+        <v>22649</v>
       </c>
       <c r="H297">
         <v>28844</v>
@@ -8126,7 +8126,7 @@
         <v>18061</v>
       </c>
       <c r="C298">
-        <v>11782</v>
+        <v>12538</v>
       </c>
       <c r="D298">
         <v>13639</v>
@@ -8138,7 +8138,7 @@
         <v>22064</v>
       </c>
       <c r="G298">
-        <v>20653</v>
+        <v>20664</v>
       </c>
       <c r="H298">
         <v>26007</v>
@@ -8152,7 +8152,7 @@
         <v>17712</v>
       </c>
       <c r="C299">
-        <v>12059</v>
+        <v>12868</v>
       </c>
       <c r="D299">
         <v>12754</v>
@@ -8164,7 +8164,7 @@
         <v>21335</v>
       </c>
       <c r="G299">
-        <v>20209</v>
+        <v>20221</v>
       </c>
       <c r="H299">
         <v>25675</v>
@@ -8178,7 +8178,7 @@
         <v>20409</v>
       </c>
       <c r="C300">
-        <v>11794</v>
+        <v>12801</v>
       </c>
       <c r="D300">
         <v>13154</v>
@@ -8190,7 +8190,7 @@
         <v>23538</v>
       </c>
       <c r="G300">
-        <v>20301</v>
+        <v>20326</v>
       </c>
       <c r="H300">
         <v>27118</v>
@@ -8204,7 +8204,7 @@
         <v>21875</v>
       </c>
       <c r="C301">
-        <v>13346</v>
+        <v>14496</v>
       </c>
       <c r="D301">
         <v>15851</v>
@@ -8216,7 +8216,7 @@
         <v>25590</v>
       </c>
       <c r="G301">
-        <v>23526</v>
+        <v>23544</v>
       </c>
       <c r="H301">
         <v>29747</v>
@@ -8230,7 +8230,7 @@
         <v>18061</v>
       </c>
       <c r="C302">
-        <v>12914</v>
+        <v>13628</v>
       </c>
       <c r="D302">
         <v>13639</v>
@@ -8242,7 +8242,7 @@
         <v>22064</v>
       </c>
       <c r="G302">
-        <v>21602</v>
+        <v>21611</v>
       </c>
       <c r="H302">
         <v>26817</v>
@@ -8256,7 +8256,7 @@
         <v>18061</v>
       </c>
       <c r="C303">
-        <v>12914</v>
+        <v>13628</v>
       </c>
       <c r="D303">
         <v>13639</v>
@@ -8268,7 +8268,7 @@
         <v>22064</v>
       </c>
       <c r="G303">
-        <v>21602</v>
+        <v>21611</v>
       </c>
       <c r="H303">
         <v>26817</v>
@@ -8282,7 +8282,7 @@
         <v>18243</v>
       </c>
       <c r="C304">
-        <v>11326</v>
+        <v>12063</v>
       </c>
       <c r="D304">
         <v>10685</v>
@@ -8294,7 +8294,7 @@
         <v>20411</v>
       </c>
       <c r="G304">
-        <v>17736</v>
+        <v>17754</v>
       </c>
       <c r="H304">
         <v>23972</v>
@@ -8308,7 +8308,7 @@
         <v>18243</v>
       </c>
       <c r="C305">
-        <v>11326</v>
+        <v>12063</v>
       </c>
       <c r="D305">
         <v>10685</v>
@@ -8320,7 +8320,7 @@
         <v>20411</v>
       </c>
       <c r="G305">
-        <v>17736</v>
+        <v>17754</v>
       </c>
       <c r="H305">
         <v>23972</v>
@@ -8334,7 +8334,7 @@
         <v>21493</v>
       </c>
       <c r="C306">
-        <v>10425</v>
+        <v>10808</v>
       </c>
       <c r="D306">
         <v>10059</v>
@@ -8346,7 +8346,7 @@
         <v>22859</v>
       </c>
       <c r="G306">
-        <v>16411</v>
+        <v>16423</v>
       </c>
       <c r="H306">
         <v>25396</v>
@@ -8360,7 +8360,7 @@
         <v>18243</v>
       </c>
       <c r="C307">
-        <v>11326</v>
+        <v>12063</v>
       </c>
       <c r="D307">
         <v>10685</v>
@@ -8372,7 +8372,7 @@
         <v>20411</v>
       </c>
       <c r="G307">
-        <v>17736</v>
+        <v>17754</v>
       </c>
       <c r="H307">
         <v>23972</v>
@@ -8386,7 +8386,7 @@
         <v>21493</v>
       </c>
       <c r="C308">
-        <v>10894</v>
+        <v>11256</v>
       </c>
       <c r="D308">
         <v>10059</v>
@@ -8398,7 +8398,7 @@
         <v>22859</v>
       </c>
       <c r="G308">
-        <v>16803</v>
+        <v>16812</v>
       </c>
       <c r="H308">
         <v>25661</v>
@@ -8412,7 +8412,7 @@
         <v>21493</v>
       </c>
       <c r="C309">
-        <v>10425</v>
+        <v>10808</v>
       </c>
       <c r="D309">
         <v>10059</v>
@@ -8424,7 +8424,7 @@
         <v>22859</v>
       </c>
       <c r="G309">
-        <v>16411</v>
+        <v>16423</v>
       </c>
       <c r="H309">
         <v>25396</v>
@@ -8438,7 +8438,7 @@
         <v>18243</v>
       </c>
       <c r="C310">
-        <v>11840</v>
+        <v>12559</v>
       </c>
       <c r="D310">
         <v>10685</v>
@@ -8450,7 +8450,7 @@
         <v>20411</v>
       </c>
       <c r="G310">
-        <v>18189</v>
+        <v>18205</v>
       </c>
       <c r="H310">
         <v>24325</v>
@@ -8464,7 +8464,7 @@
         <v>7960</v>
       </c>
       <c r="C311">
-        <v>6064</v>
+        <v>6135</v>
       </c>
       <c r="D311">
         <v>2673</v>
@@ -8476,7 +8476,7 @@
         <v>8406</v>
       </c>
       <c r="G311">
-        <v>7620</v>
+        <v>7626</v>
       </c>
       <c r="H311">
         <v>10865</v>
@@ -8490,7 +8490,7 @@
         <v>7960</v>
       </c>
       <c r="C312">
-        <v>6064</v>
+        <v>6135</v>
       </c>
       <c r="D312">
         <v>2673</v>
@@ -8502,7 +8502,7 @@
         <v>8406</v>
       </c>
       <c r="G312">
-        <v>7620</v>
+        <v>7626</v>
       </c>
       <c r="H312">
         <v>10865</v>
@@ -8516,7 +8516,7 @@
         <v>7960</v>
       </c>
       <c r="C313">
-        <v>6064</v>
+        <v>6135</v>
       </c>
       <c r="D313">
         <v>2673</v>
@@ -8528,7 +8528,7 @@
         <v>8406</v>
       </c>
       <c r="G313">
-        <v>7620</v>
+        <v>7626</v>
       </c>
       <c r="H313">
         <v>10865</v>
@@ -8542,7 +8542,7 @@
         <v>7960</v>
       </c>
       <c r="C314">
-        <v>6064</v>
+        <v>6135</v>
       </c>
       <c r="D314">
         <v>2673</v>
@@ -8554,7 +8554,7 @@
         <v>8406</v>
       </c>
       <c r="G314">
-        <v>7620</v>
+        <v>7626</v>
       </c>
       <c r="H314">
         <v>10865</v>
@@ -8568,7 +8568,7 @@
         <v>31458</v>
       </c>
       <c r="C315">
-        <v>19283</v>
+        <v>20951</v>
       </c>
       <c r="D315">
         <v>20270</v>
@@ -8580,7 +8580,7 @@
         <v>34206</v>
       </c>
       <c r="G315">
-        <v>30973</v>
+        <v>31078</v>
       </c>
       <c r="H315">
         <v>39551</v>
@@ -8594,7 +8594,7 @@
         <v>37421</v>
       </c>
       <c r="C316">
-        <v>21533</v>
+        <v>24641</v>
       </c>
       <c r="D316">
         <v>31671</v>
@@ -8606,7 +8606,7 @@
         <v>41907</v>
       </c>
       <c r="G316">
-        <v>41300</v>
+        <v>41350</v>
       </c>
       <c r="H316">
         <v>47248</v>
@@ -8620,7 +8620,7 @@
         <v>38156</v>
       </c>
       <c r="C317">
-        <v>20465</v>
+        <v>23432</v>
       </c>
       <c r="D317">
         <v>28838</v>
@@ -8632,7 +8632,7 @@
         <v>41325</v>
       </c>
       <c r="G317">
-        <v>38534</v>
+        <v>38573</v>
       </c>
       <c r="H317">
         <v>46390</v>
@@ -8646,7 +8646,7 @@
         <v>35250</v>
       </c>
       <c r="C318">
-        <v>19477</v>
+        <v>22537</v>
       </c>
       <c r="D318">
         <v>26368</v>
@@ -8658,7 +8658,7 @@
         <v>38587</v>
       </c>
       <c r="G318">
-        <v>35981</v>
+        <v>36064</v>
       </c>
       <c r="H318">
         <v>43480</v>
@@ -8672,7 +8672,7 @@
         <v>31318</v>
       </c>
       <c r="C319">
-        <v>17245</v>
+        <v>19099</v>
       </c>
       <c r="D319">
         <v>18999</v>
@@ -8684,7 +8684,7 @@
         <v>33696</v>
       </c>
       <c r="G319">
-        <v>28594</v>
+        <v>28671</v>
       </c>
       <c r="H319">
         <v>38232</v>
@@ -8698,7 +8698,7 @@
         <v>31880</v>
       </c>
       <c r="C320">
-        <v>17829</v>
+        <v>20390</v>
       </c>
       <c r="D320">
         <v>23905</v>
@@ -8710,7 +8710,7 @@
         <v>35880</v>
       </c>
       <c r="G320">
-        <v>33110</v>
+        <v>33166</v>
       </c>
       <c r="H320">
         <v>40674</v>
@@ -8724,7 +8724,7 @@
         <v>35167</v>
       </c>
       <c r="C321">
-        <v>19117</v>
+        <v>21922</v>
       </c>
       <c r="D321">
         <v>26469</v>
@@ -8736,7 +8736,7 @@
         <v>38646</v>
       </c>
       <c r="G321">
-        <v>35909</v>
+        <v>35951</v>
       </c>
       <c r="H321">
         <v>43497</v>
@@ -8750,7 +8750,7 @@
         <v>29343</v>
       </c>
       <c r="C322">
-        <v>18511</v>
+        <v>19735</v>
       </c>
       <c r="D322">
         <v>18232</v>
@@ -8762,7 +8762,7 @@
         <v>32320</v>
       </c>
       <c r="G322">
-        <v>29314</v>
+        <v>29356</v>
       </c>
       <c r="H322">
         <v>37581</v>
@@ -8776,7 +8776,7 @@
         <v>32293</v>
       </c>
       <c r="C323">
-        <v>17132</v>
+        <v>19369</v>
       </c>
       <c r="D323">
         <v>25277</v>
@@ -8788,7 +8788,7 @@
         <v>36706</v>
       </c>
       <c r="G323">
-        <v>33671</v>
+        <v>33696</v>
       </c>
       <c r="H323">
         <v>40930</v>
@@ -8802,7 +8802,7 @@
         <v>32293</v>
       </c>
       <c r="C324">
-        <v>17132</v>
+        <v>19369</v>
       </c>
       <c r="D324">
         <v>25277</v>
@@ -8814,7 +8814,7 @@
         <v>36706</v>
       </c>
       <c r="G324">
-        <v>33671</v>
+        <v>33696</v>
       </c>
       <c r="H324">
         <v>40930</v>
@@ -8828,7 +8828,7 @@
         <v>32293</v>
       </c>
       <c r="C325">
-        <v>17132</v>
+        <v>19369</v>
       </c>
       <c r="D325">
         <v>25277</v>
@@ -8840,7 +8840,7 @@
         <v>36706</v>
       </c>
       <c r="G325">
-        <v>33671</v>
+        <v>33696</v>
       </c>
       <c r="H325">
         <v>40930</v>
@@ -8854,7 +8854,7 @@
         <v>36570</v>
       </c>
       <c r="C326">
-        <v>20692</v>
+        <v>23520</v>
       </c>
       <c r="D326">
         <v>29421</v>
@@ -8866,7 +8866,7 @@
         <v>40719</v>
       </c>
       <c r="G326">
-        <v>39240</v>
+        <v>39313</v>
       </c>
       <c r="H326">
         <v>46027</v>
@@ -8880,7 +8880,7 @@
         <v>27617</v>
       </c>
       <c r="C327">
-        <v>16935</v>
+        <v>17788</v>
       </c>
       <c r="D327">
         <v>12164</v>
@@ -8892,7 +8892,7 @@
         <v>29150</v>
       </c>
       <c r="G327">
-        <v>23725</v>
+        <v>23811</v>
       </c>
       <c r="H327">
         <v>34728</v>
@@ -8906,7 +8906,7 @@
         <v>27617</v>
       </c>
       <c r="C328">
-        <v>16935</v>
+        <v>17788</v>
       </c>
       <c r="D328">
         <v>12164</v>
@@ -8918,7 +8918,7 @@
         <v>29150</v>
       </c>
       <c r="G328">
-        <v>23725</v>
+        <v>23811</v>
       </c>
       <c r="H328">
         <v>34728</v>
@@ -8932,7 +8932,7 @@
         <v>25750</v>
       </c>
       <c r="C329">
-        <v>15198</v>
+        <v>15759</v>
       </c>
       <c r="D329">
         <v>11980</v>
@@ -8944,7 +8944,7 @@
         <v>27658</v>
       </c>
       <c r="G329">
-        <v>22313</v>
+        <v>22337</v>
       </c>
       <c r="H329">
         <v>32531</v>
@@ -8958,7 +8958,7 @@
         <v>27617</v>
       </c>
       <c r="C330">
-        <v>16935</v>
+        <v>17788</v>
       </c>
       <c r="D330">
         <v>12164</v>
@@ -8970,7 +8970,7 @@
         <v>29150</v>
       </c>
       <c r="G330">
-        <v>23725</v>
+        <v>23811</v>
       </c>
       <c r="H330">
         <v>34728</v>
@@ -8984,7 +8984,7 @@
         <v>27617</v>
       </c>
       <c r="C331">
-        <v>16174</v>
+        <v>17088</v>
       </c>
       <c r="D331">
         <v>12164</v>
@@ -8996,7 +8996,7 @@
         <v>29150</v>
       </c>
       <c r="G331">
-        <v>23066</v>
+        <v>23158</v>
       </c>
       <c r="H331">
         <v>34212</v>
@@ -9010,7 +9010,7 @@
         <v>32498</v>
       </c>
       <c r="C332">
-        <v>19396</v>
+        <v>20837</v>
       </c>
       <c r="D332">
         <v>17413</v>
@@ -9022,7 +9022,7 @@
         <v>33867</v>
       </c>
       <c r="G332">
-        <v>29067</v>
+        <v>29231</v>
       </c>
       <c r="H332">
         <v>39270</v>
@@ -9036,7 +9036,7 @@
         <v>34018</v>
       </c>
       <c r="C333">
-        <v>19567</v>
+        <v>21396</v>
       </c>
       <c r="D333">
         <v>22115</v>
@@ -9048,7 +9048,7 @@
         <v>36276</v>
       </c>
       <c r="G333">
-        <v>33054</v>
+        <v>33129</v>
       </c>
       <c r="H333">
         <v>41705</v>
@@ -9062,7 +9062,7 @@
         <v>36316</v>
       </c>
       <c r="C334">
-        <v>22559</v>
+        <v>24514</v>
       </c>
       <c r="D334">
         <v>22831</v>
@@ -9074,7 +9074,7 @@
         <v>38390</v>
       </c>
       <c r="G334">
-        <v>35812</v>
+        <v>35972</v>
       </c>
       <c r="H334">
         <v>45079</v>
@@ -9088,7 +9088,7 @@
         <v>33083</v>
       </c>
       <c r="C335">
-        <v>20937</v>
+        <v>22568</v>
       </c>
       <c r="D335">
         <v>20270</v>
@@ -9100,7 +9100,7 @@
         <v>35213</v>
       </c>
       <c r="G335">
-        <v>32871</v>
+        <v>33002</v>
       </c>
       <c r="H335">
         <v>41881</v>
@@ -9114,7 +9114,7 @@
         <v>30242</v>
       </c>
       <c r="C336">
-        <v>18238</v>
+        <v>19308</v>
       </c>
       <c r="D336">
         <v>14312</v>
@@ -9126,7 +9126,7 @@
         <v>31396</v>
       </c>
       <c r="G336">
-        <v>26126</v>
+        <v>26304</v>
       </c>
       <c r="H336">
         <v>36755</v>
@@ -9140,7 +9140,7 @@
         <v>12283</v>
       </c>
       <c r="C337">
-        <v>9369</v>
+        <v>10115</v>
       </c>
       <c r="D337">
         <v>8026</v>
@@ -9152,7 +9152,7 @@
         <v>14547</v>
       </c>
       <c r="G337">
-        <v>14227</v>
+        <v>14247</v>
       </c>
       <c r="H337">
         <v>17671</v>
@@ -9166,7 +9166,7 @@
         <v>10556</v>
       </c>
       <c r="C338">
-        <v>8400</v>
+        <v>8892</v>
       </c>
       <c r="D338">
         <v>10447</v>
@@ -9178,7 +9178,7 @@
         <v>14562</v>
       </c>
       <c r="G338">
-        <v>15301</v>
+        <v>15315</v>
       </c>
       <c r="H338">
         <v>17428</v>
@@ -9192,7 +9192,7 @@
         <v>12283</v>
       </c>
       <c r="C339">
-        <v>9369</v>
+        <v>10115</v>
       </c>
       <c r="D339">
         <v>8026</v>
@@ -9204,7 +9204,7 @@
         <v>14547</v>
       </c>
       <c r="G339">
-        <v>14227</v>
+        <v>14247</v>
       </c>
       <c r="H339">
         <v>17671</v>
@@ -9218,7 +9218,7 @@
         <v>9974</v>
       </c>
       <c r="C340">
-        <v>7638</v>
+        <v>8005</v>
       </c>
       <c r="D340">
         <v>7439</v>
@@ -9230,7 +9230,7 @@
         <v>12421</v>
       </c>
       <c r="G340">
-        <v>12358</v>
+        <v>12363</v>
       </c>
       <c r="H340">
         <v>15067</v>
@@ -9244,7 +9244,7 @@
         <v>9974</v>
       </c>
       <c r="C341">
-        <v>7638</v>
+        <v>8005</v>
       </c>
       <c r="D341">
         <v>7439</v>
@@ -9256,7 +9256,7 @@
         <v>12421</v>
       </c>
       <c r="G341">
-        <v>12358</v>
+        <v>12363</v>
       </c>
       <c r="H341">
         <v>15067</v>
@@ -9270,7 +9270,7 @@
         <v>10224</v>
       </c>
       <c r="C342">
-        <v>9419</v>
+        <v>9789</v>
       </c>
       <c r="D342">
         <v>9126</v>
@@ -9282,7 +9282,7 @@
         <v>13654</v>
       </c>
       <c r="G342">
-        <v>15186</v>
+        <v>15195</v>
       </c>
       <c r="H342">
         <v>17384</v>
@@ -9296,7 +9296,7 @@
         <v>10224</v>
       </c>
       <c r="C343">
-        <v>9419</v>
+        <v>9789</v>
       </c>
       <c r="D343">
         <v>9126</v>
@@ -9308,7 +9308,7 @@
         <v>13654</v>
       </c>
       <c r="G343">
-        <v>15186</v>
+        <v>15195</v>
       </c>
       <c r="H343">
         <v>17384</v>
@@ -9322,7 +9322,7 @@
         <v>9974</v>
       </c>
       <c r="C344">
-        <v>7638</v>
+        <v>8005</v>
       </c>
       <c r="D344">
         <v>7439</v>
@@ -9334,7 +9334,7 @@
         <v>12421</v>
       </c>
       <c r="G344">
-        <v>12358</v>
+        <v>12363</v>
       </c>
       <c r="H344">
         <v>15067</v>
@@ -9348,7 +9348,7 @@
         <v>6587</v>
       </c>
       <c r="C345">
-        <v>5953</v>
+        <v>6046</v>
       </c>
       <c r="D345">
         <v>4624</v>
@@ -9360,7 +9360,7 @@
         <v>8236</v>
       </c>
       <c r="G345">
-        <v>8657</v>
+        <v>8662</v>
       </c>
       <c r="H345">
         <v>10592</v>
@@ -9374,7 +9374,7 @@
         <v>6587</v>
       </c>
       <c r="C346">
-        <v>5953</v>
+        <v>6046</v>
       </c>
       <c r="D346">
         <v>4624</v>
@@ -9386,7 +9386,7 @@
         <v>8236</v>
       </c>
       <c r="G346">
-        <v>8657</v>
+        <v>8662</v>
       </c>
       <c r="H346">
         <v>10592</v>
@@ -9400,7 +9400,7 @@
         <v>6587</v>
       </c>
       <c r="C347">
-        <v>5953</v>
+        <v>6046</v>
       </c>
       <c r="D347">
         <v>4624</v>
@@ -9412,7 +9412,7 @@
         <v>8236</v>
       </c>
       <c r="G347">
-        <v>8657</v>
+        <v>8662</v>
       </c>
       <c r="H347">
         <v>10592</v>
@@ -9426,7 +9426,7 @@
         <v>13917</v>
       </c>
       <c r="C348">
-        <v>9788</v>
+        <v>10078</v>
       </c>
       <c r="D348">
         <v>7572</v>
@@ -9438,7 +9438,7 @@
         <v>15803</v>
       </c>
       <c r="G348">
-        <v>14325</v>
+        <v>14335</v>
       </c>
       <c r="H348">
         <v>18796</v>
@@ -9452,7 +9452,7 @@
         <v>13917</v>
       </c>
       <c r="C349">
-        <v>9788</v>
+        <v>10078</v>
       </c>
       <c r="D349">
         <v>7572</v>
@@ -9464,7 +9464,7 @@
         <v>15803</v>
       </c>
       <c r="G349">
-        <v>14325</v>
+        <v>14335</v>
       </c>
       <c r="H349">
         <v>18796</v>
@@ -9478,7 +9478,7 @@
         <v>13917</v>
       </c>
       <c r="C350">
-        <v>9788</v>
+        <v>10078</v>
       </c>
       <c r="D350">
         <v>7572</v>
@@ -9490,7 +9490,7 @@
         <v>15803</v>
       </c>
       <c r="G350">
-        <v>14325</v>
+        <v>14335</v>
       </c>
       <c r="H350">
         <v>18796</v>
@@ -9504,7 +9504,7 @@
         <v>4389</v>
       </c>
       <c r="C351">
-        <v>5368</v>
+        <v>5444</v>
       </c>
       <c r="D351">
         <v>2898</v>
@@ -9516,7 +9516,7 @@
         <v>5361</v>
       </c>
       <c r="G351">
-        <v>6995</v>
+        <v>7006</v>
       </c>
       <c r="H351">
         <v>8205</v>
@@ -9530,7 +9530,7 @@
         <v>4389</v>
       </c>
       <c r="C352">
-        <v>5368</v>
+        <v>5444</v>
       </c>
       <c r="D352">
         <v>2898</v>
@@ -9542,7 +9542,7 @@
         <v>5361</v>
       </c>
       <c r="G352">
-        <v>6995</v>
+        <v>7006</v>
       </c>
       <c r="H352">
         <v>8205</v>
@@ -9556,7 +9556,7 @@
         <v>19013</v>
       </c>
       <c r="C353">
-        <v>14216</v>
+        <v>14914</v>
       </c>
       <c r="D353">
         <v>10463</v>
@@ -9568,7 +9568,7 @@
         <v>19861</v>
       </c>
       <c r="G353">
-        <v>19566</v>
+        <v>19591</v>
       </c>
       <c r="H353">
         <v>23929</v>
@@ -9582,7 +9582,7 @@
         <v>18960</v>
       </c>
       <c r="C354">
-        <v>10761</v>
+        <v>11068</v>
       </c>
       <c r="D354">
         <v>9212</v>
@@ -9594,7 +9594,7 @@
         <v>19697</v>
       </c>
       <c r="G354">
-        <v>16299</v>
+        <v>16302</v>
       </c>
       <c r="H354">
         <v>21994</v>
@@ -9608,7 +9608,7 @@
         <v>19013</v>
       </c>
       <c r="C355">
-        <v>14216</v>
+        <v>14914</v>
       </c>
       <c r="D355">
         <v>10463</v>
@@ -9620,7 +9620,7 @@
         <v>19861</v>
       </c>
       <c r="G355">
-        <v>19566</v>
+        <v>19591</v>
       </c>
       <c r="H355">
         <v>23929</v>
@@ -9634,7 +9634,7 @@
         <v>12984</v>
       </c>
       <c r="C356">
-        <v>9700</v>
+        <v>9943</v>
       </c>
       <c r="D356">
         <v>8479</v>
@@ -9646,7 +9646,7 @@
         <v>14381</v>
       </c>
       <c r="G356">
-        <v>14594</v>
+        <v>14595</v>
       </c>
       <c r="H356">
         <v>17802</v>
@@ -9660,7 +9660,7 @@
         <v>12984</v>
       </c>
       <c r="C357">
-        <v>9700</v>
+        <v>9943</v>
       </c>
       <c r="D357">
         <v>8479</v>
@@ -9672,7 +9672,7 @@
         <v>14381</v>
       </c>
       <c r="G357">
-        <v>14594</v>
+        <v>14595</v>
       </c>
       <c r="H357">
         <v>17802</v>
@@ -9686,7 +9686,7 @@
         <v>12984</v>
       </c>
       <c r="C358">
-        <v>9700</v>
+        <v>9943</v>
       </c>
       <c r="D358">
         <v>8479</v>
@@ -9698,7 +9698,7 @@
         <v>14381</v>
       </c>
       <c r="G358">
-        <v>14594</v>
+        <v>14595</v>
       </c>
       <c r="H358">
         <v>17802</v>
@@ -9712,7 +9712,7 @@
         <v>4560</v>
       </c>
       <c r="C359">
-        <v>5613</v>
+        <v>5668</v>
       </c>
       <c r="D359">
         <v>2711</v>
@@ -9724,7 +9724,7 @@
         <v>5952</v>
       </c>
       <c r="G359">
-        <v>7472</v>
+        <v>7486</v>
       </c>
       <c r="H359">
         <v>9227</v>
@@ -9738,7 +9738,7 @@
         <v>4560</v>
       </c>
       <c r="C360">
-        <v>5613</v>
+        <v>5668</v>
       </c>
       <c r="D360">
         <v>2711</v>
@@ -9750,7 +9750,7 @@
         <v>5952</v>
       </c>
       <c r="G360">
-        <v>7472</v>
+        <v>7486</v>
       </c>
       <c r="H360">
         <v>9227</v>
@@ -9764,7 +9764,7 @@
         <v>18049</v>
       </c>
       <c r="C361">
-        <v>10469</v>
+        <v>10884</v>
       </c>
       <c r="D361">
         <v>14877</v>
@@ -9776,7 +9776,7 @@
         <v>24929</v>
       </c>
       <c r="G361">
-        <v>22217</v>
+        <v>22228</v>
       </c>
       <c r="H361">
         <v>28986</v>
@@ -9790,7 +9790,7 @@
         <v>13413</v>
       </c>
       <c r="C362">
-        <v>10422</v>
+        <v>10629</v>
       </c>
       <c r="D362">
         <v>4543</v>
@@ -9802,7 +9802,7 @@
         <v>14626</v>
       </c>
       <c r="G362">
-        <v>13106</v>
+        <v>13122</v>
       </c>
       <c r="H362">
         <v>19817</v>
@@ -9816,7 +9816,7 @@
         <v>17766</v>
       </c>
       <c r="C363">
-        <v>7993</v>
+        <v>8045</v>
       </c>
       <c r="D363">
         <v>4363</v>
@@ -9828,7 +9828,7 @@
         <v>18708</v>
       </c>
       <c r="G363">
-        <v>10647</v>
+        <v>10648</v>
       </c>
       <c r="H363">
         <v>21225</v>
@@ -9842,7 +9842,7 @@
         <v>13007</v>
       </c>
       <c r="C364">
-        <v>10483</v>
+        <v>10736</v>
       </c>
       <c r="D364">
         <v>17398</v>
@@ -9854,7 +9854,7 @@
         <v>22350</v>
       </c>
       <c r="G364">
-        <v>23564</v>
+        <v>23565</v>
       </c>
       <c r="H364">
         <v>26237</v>
@@ -9868,7 +9868,7 @@
         <v>13007</v>
       </c>
       <c r="C365">
-        <v>10483</v>
+        <v>10736</v>
       </c>
       <c r="D365">
         <v>17398</v>
@@ -9880,7 +9880,7 @@
         <v>22350</v>
       </c>
       <c r="G365">
-        <v>23564</v>
+        <v>23565</v>
       </c>
       <c r="H365">
         <v>26237</v>
@@ -9894,7 +9894,7 @@
         <v>8529</v>
       </c>
       <c r="C366">
-        <v>8235</v>
+        <v>8332</v>
       </c>
       <c r="D366">
         <v>10668</v>
@@ -9906,7 +9906,7 @@
         <v>15030</v>
       </c>
       <c r="G366">
-        <v>16285</v>
+        <v>16287</v>
       </c>
       <c r="H366">
         <v>18526</v>
@@ -9920,7 +9920,7 @@
         <v>8529</v>
       </c>
       <c r="C367">
-        <v>8235</v>
+        <v>8332</v>
       </c>
       <c r="D367">
         <v>10668</v>
@@ -9932,7 +9932,7 @@
         <v>15030</v>
       </c>
       <c r="G367">
-        <v>16285</v>
+        <v>16287</v>
       </c>
       <c r="H367">
         <v>18526</v>
@@ -9946,7 +9946,7 @@
         <v>10004</v>
       </c>
       <c r="C368">
-        <v>8612</v>
+        <v>8720</v>
       </c>
       <c r="D368">
         <v>13184</v>
@@ -9958,7 +9958,7 @@
         <v>18164</v>
       </c>
       <c r="G368">
-        <v>18874</v>
+        <v>18875</v>
       </c>
       <c r="H368">
         <v>21339</v>
@@ -9972,7 +9972,7 @@
         <v>8529</v>
       </c>
       <c r="C369">
-        <v>8235</v>
+        <v>8332</v>
       </c>
       <c r="D369">
         <v>10668</v>
@@ -9984,7 +9984,7 @@
         <v>15030</v>
       </c>
       <c r="G369">
-        <v>16285</v>
+        <v>16287</v>
       </c>
       <c r="H369">
         <v>18526</v>
@@ -9998,7 +9998,7 @@
         <v>8527</v>
       </c>
       <c r="C370">
-        <v>6991</v>
+        <v>7044</v>
       </c>
       <c r="D370">
         <v>2620</v>
@@ -10010,7 +10010,7 @@
         <v>9572</v>
       </c>
       <c r="G370">
-        <v>8555</v>
+        <v>8560</v>
       </c>
       <c r="H370">
         <v>12604</v>
@@ -10024,7 +10024,7 @@
         <v>8527</v>
       </c>
       <c r="C371">
-        <v>6991</v>
+        <v>7044</v>
       </c>
       <c r="D371">
         <v>2620</v>
@@ -10036,7 +10036,7 @@
         <v>9572</v>
       </c>
       <c r="G371">
-        <v>8555</v>
+        <v>8560</v>
       </c>
       <c r="H371">
         <v>12604</v>
@@ -10050,7 +10050,7 @@
         <v>8527</v>
       </c>
       <c r="C372">
-        <v>6991</v>
+        <v>7044</v>
       </c>
       <c r="D372">
         <v>2620</v>
@@ -10062,7 +10062,7 @@
         <v>9572</v>
       </c>
       <c r="G372">
-        <v>8555</v>
+        <v>8560</v>
       </c>
       <c r="H372">
         <v>12604</v>
@@ -10076,7 +10076,7 @@
         <v>20051</v>
       </c>
       <c r="C373">
-        <v>13437</v>
+        <v>14073</v>
       </c>
       <c r="D373">
         <v>14415</v>
@@ -10088,7 +10088,7 @@
         <v>24706</v>
       </c>
       <c r="G373">
-        <v>22744</v>
+        <v>22757</v>
       </c>
       <c r="H373">
         <v>28231</v>
@@ -10102,7 +10102,7 @@
         <v>17220</v>
       </c>
       <c r="C374">
-        <v>10831</v>
+        <v>11257</v>
       </c>
       <c r="D374">
         <v>10247</v>
@@ -10114,7 +10114,7 @@
         <v>20275</v>
       </c>
       <c r="G374">
-        <v>17361</v>
+        <v>17367</v>
       </c>
       <c r="H374">
         <v>23174</v>
@@ -10128,7 +10128,7 @@
         <v>20051</v>
       </c>
       <c r="C375">
-        <v>13437</v>
+        <v>14073</v>
       </c>
       <c r="D375">
         <v>14415</v>
@@ -10140,7 +10140,7 @@
         <v>24706</v>
       </c>
       <c r="G375">
-        <v>22744</v>
+        <v>22757</v>
       </c>
       <c r="H375">
         <v>28231</v>
@@ -10154,7 +10154,7 @@
         <v>16563</v>
       </c>
       <c r="C376">
-        <v>11418</v>
+        <v>11811</v>
       </c>
       <c r="D376">
         <v>10679</v>
@@ -10166,7 +10166,7 @@
         <v>19618</v>
       </c>
       <c r="G376">
-        <v>17961</v>
+        <v>17974</v>
       </c>
       <c r="H376">
         <v>22865</v>
@@ -10180,7 +10180,7 @@
         <v>16563</v>
       </c>
       <c r="C377">
-        <v>11418</v>
+        <v>11811</v>
       </c>
       <c r="D377">
         <v>10679</v>
@@ -10192,7 +10192,7 @@
         <v>19618</v>
       </c>
       <c r="G377">
-        <v>17961</v>
+        <v>17974</v>
       </c>
       <c r="H377">
         <v>22865</v>
@@ -10206,7 +10206,7 @@
         <v>23766</v>
       </c>
       <c r="C378">
-        <v>15936</v>
+        <v>16644</v>
       </c>
       <c r="D378">
         <v>21236</v>
@@ -10218,7 +10218,7 @@
         <v>31007</v>
       </c>
       <c r="G378">
-        <v>30240</v>
+        <v>30257</v>
       </c>
       <c r="H378">
         <v>34673</v>
@@ -10232,7 +10232,7 @@
         <v>23766</v>
       </c>
       <c r="C379">
-        <v>15936</v>
+        <v>16644</v>
       </c>
       <c r="D379">
         <v>21236</v>
@@ -10244,7 +10244,7 @@
         <v>31007</v>
       </c>
       <c r="G379">
-        <v>30240</v>
+        <v>30257</v>
       </c>
       <c r="H379">
         <v>34673</v>
@@ -10258,7 +10258,7 @@
         <v>23766</v>
       </c>
       <c r="C380">
-        <v>15936</v>
+        <v>16644</v>
       </c>
       <c r="D380">
         <v>21236</v>
@@ -10270,7 +10270,7 @@
         <v>31007</v>
       </c>
       <c r="G380">
-        <v>30240</v>
+        <v>30257</v>
       </c>
       <c r="H380">
         <v>34673</v>
@@ -10284,7 +10284,7 @@
         <v>23766</v>
       </c>
       <c r="C381">
-        <v>15936</v>
+        <v>16644</v>
       </c>
       <c r="D381">
         <v>21236</v>
@@ -10296,7 +10296,7 @@
         <v>31007</v>
       </c>
       <c r="G381">
-        <v>30240</v>
+        <v>30257</v>
       </c>
       <c r="H381">
         <v>34673</v>
@@ -10310,7 +10310,7 @@
         <v>21345</v>
       </c>
       <c r="C382">
-        <v>14415</v>
+        <v>14984</v>
       </c>
       <c r="D382">
         <v>17236</v>
@@ -10322,7 +10322,7 @@
         <v>27539</v>
       </c>
       <c r="G382">
-        <v>26008</v>
+        <v>26025</v>
       </c>
       <c r="H382">
         <v>30897</v>
@@ -10336,7 +10336,7 @@
         <v>22926</v>
       </c>
       <c r="C383">
-        <v>13656</v>
+        <v>13946</v>
       </c>
       <c r="D383">
         <v>13582</v>
@@ -10348,7 +10348,7 @@
         <v>26294</v>
       </c>
       <c r="G383">
-        <v>22286</v>
+        <v>22291</v>
       </c>
       <c r="H383">
         <v>30032</v>
@@ -10362,7 +10362,7 @@
         <v>20843</v>
       </c>
       <c r="C384">
-        <v>11947</v>
+        <v>12305</v>
       </c>
       <c r="D384">
         <v>13920</v>
@@ -10374,7 +10374,7 @@
         <v>24912</v>
       </c>
       <c r="G384">
-        <v>21260</v>
+        <v>21267</v>
       </c>
       <c r="H384">
         <v>27823</v>
@@ -10388,7 +10388,7 @@
         <v>27279</v>
       </c>
       <c r="C385">
-        <v>16528</v>
+        <v>16848</v>
       </c>
       <c r="D385">
         <v>23435</v>
@@ -10400,7 +10400,7 @@
         <v>35522</v>
       </c>
       <c r="G385">
-        <v>33250</v>
+        <v>33268</v>
       </c>
       <c r="H385">
         <v>39910</v>
@@ -10414,7 +10414,7 @@
         <v>14732</v>
       </c>
       <c r="C386">
-        <v>9876</v>
+        <v>9997</v>
       </c>
       <c r="D386">
         <v>6445</v>
@@ -10426,7 +10426,7 @@
         <v>16724</v>
       </c>
       <c r="G386">
-        <v>13850</v>
+        <v>13851</v>
       </c>
       <c r="H386">
         <v>20324</v>
@@ -10440,7 +10440,7 @@
         <v>14732</v>
       </c>
       <c r="C387">
-        <v>9876</v>
+        <v>9997</v>
       </c>
       <c r="D387">
         <v>6445</v>
@@ -10452,7 +10452,7 @@
         <v>16724</v>
       </c>
       <c r="G387">
-        <v>13850</v>
+        <v>13851</v>
       </c>
       <c r="H387">
         <v>20324</v>
@@ -10466,7 +10466,7 @@
         <v>4730</v>
       </c>
       <c r="C388">
-        <v>4344</v>
+        <v>4613</v>
       </c>
       <c r="D388">
         <v>4080</v>
@@ -10478,7 +10478,7 @@
         <v>5782</v>
       </c>
       <c r="G388">
-        <v>6491</v>
+        <v>6501</v>
       </c>
       <c r="H388">
         <v>7062</v>
@@ -10492,7 +10492,7 @@
         <v>3924</v>
       </c>
       <c r="C389">
-        <v>3597</v>
+        <v>3746</v>
       </c>
       <c r="D389">
         <v>1656</v>
@@ -10504,7 +10504,7 @@
         <v>4439</v>
       </c>
       <c r="G389">
-        <v>4511</v>
+        <v>4625</v>
       </c>
       <c r="H389">
         <v>5588</v>
@@ -10518,7 +10518,7 @@
         <v>3924</v>
       </c>
       <c r="C390">
-        <v>3597</v>
+        <v>3746</v>
       </c>
       <c r="D390">
         <v>1656</v>
@@ -10530,7 +10530,7 @@
         <v>4439</v>
       </c>
       <c r="G390">
-        <v>4511</v>
+        <v>4625</v>
       </c>
       <c r="H390">
         <v>5588</v>
@@ -10544,7 +10544,7 @@
         <v>4730</v>
       </c>
       <c r="C391">
-        <v>4344</v>
+        <v>4613</v>
       </c>
       <c r="D391">
         <v>4080</v>
@@ -10556,7 +10556,7 @@
         <v>5782</v>
       </c>
       <c r="G391">
-        <v>6491</v>
+        <v>6501</v>
       </c>
       <c r="H391">
         <v>7062</v>
@@ -10570,7 +10570,7 @@
         <v>3924</v>
       </c>
       <c r="C392">
-        <v>3597</v>
+        <v>3746</v>
       </c>
       <c r="D392">
         <v>1656</v>
@@ -10582,7 +10582,7 @@
         <v>4439</v>
       </c>
       <c r="G392">
-        <v>4511</v>
+        <v>4625</v>
       </c>
       <c r="H392">
         <v>5588</v>
@@ -10596,7 +10596,7 @@
         <v>3380</v>
       </c>
       <c r="C393">
-        <v>3292</v>
+        <v>3337</v>
       </c>
       <c r="D393">
         <v>1702</v>
@@ -10608,7 +10608,7 @@
         <v>3624</v>
       </c>
       <c r="G393">
-        <v>4005</v>
+        <v>4009</v>
       </c>
       <c r="H393">
         <v>4789</v>
@@ -10622,7 +10622,7 @@
         <v>3380</v>
       </c>
       <c r="C394">
-        <v>3292</v>
+        <v>3337</v>
       </c>
       <c r="D394">
         <v>1702</v>
@@ -10634,7 +10634,7 @@
         <v>3624</v>
       </c>
       <c r="G394">
-        <v>4005</v>
+        <v>4009</v>
       </c>
       <c r="H394">
         <v>4789</v>
@@ -10648,7 +10648,7 @@
         <v>3843</v>
       </c>
       <c r="C395">
-        <v>3719</v>
+        <v>3774</v>
       </c>
       <c r="D395">
         <v>1227</v>
@@ -10660,7 +10660,7 @@
         <v>4005</v>
       </c>
       <c r="G395">
-        <v>4225</v>
+        <v>4231</v>
       </c>
       <c r="H395">
         <v>5366</v>
@@ -10674,7 +10674,7 @@
         <v>3843</v>
       </c>
       <c r="C396">
-        <v>3719</v>
+        <v>3774</v>
       </c>
       <c r="D396">
         <v>1227</v>
@@ -10686,7 +10686,7 @@
         <v>4005</v>
       </c>
       <c r="G396">
-        <v>4225</v>
+        <v>4231</v>
       </c>
       <c r="H396">
         <v>5366</v>
@@ -10700,7 +10700,7 @@
         <v>5343</v>
       </c>
       <c r="C397">
-        <v>4128</v>
+        <v>4163</v>
       </c>
       <c r="D397">
         <v>524</v>
@@ -10712,7 +10712,7 @@
         <v>5475</v>
       </c>
       <c r="G397">
-        <v>4427</v>
+        <v>4441</v>
       </c>
       <c r="H397">
         <v>6347</v>
@@ -10726,7 +10726,7 @@
         <v>5343</v>
       </c>
       <c r="C398">
-        <v>4128</v>
+        <v>4163</v>
       </c>
       <c r="D398">
         <v>524</v>
@@ -10738,7 +10738,7 @@
         <v>5475</v>
       </c>
       <c r="G398">
-        <v>4427</v>
+        <v>4441</v>
       </c>
       <c r="H398">
         <v>6347</v>
@@ -10752,7 +10752,7 @@
         <v>3954</v>
       </c>
       <c r="C399">
-        <v>2929</v>
+        <v>3276</v>
       </c>
       <c r="D399">
         <v>2768</v>
@@ -10764,7 +10764,7 @@
         <v>4635</v>
       </c>
       <c r="G399">
-        <v>4438</v>
+        <v>4441</v>
       </c>
       <c r="H399">
         <v>5351</v>
@@ -10778,7 +10778,7 @@
         <v>3619</v>
       </c>
       <c r="C400">
-        <v>2864</v>
+        <v>3012</v>
       </c>
       <c r="D400">
         <v>2490</v>
@@ -10790,7 +10790,7 @@
         <v>4180</v>
       </c>
       <c r="G400">
-        <v>4158</v>
+        <v>4160</v>
       </c>
       <c r="H400">
         <v>4883</v>
@@ -10804,7 +10804,7 @@
         <v>3954</v>
       </c>
       <c r="C401">
-        <v>2929</v>
+        <v>3276</v>
       </c>
       <c r="D401">
         <v>2768</v>
@@ -10816,7 +10816,7 @@
         <v>4635</v>
       </c>
       <c r="G401">
-        <v>4438</v>
+        <v>4441</v>
       </c>
       <c r="H401">
         <v>5351</v>
@@ -10830,7 +10830,7 @@
         <v>4165</v>
       </c>
       <c r="C402">
-        <v>2681</v>
+        <v>2822</v>
       </c>
       <c r="D402">
         <v>1877</v>
@@ -10842,7 +10842,7 @@
         <v>4438</v>
       </c>
       <c r="G402">
-        <v>3594</v>
+        <v>3599</v>
       </c>
       <c r="H402">
         <v>4990</v>
@@ -10856,7 +10856,7 @@
         <v>3619</v>
       </c>
       <c r="C403">
-        <v>2864</v>
+        <v>3012</v>
       </c>
       <c r="D403">
         <v>2490</v>
@@ -10868,7 +10868,7 @@
         <v>4180</v>
       </c>
       <c r="G403">
-        <v>4158</v>
+        <v>4160</v>
       </c>
       <c r="H403">
         <v>4883</v>
@@ -10882,7 +10882,7 @@
         <v>3080</v>
       </c>
       <c r="C404">
-        <v>2476</v>
+        <v>2682</v>
       </c>
       <c r="D404">
         <v>2124</v>
@@ -10894,7 +10894,7 @@
         <v>3496</v>
       </c>
       <c r="G404">
-        <v>3556</v>
+        <v>3559</v>
       </c>
       <c r="H404">
         <v>4130</v>
@@ -10908,7 +10908,7 @@
         <v>3080</v>
       </c>
       <c r="C405">
-        <v>2476</v>
+        <v>2682</v>
       </c>
       <c r="D405">
         <v>2124</v>
@@ -10920,7 +10920,7 @@
         <v>3496</v>
       </c>
       <c r="G405">
-        <v>3556</v>
+        <v>3559</v>
       </c>
       <c r="H405">
         <v>4130</v>
@@ -10934,7 +10934,7 @@
         <v>3080</v>
       </c>
       <c r="C406">
-        <v>2476</v>
+        <v>2682</v>
       </c>
       <c r="D406">
         <v>2124</v>
@@ -10946,7 +10946,7 @@
         <v>3496</v>
       </c>
       <c r="G406">
-        <v>3556</v>
+        <v>3559</v>
       </c>
       <c r="H406">
         <v>4130</v>
@@ -10960,7 +10960,7 @@
         <v>2567</v>
       </c>
       <c r="C407">
-        <v>2285</v>
+        <v>2354</v>
       </c>
       <c r="D407">
         <v>1885</v>
@@ -10986,7 +10986,7 @@
         <v>2567</v>
       </c>
       <c r="C408">
-        <v>2285</v>
+        <v>2354</v>
       </c>
       <c r="D408">
         <v>1885</v>
@@ -11012,7 +11012,7 @@
         <v>2567</v>
       </c>
       <c r="C409">
-        <v>2285</v>
+        <v>2354</v>
       </c>
       <c r="D409">
         <v>1885</v>
@@ -11038,19 +11038,19 @@
         <v>5600</v>
       </c>
       <c r="C410">
-        <v>7045</v>
+        <v>7209</v>
       </c>
       <c r="D410">
         <v>5095</v>
       </c>
       <c r="E410">
-        <v>9425</v>
+        <v>9426</v>
       </c>
       <c r="F410">
         <v>8103</v>
       </c>
       <c r="G410">
-        <v>10354</v>
+        <v>10356</v>
       </c>
       <c r="H410">
         <v>11559</v>
@@ -11064,7 +11064,7 @@
         <v>4744</v>
       </c>
       <c r="C411">
-        <v>5464</v>
+        <v>5536</v>
       </c>
       <c r="D411">
         <v>3655</v>
@@ -11076,7 +11076,7 @@
         <v>6339</v>
       </c>
       <c r="G411">
-        <v>7836</v>
+        <v>7837</v>
       </c>
       <c r="H411">
         <v>8981</v>
@@ -11090,7 +11090,7 @@
         <v>4744</v>
       </c>
       <c r="C412">
-        <v>5464</v>
+        <v>5536</v>
       </c>
       <c r="D412">
         <v>3655</v>
@@ -11102,7 +11102,7 @@
         <v>6339</v>
       </c>
       <c r="G412">
-        <v>7836</v>
+        <v>7837</v>
       </c>
       <c r="H412">
         <v>8981</v>
@@ -11116,7 +11116,7 @@
         <v>4665</v>
       </c>
       <c r="C413">
-        <v>5577</v>
+        <v>5648</v>
       </c>
       <c r="D413">
         <v>1549</v>
@@ -11128,7 +11128,7 @@
         <v>5080</v>
       </c>
       <c r="G413">
-        <v>6447</v>
+        <v>6453</v>
       </c>
       <c r="H413">
         <v>8044</v>
@@ -11142,19 +11142,19 @@
         <v>5600</v>
       </c>
       <c r="C414">
-        <v>7045</v>
+        <v>7209</v>
       </c>
       <c r="D414">
         <v>5095</v>
       </c>
       <c r="E414">
-        <v>9425</v>
+        <v>9426</v>
       </c>
       <c r="F414">
         <v>8103</v>
       </c>
       <c r="G414">
-        <v>10354</v>
+        <v>10356</v>
       </c>
       <c r="H414">
         <v>11559</v>
@@ -11168,7 +11168,7 @@
         <v>5505</v>
       </c>
       <c r="C415">
-        <v>5617</v>
+        <v>5667</v>
       </c>
       <c r="D415">
         <v>5136</v>
@@ -11180,7 +11180,7 @@
         <v>8223</v>
       </c>
       <c r="G415">
-        <v>9071</v>
+        <v>9072</v>
       </c>
       <c r="H415">
         <v>10503</v>
@@ -11194,7 +11194,7 @@
         <v>5505</v>
       </c>
       <c r="C416">
-        <v>5617</v>
+        <v>5667</v>
       </c>
       <c r="D416">
         <v>5136</v>
@@ -11206,7 +11206,7 @@
         <v>8223</v>
       </c>
       <c r="G416">
-        <v>9071</v>
+        <v>9072</v>
       </c>
       <c r="H416">
         <v>10503</v>
@@ -11220,7 +11220,7 @@
         <v>4890</v>
       </c>
       <c r="C417">
-        <v>3891</v>
+        <v>4036</v>
       </c>
       <c r="D417">
         <v>2355</v>
@@ -11232,7 +11232,7 @@
         <v>5340</v>
       </c>
       <c r="G417">
-        <v>5023</v>
+        <v>5024</v>
       </c>
       <c r="H417">
         <v>6685</v>
@@ -11246,7 +11246,7 @@
         <v>4890</v>
       </c>
       <c r="C418">
-        <v>3891</v>
+        <v>4036</v>
       </c>
       <c r="D418">
         <v>2355</v>
@@ -11258,7 +11258,7 @@
         <v>5340</v>
       </c>
       <c r="G418">
-        <v>5023</v>
+        <v>5024</v>
       </c>
       <c r="H418">
         <v>6685</v>
@@ -11272,7 +11272,7 @@
         <v>9125</v>
       </c>
       <c r="C419">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D419">
         <v>5044</v>
@@ -11284,7 +11284,7 @@
         <v>10505</v>
       </c>
       <c r="G419">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H419">
         <v>12731</v>
@@ -11298,7 +11298,7 @@
         <v>9125</v>
       </c>
       <c r="C420">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D420">
         <v>5044</v>
@@ -11310,7 +11310,7 @@
         <v>10505</v>
       </c>
       <c r="G420">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H420">
         <v>12731</v>
@@ -11324,7 +11324,7 @@
         <v>9125</v>
       </c>
       <c r="C421">
-        <v>6595</v>
+        <v>6979</v>
       </c>
       <c r="D421">
         <v>5044</v>
@@ -11336,7 +11336,7 @@
         <v>10505</v>
       </c>
       <c r="G421">
-        <v>9645</v>
+        <v>9664</v>
       </c>
       <c r="H421">
         <v>12536</v>
@@ -11350,7 +11350,7 @@
         <v>9125</v>
       </c>
       <c r="C422">
-        <v>6595</v>
+        <v>6979</v>
       </c>
       <c r="D422">
         <v>5044</v>
@@ -11362,7 +11362,7 @@
         <v>10505</v>
       </c>
       <c r="G422">
-        <v>9645</v>
+        <v>9664</v>
       </c>
       <c r="H422">
         <v>12536</v>
@@ -11376,7 +11376,7 @@
         <v>9125</v>
       </c>
       <c r="C423">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D423">
         <v>5044</v>
@@ -11388,7 +11388,7 @@
         <v>10505</v>
       </c>
       <c r="G423">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H423">
         <v>12731</v>
@@ -11402,7 +11402,7 @@
         <v>9125</v>
       </c>
       <c r="C424">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D424">
         <v>5044</v>
@@ -11414,7 +11414,7 @@
         <v>10505</v>
       </c>
       <c r="G424">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H424">
         <v>12731</v>
@@ -11428,7 +11428,7 @@
         <v>9125</v>
       </c>
       <c r="C425">
-        <v>6595</v>
+        <v>6979</v>
       </c>
       <c r="D425">
         <v>5044</v>
@@ -11440,7 +11440,7 @@
         <v>10505</v>
       </c>
       <c r="G425">
-        <v>9645</v>
+        <v>9664</v>
       </c>
       <c r="H425">
         <v>12536</v>
@@ -11454,7 +11454,7 @@
         <v>9125</v>
       </c>
       <c r="C426">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D426">
         <v>5044</v>
@@ -11466,7 +11466,7 @@
         <v>10505</v>
       </c>
       <c r="G426">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H426">
         <v>12731</v>
@@ -11480,7 +11480,7 @@
         <v>9125</v>
       </c>
       <c r="C427">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D427">
         <v>5044</v>
@@ -11492,7 +11492,7 @@
         <v>10505</v>
       </c>
       <c r="G427">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H427">
         <v>12731</v>
@@ -11506,7 +11506,7 @@
         <v>9125</v>
       </c>
       <c r="C428">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D428">
         <v>5044</v>
@@ -11518,7 +11518,7 @@
         <v>10505</v>
       </c>
       <c r="G428">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H428">
         <v>12731</v>
@@ -11532,7 +11532,7 @@
         <v>9125</v>
       </c>
       <c r="C429">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D429">
         <v>5044</v>
@@ -11544,7 +11544,7 @@
         <v>10505</v>
       </c>
       <c r="G429">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H429">
         <v>12731</v>
@@ -11558,7 +11558,7 @@
         <v>9125</v>
       </c>
       <c r="C430">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D430">
         <v>5044</v>
@@ -11570,7 +11570,7 @@
         <v>10505</v>
       </c>
       <c r="G430">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H430">
         <v>12731</v>
@@ -11584,7 +11584,7 @@
         <v>9125</v>
       </c>
       <c r="C431">
-        <v>6595</v>
+        <v>6979</v>
       </c>
       <c r="D431">
         <v>5044</v>
@@ -11596,7 +11596,7 @@
         <v>10505</v>
       </c>
       <c r="G431">
-        <v>9645</v>
+        <v>9664</v>
       </c>
       <c r="H431">
         <v>12536</v>
@@ -11610,7 +11610,7 @@
         <v>9125</v>
       </c>
       <c r="C432">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D432">
         <v>5044</v>
@@ -11622,7 +11622,7 @@
         <v>10505</v>
       </c>
       <c r="G432">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H432">
         <v>12731</v>
@@ -11636,7 +11636,7 @@
         <v>9125</v>
       </c>
       <c r="C433">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D433">
         <v>5044</v>
@@ -11648,7 +11648,7 @@
         <v>10505</v>
       </c>
       <c r="G433">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H433">
         <v>12731</v>
@@ -11662,7 +11662,7 @@
         <v>7106</v>
       </c>
       <c r="C434">
-        <v>4710</v>
+        <v>4874</v>
       </c>
       <c r="D434">
         <v>3484</v>
@@ -11674,7 +11674,7 @@
         <v>8164</v>
       </c>
       <c r="G434">
-        <v>6793</v>
+        <v>6800</v>
       </c>
       <c r="H434">
         <v>9371</v>
@@ -11688,7 +11688,7 @@
         <v>9125</v>
       </c>
       <c r="C435">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D435">
         <v>5044</v>
@@ -11700,7 +11700,7 @@
         <v>10505</v>
       </c>
       <c r="G435">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H435">
         <v>12731</v>
@@ -11714,7 +11714,7 @@
         <v>5370</v>
       </c>
       <c r="C436">
-        <v>4751</v>
+        <v>4787</v>
       </c>
       <c r="D436">
         <v>514</v>
@@ -11726,7 +11726,7 @@
         <v>5454</v>
       </c>
       <c r="G436">
-        <v>4961</v>
+        <v>4974</v>
       </c>
       <c r="H436">
         <v>7272</v>
@@ -11740,7 +11740,7 @@
         <v>4586</v>
       </c>
       <c r="C437">
-        <v>3529</v>
+        <v>3603</v>
       </c>
       <c r="D437">
         <v>1871</v>
@@ -11752,7 +11752,7 @@
         <v>5137</v>
       </c>
       <c r="G437">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="H437">
         <v>6310</v>
@@ -11766,7 +11766,7 @@
         <v>4586</v>
       </c>
       <c r="C438">
-        <v>3529</v>
+        <v>3603</v>
       </c>
       <c r="D438">
         <v>1871</v>
@@ -11778,7 +11778,7 @@
         <v>5137</v>
       </c>
       <c r="G438">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="H438">
         <v>6310</v>
@@ -11792,7 +11792,7 @@
         <v>4586</v>
       </c>
       <c r="C439">
-        <v>3529</v>
+        <v>3603</v>
       </c>
       <c r="D439">
         <v>1871</v>
@@ -11804,7 +11804,7 @@
         <v>5137</v>
       </c>
       <c r="G439">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="H439">
         <v>6310</v>
@@ -11818,7 +11818,7 @@
         <v>4586</v>
       </c>
       <c r="C440">
-        <v>3529</v>
+        <v>3603</v>
       </c>
       <c r="D440">
         <v>1871</v>
@@ -11830,7 +11830,7 @@
         <v>5137</v>
       </c>
       <c r="G440">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="H440">
         <v>6310</v>
@@ -11844,7 +11844,7 @@
         <v>4586</v>
       </c>
       <c r="C441">
-        <v>3529</v>
+        <v>3603</v>
       </c>
       <c r="D441">
         <v>1871</v>
@@ -11856,7 +11856,7 @@
         <v>5137</v>
       </c>
       <c r="G441">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="H441">
         <v>6310</v>
@@ -11870,7 +11870,7 @@
         <v>4586</v>
       </c>
       <c r="C442">
-        <v>3529</v>
+        <v>3603</v>
       </c>
       <c r="D442">
         <v>1871</v>
@@ -11882,7 +11882,7 @@
         <v>5137</v>
       </c>
       <c r="G442">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="H442">
         <v>6310</v>
@@ -11896,7 +11896,7 @@
         <v>4586</v>
       </c>
       <c r="C443">
-        <v>3529</v>
+        <v>3603</v>
       </c>
       <c r="D443">
         <v>1871</v>
@@ -11908,7 +11908,7 @@
         <v>5137</v>
       </c>
       <c r="G443">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="H443">
         <v>6310</v>
@@ -11922,7 +11922,7 @@
         <v>4586</v>
       </c>
       <c r="C444">
-        <v>3529</v>
+        <v>3603</v>
       </c>
       <c r="D444">
         <v>1871</v>
@@ -11934,7 +11934,7 @@
         <v>5137</v>
       </c>
       <c r="G444">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="H444">
         <v>6310</v>
@@ -11948,7 +11948,7 @@
         <v>4586</v>
       </c>
       <c r="C445">
-        <v>3529</v>
+        <v>3603</v>
       </c>
       <c r="D445">
         <v>1871</v>
@@ -11960,7 +11960,7 @@
         <v>5137</v>
       </c>
       <c r="G445">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="H445">
         <v>6310</v>
@@ -11974,7 +11974,7 @@
         <v>4586</v>
       </c>
       <c r="C446">
-        <v>3529</v>
+        <v>3603</v>
       </c>
       <c r="D446">
         <v>1871</v>
@@ -11986,7 +11986,7 @@
         <v>5137</v>
       </c>
       <c r="G446">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="H446">
         <v>6310</v>
@@ -12000,7 +12000,7 @@
         <v>4586</v>
       </c>
       <c r="C447">
-        <v>3529</v>
+        <v>3603</v>
       </c>
       <c r="D447">
         <v>1871</v>
@@ -12012,7 +12012,7 @@
         <v>5137</v>
       </c>
       <c r="G447">
-        <v>4579</v>
+        <v>4580</v>
       </c>
       <c r="H447">
         <v>6310</v>
@@ -12026,7 +12026,7 @@
         <v>18252</v>
       </c>
       <c r="C448">
-        <v>9589</v>
+        <v>9778</v>
       </c>
       <c r="D448">
         <v>5403</v>
@@ -12038,7 +12038,7 @@
         <v>19280</v>
       </c>
       <c r="G448">
-        <v>12893</v>
+        <v>12979</v>
       </c>
       <c r="H448">
         <v>21237</v>
@@ -12052,7 +12052,7 @@
         <v>18252</v>
       </c>
       <c r="C449">
-        <v>9589</v>
+        <v>9778</v>
       </c>
       <c r="D449">
         <v>5403</v>
@@ -12064,7 +12064,7 @@
         <v>19280</v>
       </c>
       <c r="G449">
-        <v>12893</v>
+        <v>12979</v>
       </c>
       <c r="H449">
         <v>21237</v>
@@ -12078,7 +12078,7 @@
         <v>18252</v>
       </c>
       <c r="C450">
-        <v>9589</v>
+        <v>9778</v>
       </c>
       <c r="D450">
         <v>5403</v>
@@ -12090,7 +12090,7 @@
         <v>19280</v>
       </c>
       <c r="G450">
-        <v>12893</v>
+        <v>12979</v>
       </c>
       <c r="H450">
         <v>21237</v>
@@ -12104,7 +12104,7 @@
         <v>18252</v>
       </c>
       <c r="C451">
-        <v>9589</v>
+        <v>9778</v>
       </c>
       <c r="D451">
         <v>5403</v>
@@ -12116,7 +12116,7 @@
         <v>19280</v>
       </c>
       <c r="G451">
-        <v>12893</v>
+        <v>12979</v>
       </c>
       <c r="H451">
         <v>21237</v>
@@ -12130,7 +12130,7 @@
         <v>18252</v>
       </c>
       <c r="C452">
-        <v>9589</v>
+        <v>9778</v>
       </c>
       <c r="D452">
         <v>5403</v>
@@ -12142,7 +12142,7 @@
         <v>19280</v>
       </c>
       <c r="G452">
-        <v>12893</v>
+        <v>12979</v>
       </c>
       <c r="H452">
         <v>21237</v>
@@ -12156,7 +12156,7 @@
         <v>18252</v>
       </c>
       <c r="C453">
-        <v>9589</v>
+        <v>9778</v>
       </c>
       <c r="D453">
         <v>5403</v>
@@ -12168,7 +12168,7 @@
         <v>19280</v>
       </c>
       <c r="G453">
-        <v>12893</v>
+        <v>12979</v>
       </c>
       <c r="H453">
         <v>21237</v>
@@ -12182,7 +12182,7 @@
         <v>11766</v>
       </c>
       <c r="C454">
-        <v>8295</v>
+        <v>8473</v>
       </c>
       <c r="D454">
         <v>7553</v>
@@ -12194,7 +12194,7 @@
         <v>13718</v>
       </c>
       <c r="G454">
-        <v>12788</v>
+        <v>12798</v>
       </c>
       <c r="H454">
         <v>16246</v>
@@ -12208,7 +12208,7 @@
         <v>11766</v>
       </c>
       <c r="C455">
-        <v>8295</v>
+        <v>8473</v>
       </c>
       <c r="D455">
         <v>7553</v>
@@ -12220,7 +12220,7 @@
         <v>13718</v>
       </c>
       <c r="G455">
-        <v>12788</v>
+        <v>12798</v>
       </c>
       <c r="H455">
         <v>16246</v>
@@ -12234,7 +12234,7 @@
         <v>11766</v>
       </c>
       <c r="C456">
-        <v>8295</v>
+        <v>8473</v>
       </c>
       <c r="D456">
         <v>7553</v>
@@ -12246,7 +12246,7 @@
         <v>13718</v>
       </c>
       <c r="G456">
-        <v>12788</v>
+        <v>12798</v>
       </c>
       <c r="H456">
         <v>16246</v>
@@ -12260,7 +12260,7 @@
         <v>11766</v>
       </c>
       <c r="C457">
-        <v>8295</v>
+        <v>8473</v>
       </c>
       <c r="D457">
         <v>7553</v>
@@ -12272,7 +12272,7 @@
         <v>13718</v>
       </c>
       <c r="G457">
-        <v>12788</v>
+        <v>12798</v>
       </c>
       <c r="H457">
         <v>16246</v>
@@ -12286,7 +12286,7 @@
         <v>11766</v>
       </c>
       <c r="C458">
-        <v>8295</v>
+        <v>8473</v>
       </c>
       <c r="D458">
         <v>7553</v>
@@ -12298,7 +12298,7 @@
         <v>13718</v>
       </c>
       <c r="G458">
-        <v>12788</v>
+        <v>12798</v>
       </c>
       <c r="H458">
         <v>16246</v>
@@ -12312,7 +12312,7 @@
         <v>11766</v>
       </c>
       <c r="C459">
-        <v>8295</v>
+        <v>8473</v>
       </c>
       <c r="D459">
         <v>7553</v>
@@ -12324,7 +12324,7 @@
         <v>13718</v>
       </c>
       <c r="G459">
-        <v>12788</v>
+        <v>12798</v>
       </c>
       <c r="H459">
         <v>16246</v>
@@ -12338,7 +12338,7 @@
         <v>11766</v>
       </c>
       <c r="C460">
-        <v>8295</v>
+        <v>8473</v>
       </c>
       <c r="D460">
         <v>7553</v>
@@ -12350,7 +12350,7 @@
         <v>13718</v>
       </c>
       <c r="G460">
-        <v>12788</v>
+        <v>12798</v>
       </c>
       <c r="H460">
         <v>16246</v>
@@ -12364,7 +12364,7 @@
         <v>11766</v>
       </c>
       <c r="C461">
-        <v>8295</v>
+        <v>8473</v>
       </c>
       <c r="D461">
         <v>7553</v>
@@ -12376,7 +12376,7 @@
         <v>13718</v>
       </c>
       <c r="G461">
-        <v>12788</v>
+        <v>12798</v>
       </c>
       <c r="H461">
         <v>16246</v>
@@ -12390,7 +12390,7 @@
         <v>11766</v>
       </c>
       <c r="C462">
-        <v>8295</v>
+        <v>8473</v>
       </c>
       <c r="D462">
         <v>7553</v>
@@ -12402,7 +12402,7 @@
         <v>13718</v>
       </c>
       <c r="G462">
-        <v>12788</v>
+        <v>12798</v>
       </c>
       <c r="H462">
         <v>16246</v>
@@ -12416,7 +12416,7 @@
         <v>9125</v>
       </c>
       <c r="C463">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D463">
         <v>5044</v>
@@ -12428,7 +12428,7 @@
         <v>10505</v>
       </c>
       <c r="G463">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H463">
         <v>12731</v>
@@ -12442,7 +12442,7 @@
         <v>9125</v>
       </c>
       <c r="C464">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D464">
         <v>5044</v>
@@ -12454,7 +12454,7 @@
         <v>10505</v>
       </c>
       <c r="G464">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H464">
         <v>12731</v>
@@ -12468,7 +12468,7 @@
         <v>7106</v>
       </c>
       <c r="C465">
-        <v>4710</v>
+        <v>4874</v>
       </c>
       <c r="D465">
         <v>3484</v>
@@ -12480,7 +12480,7 @@
         <v>8164</v>
       </c>
       <c r="G465">
-        <v>6793</v>
+        <v>6800</v>
       </c>
       <c r="H465">
         <v>9371</v>
@@ -12494,7 +12494,7 @@
         <v>7106</v>
       </c>
       <c r="C466">
-        <v>4710</v>
+        <v>4874</v>
       </c>
       <c r="D466">
         <v>3484</v>
@@ -12506,7 +12506,7 @@
         <v>8164</v>
       </c>
       <c r="G466">
-        <v>6793</v>
+        <v>6800</v>
       </c>
       <c r="H466">
         <v>9371</v>
@@ -12520,7 +12520,7 @@
         <v>9125</v>
       </c>
       <c r="C467">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D467">
         <v>5044</v>
@@ -12532,7 +12532,7 @@
         <v>10505</v>
       </c>
       <c r="G467">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H467">
         <v>12731</v>
@@ -12546,7 +12546,7 @@
         <v>18252</v>
       </c>
       <c r="C468">
-        <v>9589</v>
+        <v>9778</v>
       </c>
       <c r="D468">
         <v>5403</v>
@@ -12558,7 +12558,7 @@
         <v>19280</v>
       </c>
       <c r="G468">
-        <v>12893</v>
+        <v>12979</v>
       </c>
       <c r="H468">
         <v>21237</v>
@@ -12572,7 +12572,7 @@
         <v>18252</v>
       </c>
       <c r="C469">
-        <v>9589</v>
+        <v>9778</v>
       </c>
       <c r="D469">
         <v>5403</v>
@@ -12584,7 +12584,7 @@
         <v>19280</v>
       </c>
       <c r="G469">
-        <v>12893</v>
+        <v>12979</v>
       </c>
       <c r="H469">
         <v>21237</v>
@@ -12598,7 +12598,7 @@
         <v>18252</v>
       </c>
       <c r="C470">
-        <v>9589</v>
+        <v>9778</v>
       </c>
       <c r="D470">
         <v>5403</v>
@@ -12610,7 +12610,7 @@
         <v>19280</v>
       </c>
       <c r="G470">
-        <v>12893</v>
+        <v>12979</v>
       </c>
       <c r="H470">
         <v>21237</v>
@@ -12624,7 +12624,7 @@
         <v>9125</v>
       </c>
       <c r="C471">
-        <v>6852</v>
+        <v>7225</v>
       </c>
       <c r="D471">
         <v>5044</v>
@@ -12636,7 +12636,7 @@
         <v>10505</v>
       </c>
       <c r="G471">
-        <v>9870</v>
+        <v>9883</v>
       </c>
       <c r="H471">
         <v>12731</v>
@@ -12650,7 +12650,7 @@
         <v>11766</v>
       </c>
       <c r="C472">
-        <v>8295</v>
+        <v>8473</v>
       </c>
       <c r="D472">
         <v>7553</v>
@@ -12662,7 +12662,7 @@
         <v>13718</v>
       </c>
       <c r="G472">
-        <v>12788</v>
+        <v>12798</v>
       </c>
       <c r="H472">
         <v>16246</v>
@@ -12676,7 +12676,7 @@
         <v>7106</v>
       </c>
       <c r="C473">
-        <v>4710</v>
+        <v>4874</v>
       </c>
       <c r="D473">
         <v>3484</v>
@@ -12688,7 +12688,7 @@
         <v>8164</v>
       </c>
       <c r="G473">
-        <v>6793</v>
+        <v>6800</v>
       </c>
       <c r="H473">
         <v>9371</v>
@@ -12702,7 +12702,7 @@
         <v>7106</v>
       </c>
       <c r="C474">
-        <v>4710</v>
+        <v>4874</v>
       </c>
       <c r="D474">
         <v>3484</v>
@@ -12714,7 +12714,7 @@
         <v>8164</v>
       </c>
       <c r="G474">
-        <v>6793</v>
+        <v>6800</v>
       </c>
       <c r="H474">
         <v>9371</v>
@@ -12728,7 +12728,7 @@
         <v>5370</v>
       </c>
       <c r="C475">
-        <v>4751</v>
+        <v>4787</v>
       </c>
       <c r="D475">
         <v>514</v>
@@ -12740,7 +12740,7 @@
         <v>5454</v>
       </c>
       <c r="G475">
-        <v>4961</v>
+        <v>4974</v>
       </c>
       <c r="H475">
         <v>7272</v>
@@ -12754,7 +12754,7 @@
         <v>6079</v>
       </c>
       <c r="C476">
-        <v>4366</v>
+        <v>4393</v>
       </c>
       <c r="D476">
         <v>2622</v>
@@ -12766,7 +12766,7 @@
         <v>6772</v>
       </c>
       <c r="G476">
-        <v>5837</v>
+        <v>5841</v>
       </c>
       <c r="H476">
         <v>8129</v>
@@ -12780,7 +12780,7 @@
         <v>6079</v>
       </c>
       <c r="C477">
-        <v>4366</v>
+        <v>4393</v>
       </c>
       <c r="D477">
         <v>2622</v>
@@ -12792,7 +12792,7 @@
         <v>6772</v>
       </c>
       <c r="G477">
-        <v>5837</v>
+        <v>5841</v>
       </c>
       <c r="H477">
         <v>8129</v>
@@ -12806,7 +12806,7 @@
         <v>6705</v>
       </c>
       <c r="C478">
-        <v>5824</v>
+        <v>6282</v>
       </c>
       <c r="D478">
         <v>4776</v>
@@ -12818,7 +12818,7 @@
         <v>7804</v>
       </c>
       <c r="G478">
-        <v>8301</v>
+        <v>8313</v>
       </c>
       <c r="H478">
         <v>9518</v>
@@ -12832,7 +12832,7 @@
         <v>5736</v>
       </c>
       <c r="C479">
-        <v>5166</v>
+        <v>5444</v>
       </c>
       <c r="D479">
         <v>4577</v>
@@ -12844,7 +12844,7 @@
         <v>6828</v>
       </c>
       <c r="G479">
-        <v>7648</v>
+        <v>7652</v>
       </c>
       <c r="H479">
         <v>8474</v>
@@ -12858,7 +12858,7 @@
         <v>6705</v>
       </c>
       <c r="C480">
-        <v>5994</v>
+        <v>6441</v>
       </c>
       <c r="D480">
         <v>4776</v>
@@ -12870,7 +12870,7 @@
         <v>7804</v>
       </c>
       <c r="G480">
-        <v>8454</v>
+        <v>8464</v>
       </c>
       <c r="H480">
         <v>9654</v>
@@ -12884,7 +12884,7 @@
         <v>6705</v>
       </c>
       <c r="C481">
-        <v>5824</v>
+        <v>6282</v>
       </c>
       <c r="D481">
         <v>4776</v>
@@ -12896,7 +12896,7 @@
         <v>7804</v>
       </c>
       <c r="G481">
-        <v>8301</v>
+        <v>8313</v>
       </c>
       <c r="H481">
         <v>9518</v>
@@ -12910,7 +12910,7 @@
         <v>6705</v>
       </c>
       <c r="C482">
-        <v>5824</v>
+        <v>6282</v>
       </c>
       <c r="D482">
         <v>4776</v>
@@ -12922,7 +12922,7 @@
         <v>7804</v>
       </c>
       <c r="G482">
-        <v>8301</v>
+        <v>8313</v>
       </c>
       <c r="H482">
         <v>9518</v>
@@ -12936,7 +12936,7 @@
         <v>6705</v>
       </c>
       <c r="C483">
-        <v>5824</v>
+        <v>6282</v>
       </c>
       <c r="D483">
         <v>4776</v>
@@ -12948,7 +12948,7 @@
         <v>7804</v>
       </c>
       <c r="G483">
-        <v>8301</v>
+        <v>8313</v>
       </c>
       <c r="H483">
         <v>9518</v>
@@ -12962,7 +12962,7 @@
         <v>6705</v>
       </c>
       <c r="C484">
-        <v>5824</v>
+        <v>6282</v>
       </c>
       <c r="D484">
         <v>4776</v>
@@ -12974,7 +12974,7 @@
         <v>7804</v>
       </c>
       <c r="G484">
-        <v>8301</v>
+        <v>8313</v>
       </c>
       <c r="H484">
         <v>9518</v>
@@ -12988,7 +12988,7 @@
         <v>6705</v>
       </c>
       <c r="C485">
-        <v>5994</v>
+        <v>6441</v>
       </c>
       <c r="D485">
         <v>4776</v>
@@ -13000,7 +13000,7 @@
         <v>7804</v>
       </c>
       <c r="G485">
-        <v>8454</v>
+        <v>8464</v>
       </c>
       <c r="H485">
         <v>9654</v>
@@ -13014,7 +13014,7 @@
         <v>6217</v>
       </c>
       <c r="C486">
-        <v>5718</v>
+        <v>5901</v>
       </c>
       <c r="D486">
         <v>4973</v>
@@ -13026,7 +13026,7 @@
         <v>7485</v>
       </c>
       <c r="G486">
-        <v>8350</v>
+        <v>8352</v>
       </c>
       <c r="H486">
         <v>9307</v>
@@ -13040,7 +13040,7 @@
         <v>6471</v>
       </c>
       <c r="C487">
-        <v>5394</v>
+        <v>5582</v>
       </c>
       <c r="D487">
         <v>4169</v>
@@ -13052,7 +13052,7 @@
         <v>7319</v>
       </c>
       <c r="G487">
-        <v>7556</v>
+        <v>7560</v>
       </c>
       <c r="H487">
         <v>8841</v>
@@ -13066,7 +13066,7 @@
         <v>6471</v>
       </c>
       <c r="C488">
-        <v>5834</v>
+        <v>5896</v>
       </c>
       <c r="D488">
         <v>839</v>
@@ -13078,7 +13078,7 @@
         <v>6722</v>
       </c>
       <c r="G488">
-        <v>6283</v>
+        <v>6305</v>
       </c>
       <c r="H488">
         <v>8734</v>
@@ -13092,7 +13092,7 @@
         <v>6471</v>
       </c>
       <c r="C489">
-        <v>5834</v>
+        <v>5896</v>
       </c>
       <c r="D489">
         <v>839</v>
@@ -13104,7 +13104,7 @@
         <v>6722</v>
       </c>
       <c r="G489">
-        <v>6283</v>
+        <v>6305</v>
       </c>
       <c r="H489">
         <v>8734</v>
@@ -13118,7 +13118,7 @@
         <v>8602</v>
       </c>
       <c r="C490">
-        <v>7837</v>
+        <v>8066</v>
       </c>
       <c r="D490">
         <v>6475</v>
@@ -13130,7 +13130,7 @@
         <v>10620</v>
       </c>
       <c r="G490">
-        <v>11443</v>
+        <v>11446</v>
       </c>
       <c r="H490">
         <v>13318</v>
@@ -13144,7 +13144,7 @@
         <v>8602</v>
       </c>
       <c r="C491">
-        <v>7837</v>
+        <v>8066</v>
       </c>
       <c r="D491">
         <v>6475</v>
@@ -13156,7 +13156,7 @@
         <v>10620</v>
       </c>
       <c r="G491">
-        <v>11443</v>
+        <v>11446</v>
       </c>
       <c r="H491">
         <v>13318</v>
@@ -13170,7 +13170,7 @@
         <v>8602</v>
       </c>
       <c r="C492">
-        <v>7837</v>
+        <v>8066</v>
       </c>
       <c r="D492">
         <v>6475</v>
@@ -13182,7 +13182,7 @@
         <v>10620</v>
       </c>
       <c r="G492">
-        <v>11443</v>
+        <v>11446</v>
       </c>
       <c r="H492">
         <v>13318</v>
@@ -13196,7 +13196,7 @@
         <v>8602</v>
       </c>
       <c r="C493">
-        <v>7837</v>
+        <v>8066</v>
       </c>
       <c r="D493">
         <v>6475</v>
@@ -13208,7 +13208,7 @@
         <v>10620</v>
       </c>
       <c r="G493">
-        <v>11443</v>
+        <v>11446</v>
       </c>
       <c r="H493">
         <v>13318</v>
@@ -13222,7 +13222,7 @@
         <v>8602</v>
       </c>
       <c r="C494">
-        <v>7837</v>
+        <v>8066</v>
       </c>
       <c r="D494">
         <v>6475</v>
@@ -13234,7 +13234,7 @@
         <v>10620</v>
       </c>
       <c r="G494">
-        <v>11443</v>
+        <v>11446</v>
       </c>
       <c r="H494">
         <v>13318</v>
@@ -13248,7 +13248,7 @@
         <v>6976</v>
       </c>
       <c r="C495">
-        <v>7462</v>
+        <v>7579</v>
       </c>
       <c r="D495">
         <v>1809</v>
@@ -13260,7 +13260,7 @@
         <v>7227</v>
       </c>
       <c r="G495">
-        <v>8306</v>
+        <v>8372</v>
       </c>
       <c r="H495">
         <v>10602</v>
@@ -13274,7 +13274,7 @@
         <v>8321</v>
       </c>
       <c r="C496">
-        <v>8280</v>
+        <v>8409</v>
       </c>
       <c r="D496">
         <v>4895</v>
@@ -13286,7 +13286,7 @@
         <v>9768</v>
       </c>
       <c r="G496">
-        <v>10931</v>
+        <v>10936</v>
       </c>
       <c r="H496">
         <v>13211</v>
@@ -13300,7 +13300,7 @@
         <v>6976</v>
       </c>
       <c r="C497">
-        <v>7462</v>
+        <v>7579</v>
       </c>
       <c r="D497">
         <v>1809</v>
@@ -13312,7 +13312,7 @@
         <v>7227</v>
       </c>
       <c r="G497">
-        <v>8306</v>
+        <v>8372</v>
       </c>
       <c r="H497">
         <v>10602</v>
@@ -13326,7 +13326,7 @@
         <v>10483</v>
       </c>
       <c r="C498">
-        <v>8530</v>
+        <v>8629</v>
       </c>
       <c r="D498">
         <v>1668</v>
@@ -13338,7 +13338,7 @@
         <v>10844</v>
       </c>
       <c r="G498">
-        <v>9414</v>
+        <v>9445</v>
       </c>
       <c r="H498">
         <v>14143</v>
@@ -13352,7 +13352,7 @@
         <v>10483</v>
       </c>
       <c r="C499">
-        <v>8530</v>
+        <v>8629</v>
       </c>
       <c r="D499">
         <v>1668</v>
@@ -13364,7 +13364,7 @@
         <v>10844</v>
       </c>
       <c r="G499">
-        <v>9414</v>
+        <v>9445</v>
       </c>
       <c r="H499">
         <v>14143</v>
@@ -13378,7 +13378,7 @@
         <v>10483</v>
       </c>
       <c r="C500">
-        <v>8530</v>
+        <v>8629</v>
       </c>
       <c r="D500">
         <v>1668</v>
@@ -13390,7 +13390,7 @@
         <v>10844</v>
       </c>
       <c r="G500">
-        <v>9414</v>
+        <v>9445</v>
       </c>
       <c r="H500">
         <v>14143</v>
@@ -13404,7 +13404,7 @@
         <v>8145</v>
       </c>
       <c r="C501">
-        <v>6355</v>
+        <v>6414</v>
       </c>
       <c r="D501">
         <v>1371</v>
@@ -13416,7 +13416,7 @@
         <v>8514</v>
       </c>
       <c r="G501">
-        <v>7117</v>
+        <v>7135</v>
       </c>
       <c r="H501">
         <v>10540</v>

--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_laag.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_laag.xlsx
@@ -14,15 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
   <si>
     <t>Fiets</t>
-  </si>
-  <si>
-    <t>EFiets</t>
   </si>
   <si>
     <t>Auto</t>
@@ -37,19 +34,10 @@
     <t>OV_Fiets</t>
   </si>
   <si>
-    <t>Auto_EFiets</t>
-  </si>
-  <si>
-    <t>OV_EFiets</t>
-  </si>
-  <si>
     <t>Auto_OV</t>
   </si>
   <si>
     <t>Auto_OV_Fiets</t>
-  </si>
-  <si>
-    <t>Auto_OV_EFiets</t>
   </si>
 </sst>
 </file>
@@ -381,10 +369,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L501"/>
+  <dimension ref="A1:H501"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -409,20 +397,8 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -448,7 +424,7 @@
         <v>17594</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -474,7 +450,7 @@
         <v>17857</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -500,7 +476,7 @@
         <v>14363</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -526,7 +502,7 @@
         <v>14363</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
@@ -552,7 +528,7 @@
         <v>14363</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
@@ -578,7 +554,7 @@
         <v>17532</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -604,7 +580,7 @@
         <v>17532</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
@@ -630,7 +606,7 @@
         <v>17214</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
@@ -656,7 +632,7 @@
         <v>17532</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
@@ -682,7 +658,7 @@
         <v>17532</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
@@ -708,7 +684,7 @@
         <v>14363</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
@@ -734,7 +710,7 @@
         <v>17857</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>13</v>
       </c>
@@ -760,7 +736,7 @@
         <v>14363</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>14</v>
       </c>
@@ -786,7 +762,7 @@
         <v>17532</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>15</v>
       </c>
